--- a/research/traditional_assets/database/data/belgium/belgium_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_telecom_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.1435631124884831</v>
       </c>
       <c r="X2">
-        <v>0.1442155697055857</v>
+        <v>0.1441696086642596</v>
       </c>
       <c r="Y2">
-        <v>-0.0006524572171025533</v>
+        <v>-0.0006064961757764886</v>
       </c>
       <c r="Z2">
         <v>1.51421588950228</v>
@@ -662,10 +662,10 @@
         <v>0.1420277872266736</v>
       </c>
       <c r="AB2">
-        <v>0.06857853912857281</v>
+        <v>0.06856824652413217</v>
       </c>
       <c r="AC2">
-        <v>0.07344924809810077</v>
+        <v>0.07345954070254142</v>
       </c>
       <c r="AD2">
         <v>5816.4</v>
@@ -787,10 +787,10 @@
         <v>0.1435631124884831</v>
       </c>
       <c r="X3">
-        <v>0.1442155697055857</v>
+        <v>0.1441696086642596</v>
       </c>
       <c r="Y3">
-        <v>-0.0006524572171025533</v>
+        <v>-0.0006064961757764886</v>
       </c>
       <c r="Z3">
         <v>1.51421588950228</v>
@@ -799,10 +799,10 @@
         <v>0.1420277872266736</v>
       </c>
       <c r="AB3">
-        <v>0.06857853912857281</v>
+        <v>0.06856824652413217</v>
       </c>
       <c r="AC3">
-        <v>0.07344924809810077</v>
+        <v>0.07345954070254142</v>
       </c>
       <c r="AD3">
         <v>5816.4</v>
@@ -1139,49 +1139,49 @@
         <v>2.03057065217391</v>
       </c>
       <c r="F2">
-        <v>4.64224396596572</v>
+        <v>4.53688645567289</v>
       </c>
       <c r="G2">
         <v>3.46503038246157</v>
       </c>
       <c r="H2">
-        <v>0.669736685333016</v>
+        <v>0.71438579768855</v>
       </c>
       <c r="I2">
         <v>0.776058066926402</v>
       </c>
       <c r="J2">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="K2">
         <v>1678.4</v>
       </c>
       <c r="L2">
-        <v>5329.49726762847</v>
+        <v>5338.90059096273</v>
       </c>
       <c r="M2">
         <v>7197</v>
       </c>
       <c r="N2">
-        <v>6155.91726762847</v>
+        <v>6240.26859096273</v>
       </c>
       <c r="O2">
         <v>5816.4</v>
       </c>
       <c r="P2">
-        <v>1124.22</v>
+        <v>1199.168</v>
       </c>
       <c r="Q2">
-        <v>0.0685785391285728</v>
+        <v>0.0685682465241322</v>
       </c>
       <c r="R2">
-        <v>0.0724308234794543</v>
+        <v>0.0720589771330498</v>
       </c>
       <c r="S2">
         <v>0.0467524624969006</v>
       </c>
       <c r="T2">
-        <v>0.0478774624969006</v>
+        <v>0.0459274624969006</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.144215569705586</v>
+        <v>0.14416960866426</v>
       </c>
       <c r="X2">
-        <v>0.0767637695351991</v>
+        <v>0.0770364084923163</v>
       </c>
       <c r="Y2">
         <v>1.91740676812274</v>
       </c>
       <c r="Z2">
-        <v>0.603259641243675</v>
+        <v>0.608855741811798</v>
       </c>
       <c r="AA2">
         <v>5816.4</v>
@@ -1236,7 +1236,7 @@
         <v>1678.4</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0731446276414745</v>
+        <v>0.0731318574307768</v>
       </c>
       <c r="C2">
-        <v>6293.023202808936</v>
+        <v>6293.114100009267</v>
       </c>
       <c r="D2">
-        <v>5995.223202808936</v>
+        <v>5995.314100009266</v>
       </c>
       <c r="E2">
         <v>-5816.4</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0731446276414745</v>
+        <v>0.0731318574307768</v>
       </c>
       <c r="T2">
         <v>0.5327487740853231</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07305054069733982</v>
+        <v>0.07302730241216886</v>
       </c>
       <c r="C3">
-        <v>6238.774690456631</v>
+        <v>6241.188585593691</v>
       </c>
       <c r="D3">
-        <v>6015.922690456631</v>
+        <v>6018.336585593691</v>
       </c>
       <c r="E3">
         <v>-5741.451999999999</v>
@@ -1539,37 +1539,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M3">
-        <v>4.319749145623605</v>
+        <v>4.214821945623606</v>
       </c>
       <c r="N3">
-        <v>328.8373937115192</v>
+        <v>328.9423209115192</v>
       </c>
       <c r="O3">
-        <v>82.2093484278798</v>
+        <v>82.23558022787981</v>
       </c>
       <c r="P3">
-        <v>246.6280452836394</v>
+        <v>246.7067406836394</v>
       </c>
       <c r="Q3">
-        <v>1626.32804528364</v>
+        <v>1626.40674068364</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07335178391148568</v>
+        <v>0.07333891695676753</v>
       </c>
       <c r="T3">
         <v>0.5367847496465755</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>77.12418745303039</v>
+        <v>79.04417960124539</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07295645375320514</v>
+        <v>0.07292274739356093</v>
       </c>
       <c r="C4">
-        <v>6184.669610052816</v>
+        <v>6189.44056915601</v>
       </c>
       <c r="D4">
-        <v>6036.765610052816</v>
+        <v>6041.536569156009</v>
       </c>
       <c r="E4">
         <v>-5666.504</v>
@@ -1621,37 +1621,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M4">
-        <v>8.639498291247211</v>
+        <v>8.429643891247212</v>
       </c>
       <c r="N4">
-        <v>324.5176445658956</v>
+        <v>324.7274989658956</v>
       </c>
       <c r="O4">
-        <v>81.12941114147391</v>
+        <v>81.18187474147391</v>
       </c>
       <c r="P4">
-        <v>243.3882334244217</v>
+        <v>243.5456242244217</v>
       </c>
       <c r="Q4">
-        <v>1623.088233424422</v>
+        <v>1623.245624224422</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07356316786047667</v>
+        <v>0.07355020218737032</v>
       </c>
       <c r="T4">
         <v>0.5409030920560168</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>38.5620937265152</v>
+        <v>39.52208980062269</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07286236680907046</v>
+        <v>0.07281819237495298</v>
       </c>
       <c r="C5">
-        <v>6130.709457594548</v>
+        <v>6137.872111341605</v>
       </c>
       <c r="D5">
-        <v>6057.753457594547</v>
+        <v>6064.916111341605</v>
       </c>
       <c r="E5">
         <v>-5591.556</v>
@@ -1703,37 +1703,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M5">
-        <v>12.95924743687081</v>
+        <v>12.64446583687081</v>
       </c>
       <c r="N5">
-        <v>320.197895420272</v>
+        <v>320.512677020272</v>
       </c>
       <c r="O5">
-        <v>80.049473855068</v>
+        <v>80.128169255068</v>
       </c>
       <c r="P5">
-        <v>240.148421565204</v>
+        <v>240.384507765204</v>
       </c>
       <c r="Q5">
-        <v>1619.848421565204</v>
+        <v>1620.084507765204</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07377891024140562</v>
+        <v>0.07376584381448037</v>
       </c>
       <c r="T5">
         <v>0.5451063487419413</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.70806248434347</v>
+        <v>26.3480598670818</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07276827986493578</v>
+        <v>0.07271363735634505</v>
       </c>
       <c r="C6">
-        <v>6076.895749955827</v>
+        <v>6086.485304816902</v>
       </c>
       <c r="D6">
-        <v>6078.887749955828</v>
+        <v>6088.477304816903</v>
       </c>
       <c r="E6">
         <v>-5516.607999999999</v>
@@ -1785,37 +1785,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M6">
-        <v>17.27899658249442</v>
+        <v>16.85928778249442</v>
       </c>
       <c r="N6">
-        <v>315.8781462746484</v>
+        <v>316.2978550746484</v>
       </c>
       <c r="O6">
-        <v>78.96953656866211</v>
+        <v>79.0744637686621</v>
       </c>
       <c r="P6">
-        <v>236.9086097059863</v>
+        <v>237.2233913059863</v>
       </c>
       <c r="Q6">
-        <v>1616.608609705986</v>
+        <v>1616.923391305986</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07399914725527058</v>
+        <v>0.07398597797548857</v>
       </c>
       <c r="T6">
         <v>0.5493971732754894</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.2810468632576</v>
+        <v>19.76104490031135</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.0726741929208011</v>
+        <v>0.07260908233773712</v>
       </c>
       <c r="C7">
-        <v>6023.230025253048</v>
+        <v>6035.282274893816</v>
       </c>
       <c r="D7">
-        <v>6100.170025253047</v>
+        <v>6112.222274893816</v>
       </c>
       <c r="E7">
         <v>-5441.66</v>
@@ -1867,37 +1867,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M7">
-        <v>21.59874572811803</v>
+        <v>21.07410972811803</v>
       </c>
       <c r="N7">
-        <v>311.5583971290248</v>
+        <v>312.0830331290248</v>
       </c>
       <c r="O7">
-        <v>77.8895992822562</v>
+        <v>78.02075828225621</v>
       </c>
       <c r="P7">
-        <v>233.6687978467686</v>
+        <v>234.0622748467686</v>
       </c>
       <c r="Q7">
-        <v>1613.368797846769</v>
+        <v>1613.762274846769</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.0742240208378485</v>
+        <v>0.07421074653988641</v>
       </c>
       <c r="T7">
         <v>0.5537783309571122</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.42483749060608</v>
+        <v>15.80883592024908</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07258010597666642</v>
+        <v>0.07250452731912915</v>
       </c>
       <c r="C8">
-        <v>5969.713843218149</v>
+        <v>5984.265180168809</v>
       </c>
       <c r="D8">
-        <v>6121.601843218149</v>
+        <v>6136.153180168809</v>
       </c>
       <c r="E8">
         <v>-5366.712</v>
@@ -1949,37 +1949,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M8">
-        <v>25.91849487374163</v>
+        <v>25.28893167374163</v>
       </c>
       <c r="N8">
-        <v>307.2386479834012</v>
+        <v>307.8682111834012</v>
       </c>
       <c r="O8">
-        <v>76.80966199585031</v>
+        <v>76.96705279585031</v>
       </c>
       <c r="P8">
-        <v>230.4289859875509</v>
+        <v>230.9011583875509</v>
       </c>
       <c r="Q8">
-        <v>1610.128985987551</v>
+        <v>1610.601158387551</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07445367896473659</v>
+        <v>0.07444029741416504</v>
       </c>
       <c r="T8">
         <v>0.5582527047596204</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>12.85403124217173</v>
+        <v>13.1740299335409</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07254376903253174</v>
+        <v>0.07247872230052123</v>
       </c>
       <c r="C9">
-        <v>5903.083306023082</v>
+        <v>5915.252379958802</v>
       </c>
       <c r="D9">
-        <v>6129.919306023082</v>
+        <v>6142.088379958802</v>
       </c>
       <c r="E9">
         <v>-5291.763999999999</v>
@@ -2031,37 +2031,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M9">
-        <v>30.81534361936524</v>
+        <v>30.29070761936524</v>
       </c>
       <c r="N9">
-        <v>302.3417992377776</v>
+        <v>302.8664352377776</v>
       </c>
       <c r="O9">
-        <v>75.5854498094444</v>
+        <v>75.71660880944441</v>
       </c>
       <c r="P9">
-        <v>226.7563494283332</v>
+        <v>227.1498264283332</v>
       </c>
       <c r="Q9">
-        <v>1606.456349428333</v>
+        <v>1606.849826428333</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07468827597607387</v>
+        <v>0.07467478486638515</v>
       </c>
       <c r="T9">
         <v>0.5628233016546558</v>
       </c>
       <c r="U9">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>10.8114044409934</v>
+        <v>10.99865830285692</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07258993208839708</v>
+        <v>0.07248741728191331</v>
       </c>
       <c r="C10">
-        <v>5817.572539143335</v>
+        <v>5838.30323673808</v>
       </c>
       <c r="D10">
-        <v>6119.356539143335</v>
+        <v>6140.08723673808</v>
       </c>
       <c r="E10">
         <v>-5216.816</v>
@@ -2113,37 +2113,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M10">
-        <v>36.53662036498884</v>
+        <v>35.63724436498884</v>
       </c>
       <c r="N10">
-        <v>296.620522492154</v>
+        <v>297.519898492154</v>
       </c>
       <c r="O10">
-        <v>74.1551306230385</v>
+        <v>74.37997462303851</v>
       </c>
       <c r="P10">
-        <v>222.4653918691155</v>
+        <v>223.1399238691155</v>
       </c>
       <c r="Q10">
-        <v>1602.165391869116</v>
+        <v>1602.839923869116</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07492797292244024</v>
+        <v>0.07491436987191441</v>
       </c>
       <c r="T10">
         <v>0.5674932593517572</v>
       </c>
       <c r="U10">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.118444440920161</v>
+        <v>9.348566332599134</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07252059514426239</v>
+        <v>0.07240686226330538</v>
       </c>
       <c r="C11">
-        <v>5758.503582263598</v>
+        <v>5781.944983876055</v>
       </c>
       <c r="D11">
-        <v>6135.235582263598</v>
+        <v>6158.676983876055</v>
       </c>
       <c r="E11">
         <v>-5141.867999999999</v>
@@ -2195,37 +2195,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M11">
-        <v>41.10369791061245</v>
+        <v>40.09189991061244</v>
       </c>
       <c r="N11">
-        <v>292.0534449465304</v>
+        <v>293.0652429465304</v>
       </c>
       <c r="O11">
-        <v>73.0133612366326</v>
+        <v>73.2663107366326</v>
       </c>
       <c r="P11">
-        <v>219.0400837098978</v>
+        <v>219.7989322098978</v>
       </c>
       <c r="Q11">
-        <v>1598.740083709898</v>
+        <v>1599.498932209898</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.0751729379335619</v>
+        <v>0.07515922048196079</v>
       </c>
       <c r="T11">
         <v>0.5722658534817618</v>
       </c>
       <c r="U11">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.105283947484587</v>
+        <v>8.309836740088119</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07256375820012771</v>
+        <v>0.07238630724469744</v>
       </c>
       <c r="C12">
-        <v>5673.661025818872</v>
+        <v>5711.758522168633</v>
       </c>
       <c r="D12">
-        <v>6125.341025818871</v>
+        <v>6163.438522168633</v>
       </c>
       <c r="E12">
         <v>-5066.92</v>
@@ -2277,37 +2277,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M12">
-        <v>46.79499545623606</v>
+        <v>45.14613945623606</v>
       </c>
       <c r="N12">
-        <v>286.3621474009068</v>
+        <v>288.0110034009068</v>
       </c>
       <c r="O12">
-        <v>71.5905368502267</v>
+        <v>72.0027508502267</v>
       </c>
       <c r="P12">
-        <v>214.7716105506801</v>
+        <v>216.0082525506801</v>
       </c>
       <c r="Q12">
-        <v>1594.47161055068</v>
+        <v>1595.70825255068</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07542334661159739</v>
+        <v>0.07540951221667486</v>
       </c>
       <c r="T12">
         <v>0.5771445052591</v>
       </c>
       <c r="U12">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.119503690703858</v>
+        <v>7.379526729635433</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07250567125599301</v>
+        <v>0.0723117522260895</v>
       </c>
       <c r="C13">
-        <v>5612.036126315471</v>
+        <v>5654.143034549951</v>
       </c>
       <c r="D13">
-        <v>6138.664126315471</v>
+        <v>6180.771034549951</v>
       </c>
       <c r="E13">
         <v>-4991.972</v>
@@ -2359,37 +2359,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M13">
-        <v>51.47449500185965</v>
+        <v>49.66075340185965</v>
       </c>
       <c r="N13">
-        <v>281.6826478552832</v>
+        <v>283.4963894552832</v>
       </c>
       <c r="O13">
-        <v>70.42066196382081</v>
+        <v>70.87409736382079</v>
       </c>
       <c r="P13">
-        <v>211.2619858914624</v>
+        <v>212.6222920914624</v>
       </c>
       <c r="Q13">
-        <v>1590.961985891463</v>
+        <v>1592.322292091462</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07567938245093703</v>
+        <v>0.0756654284847533</v>
       </c>
       <c r="T13">
         <v>0.582132789660648</v>
       </c>
       <c r="U13">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.472276082458055</v>
+        <v>6.70866066330494</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07257358431185836</v>
+        <v>0.07223719720748156</v>
       </c>
       <c r="C14">
-        <v>5521.516978467164</v>
+        <v>5596.625305084147</v>
       </c>
       <c r="D14">
-        <v>6123.092978467164</v>
+        <v>6198.201305084147</v>
       </c>
       <c r="E14">
         <v>-4917.023999999999</v>
@@ -2441,45 +2441,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M14">
-        <v>57.41312094748326</v>
+        <v>54.17536734748326</v>
       </c>
       <c r="N14">
-        <v>275.7440219096596</v>
+        <v>278.9817755096596</v>
       </c>
       <c r="O14">
-        <v>68.93600547741489</v>
+        <v>69.7454438774149</v>
       </c>
       <c r="P14">
-        <v>206.8080164322447</v>
+        <v>209.2363316322447</v>
       </c>
       <c r="Q14">
-        <v>1586.508016432245</v>
+        <v>1588.936331632245</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07594123728662532</v>
+        <v>0.0759271610316517</v>
       </c>
       <c r="T14">
         <v>0.5872344441622311</v>
       </c>
       <c r="U14">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>5.802804957457151</v>
+        <v>6.149605608029528</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07252599736772367</v>
+        <v>0.07226014218887362</v>
       </c>
       <c r="C15">
-        <v>5457.47144468718</v>
+        <v>5516.302518637641</v>
       </c>
       <c r="D15">
-        <v>6133.99544468718</v>
+        <v>6192.82651863764</v>
       </c>
       <c r="E15">
         <v>-4842.076</v>
@@ -2523,37 +2523,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M15">
-        <v>62.19754769310687</v>
+        <v>59.66430529310687</v>
       </c>
       <c r="N15">
-        <v>270.959595164036</v>
+        <v>273.492837564036</v>
       </c>
       <c r="O15">
-        <v>67.739898791009</v>
+        <v>68.373209391009</v>
       </c>
       <c r="P15">
-        <v>203.219696373027</v>
+        <v>205.119628173027</v>
       </c>
       <c r="Q15">
-        <v>1582.919696373027</v>
+        <v>1584.819628173027</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07620911177370872</v>
+        <v>0.07619491041870868</v>
       </c>
       <c r="T15">
         <v>0.5924533780776438</v>
       </c>
       <c r="U15">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.356435345345062</v>
+        <v>5.583860253135859</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07247841042358898</v>
+        <v>0.07219308717026569</v>
       </c>
       <c r="C16">
-        <v>5393.464804907452</v>
+        <v>5457.088187638316</v>
       </c>
       <c r="D16">
-        <v>6144.936804907452</v>
+        <v>6208.560187638315</v>
       </c>
       <c r="E16">
         <v>-4767.128</v>
@@ -2605,37 +2605,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M16">
-        <v>66.98197443873048</v>
+        <v>64.25386723873048</v>
       </c>
       <c r="N16">
-        <v>266.1751684184123</v>
+        <v>268.9032756184124</v>
       </c>
       <c r="O16">
-        <v>66.54379210460309</v>
+        <v>67.22581890460309</v>
       </c>
       <c r="P16">
-        <v>199.6313763138093</v>
+        <v>201.6774567138092</v>
       </c>
       <c r="Q16">
-        <v>1579.331376313809</v>
+        <v>1581.377456713809</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07648321590002663</v>
+        <v>0.07646888653569722</v>
       </c>
       <c r="T16">
         <v>0.5977936825492288</v>
       </c>
       <c r="U16">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.973832820677557</v>
+        <v>5.185013092197582</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.0724308234794543</v>
+        <v>0.07212603215165775</v>
       </c>
       <c r="C17">
-        <v>5329.497267628474</v>
+        <v>5397.954007074239</v>
       </c>
       <c r="D17">
-        <v>6155.917267628473</v>
+        <v>6224.374007074239</v>
       </c>
       <c r="E17">
         <v>-4692.18</v>
@@ -2687,37 +2687,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M17">
-        <v>71.76640118435407</v>
+        <v>68.84342918435406</v>
       </c>
       <c r="N17">
-        <v>261.3907416727887</v>
+        <v>264.3137136727888</v>
       </c>
       <c r="O17">
-        <v>65.34768541819719</v>
+        <v>66.07842841819719</v>
       </c>
       <c r="P17">
-        <v>196.0430562545916</v>
+        <v>198.2352852545916</v>
       </c>
       <c r="Q17">
-        <v>1575.743056254592</v>
+        <v>1577.935285254592</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07676376953519908</v>
+        <v>0.07674930914955608</v>
       </c>
       <c r="T17">
         <v>0.6032596412436746</v>
       </c>
       <c r="U17">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.64224396596572</v>
+        <v>4.839345552717745</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.0726952365353196</v>
+        <v>0.0720589771330498</v>
       </c>
       <c r="C18">
-        <v>5194.029074982089</v>
+        <v>5338.900590962729</v>
       </c>
       <c r="D18">
-        <v>6095.397074982088</v>
+        <v>6240.268590962728</v>
       </c>
       <c r="E18">
         <v>-4617.232</v>
@@ -2769,45 +2769,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M18">
-        <v>79.66866472997766</v>
+        <v>73.43299112997768</v>
       </c>
       <c r="N18">
-        <v>253.4884781271652</v>
+        <v>259.7241517271652</v>
       </c>
       <c r="O18">
-        <v>63.3721195317913</v>
+        <v>64.93103793179129</v>
       </c>
       <c r="P18">
-        <v>190.1163585953739</v>
+        <v>194.7931137953739</v>
       </c>
       <c r="Q18">
-        <v>1569.816358595374</v>
+        <v>1574.493113795374</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.077051003018828</v>
+        <v>0.07703640849231634</v>
       </c>
       <c r="T18">
         <v>0.6088557418117978</v>
       </c>
       <c r="U18">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.18178394210971</v>
+        <v>4.536886455672885</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07301139959118494</v>
+        <v>0.07231067211444187</v>
       </c>
       <c r="C19">
-        <v>5048.260044278351</v>
+        <v>5204.706854751152</v>
       </c>
       <c r="D19">
-        <v>6024.576044278351</v>
+        <v>6181.022854751151</v>
       </c>
       <c r="E19">
         <v>-4542.284</v>
@@ -2851,45 +2851,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M19">
-        <v>88.08806947560129</v>
+        <v>81.20784307560129</v>
       </c>
       <c r="N19">
-        <v>245.0690733815416</v>
+        <v>251.9492997815416</v>
       </c>
       <c r="O19">
-        <v>61.26726834538539</v>
+        <v>62.98732494538539</v>
       </c>
       <c r="P19">
-        <v>183.8018050361562</v>
+        <v>188.9619748361562</v>
       </c>
       <c r="Q19">
-        <v>1563.501805036156</v>
+        <v>1568.661974836156</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07734515779121909</v>
+        <v>0.07733042589152865</v>
       </c>
       <c r="T19">
         <v>0.6145866881767432</v>
       </c>
       <c r="U19">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.782091545886597</v>
+        <v>4.10252421735899</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07300356264705025</v>
+        <v>0.07273486709583395</v>
       </c>
       <c r="C20">
-        <v>4975.047635550229</v>
+        <v>5032.414439962458</v>
       </c>
       <c r="D20">
-        <v>6026.311635550229</v>
+        <v>6083.678439962458</v>
       </c>
       <c r="E20">
         <v>-4467.335999999999</v>
@@ -2933,37 +2933,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M20">
-        <v>93.26972062122489</v>
+        <v>90.70649902122489</v>
       </c>
       <c r="N20">
-        <v>239.8874222359179</v>
+        <v>242.450643835918</v>
       </c>
       <c r="O20">
-        <v>59.97185555897948</v>
+        <v>60.61266095897949</v>
       </c>
       <c r="P20">
-        <v>179.9155666769385</v>
+        <v>181.8379828769385</v>
       </c>
       <c r="Q20">
-        <v>1559.615566676938</v>
+        <v>1561.537982876938</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07764648707025384</v>
+        <v>0.07763161444681932</v>
       </c>
       <c r="T20">
         <v>0.6204574137213213</v>
       </c>
       <c r="U20">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.571975348892897</v>
+        <v>3.672913699151652</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07366547570291558</v>
+        <v>0.07311181207722603</v>
       </c>
       <c r="C21">
-        <v>4756.95137593281</v>
+        <v>4873.50232766325</v>
       </c>
       <c r="D21">
-        <v>5883.16337593281</v>
+        <v>5999.71432766325</v>
       </c>
       <c r="E21">
         <v>-4392.388</v>
@@ -3015,37 +3015,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M21">
-        <v>105.1442281668485</v>
+        <v>99.73298256684849</v>
       </c>
       <c r="N21">
-        <v>228.0129146902943</v>
+        <v>233.4241602902944</v>
       </c>
       <c r="O21">
-        <v>57.00322867257358</v>
+        <v>58.35604007257359</v>
       </c>
       <c r="P21">
-        <v>171.0096860177208</v>
+        <v>175.0681202177208</v>
       </c>
       <c r="Q21">
-        <v>1550.709686017721</v>
+        <v>1554.768120217721</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07795525657840058</v>
+        <v>0.07794023975656161</v>
       </c>
       <c r="T21">
         <v>0.6264730954521855</v>
       </c>
       <c r="U21">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.16857281341655</v>
+        <v>3.340491122220636</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.0736928887587809</v>
+        <v>0.07311075705861808</v>
       </c>
       <c r="C22">
-        <v>4676.221418829551</v>
+        <v>4798.78609752025</v>
       </c>
       <c r="D22">
-        <v>5877.381418829551</v>
+        <v>5999.94609752025</v>
       </c>
       <c r="E22">
         <v>-4317.44</v>
@@ -3097,37 +3097,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M22">
-        <v>110.6781349124721</v>
+        <v>104.9820869124721</v>
       </c>
       <c r="N22">
-        <v>222.4790079446707</v>
+        <v>228.1750559446707</v>
       </c>
       <c r="O22">
-        <v>55.61975198616769</v>
+        <v>57.04376398616768</v>
       </c>
       <c r="P22">
-        <v>166.8592559585031</v>
+        <v>171.1312919585031</v>
       </c>
       <c r="Q22">
-        <v>1546.559255958503</v>
+        <v>1550.831291958503</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07827174532425098</v>
+        <v>0.07825658069904745</v>
       </c>
       <c r="T22">
         <v>0.6326391692263211</v>
       </c>
       <c r="U22">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.010144172745723</v>
+        <v>3.173466566109604</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07518505181464621</v>
+        <v>0.07310970204001013</v>
       </c>
       <c r="C23">
-        <v>4302.821965562569</v>
+        <v>4724.069885284551</v>
       </c>
       <c r="D23">
-        <v>5578.929965562569</v>
+        <v>6000.177885284551</v>
       </c>
       <c r="E23">
         <v>-4242.492</v>
@@ -3179,45 +3179,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M23">
-        <v>130.8493860580957</v>
+        <v>110.2311912580957</v>
       </c>
       <c r="N23">
-        <v>202.3077567990472</v>
+        <v>222.9259515990472</v>
       </c>
       <c r="O23">
-        <v>50.57693919976179</v>
+        <v>55.73148789976179</v>
       </c>
       <c r="P23">
-        <v>151.7308175992854</v>
+        <v>167.1944636992854</v>
       </c>
       <c r="Q23">
-        <v>1531.430817599285</v>
+        <v>1546.894463699285</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07859624644341405</v>
+        <v>0.07858093027298862</v>
       </c>
       <c r="T23">
         <v>0.6389613461339793</v>
       </c>
       <c r="U23">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.546111624163255</v>
+        <v>3.022349110580576</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07605771487051154</v>
+        <v>0.07439564702140219</v>
       </c>
       <c r="C24">
-        <v>4066.971990874746</v>
+        <v>4379.294151249844</v>
       </c>
       <c r="D24">
-        <v>5418.027990874745</v>
+        <v>5730.350151249843</v>
       </c>
       <c r="E24">
         <v>-4167.544</v>
@@ -3261,45 +3261,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M24">
-        <v>144.8299324037193</v>
+        <v>128.3413724037193</v>
       </c>
       <c r="N24">
-        <v>188.3272104534236</v>
+        <v>204.8157704534235</v>
       </c>
       <c r="O24">
-        <v>47.08180261335589</v>
+        <v>51.20394261335588</v>
       </c>
       <c r="P24">
-        <v>141.2454078400677</v>
+        <v>153.6118278400676</v>
       </c>
       <c r="Q24">
-        <v>1520.945407840068</v>
+        <v>1533.311827840068</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07892906810409411</v>
+        <v>0.07891359650267188</v>
       </c>
       <c r="T24">
         <v>0.6454456301418336</v>
       </c>
       <c r="U24">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.300333483056899</v>
+        <v>2.595867074018354</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07619012792637685</v>
+        <v>0.07512584200279426</v>
       </c>
       <c r="C25">
-        <v>3968.417060203919</v>
+        <v>4161.664044401446</v>
       </c>
       <c r="D25">
-        <v>5394.421060203919</v>
+        <v>5587.668044401446</v>
       </c>
       <c r="E25">
         <v>-4092.596</v>
@@ -3343,37 +3343,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M25">
-        <v>151.4131111493429</v>
+        <v>140.8979067493429</v>
       </c>
       <c r="N25">
-        <v>181.7440317077999</v>
+        <v>192.2592361077999</v>
       </c>
       <c r="O25">
-        <v>45.43600792694998</v>
+        <v>48.06480902694998</v>
       </c>
       <c r="P25">
-        <v>136.30802378085</v>
+        <v>144.1944270808499</v>
       </c>
       <c r="Q25">
-        <v>1516.00802378085</v>
+        <v>1523.89442708085</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.0792705344832334</v>
+        <v>0.07925490341364562</v>
       </c>
       <c r="T25">
         <v>0.6520983371109311</v>
       </c>
       <c r="U25">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.200318983793555</v>
+        <v>2.36452868991041</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07632254098224217</v>
+        <v>0.07521253698418633</v>
       </c>
       <c r="C26">
-        <v>3870.066952967126</v>
+        <v>4070.246102437756</v>
       </c>
       <c r="D26">
-        <v>5371.018952967125</v>
+        <v>5571.198102437756</v>
       </c>
       <c r="E26">
         <v>-4017.648</v>
@@ -3425,37 +3425,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M26">
-        <v>157.9962898949665</v>
+        <v>147.0239026949665</v>
       </c>
       <c r="N26">
-        <v>175.1608529621764</v>
+        <v>186.1332401621763</v>
       </c>
       <c r="O26">
-        <v>43.79021324054409</v>
+        <v>46.53331004054409</v>
       </c>
       <c r="P26">
-        <v>131.3706397216323</v>
+        <v>139.5999301216323</v>
       </c>
       <c r="Q26">
-        <v>1511.070639721632</v>
+        <v>1519.299930121632</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07962098681971846</v>
+        <v>0.07960519208543446</v>
       </c>
       <c r="T26">
         <v>0.6589261153160575</v>
       </c>
       <c r="U26">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.108639026135491</v>
+        <v>2.266006661164143</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07645495403810749</v>
+        <v>0.07529923196557839</v>
       </c>
       <c r="C27">
-        <v>3771.919014980304</v>
+        <v>3978.924967151186</v>
       </c>
       <c r="D27">
-        <v>5347.819014980304</v>
+        <v>5554.824967151186</v>
       </c>
       <c r="E27">
         <v>-3942.7</v>
@@ -3507,37 +3507,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M27">
-        <v>164.5794686405901</v>
+        <v>153.1498986405901</v>
       </c>
       <c r="N27">
-        <v>168.5776742165527</v>
+        <v>180.0072442165527</v>
       </c>
       <c r="O27">
-        <v>42.14441855413818</v>
+        <v>45.00181105413818</v>
       </c>
       <c r="P27">
-        <v>126.4332556624146</v>
+        <v>135.0054331624145</v>
       </c>
       <c r="Q27">
-        <v>1506.133255662415</v>
+        <v>1514.705433162414</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07998078455184314</v>
+        <v>0.079964821788471</v>
       </c>
       <c r="T27">
         <v>0.6659359676066539</v>
       </c>
       <c r="U27">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.024293465090071</v>
+        <v>2.175366394717577</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07976586709397282</v>
+        <v>0.07538592694697045</v>
       </c>
       <c r="C28">
-        <v>3175.678160947878</v>
+        <v>3887.699787530399</v>
       </c>
       <c r="D28">
-        <v>4826.526160947878</v>
+        <v>5538.547787530399</v>
       </c>
       <c r="E28">
         <v>-3867.751999999999</v>
@@ -3589,45 +3589,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M28">
-        <v>202.9256097862137</v>
+        <v>159.2758945862137</v>
       </c>
       <c r="N28">
-        <v>130.2315330709291</v>
+        <v>173.8812482709291</v>
       </c>
       <c r="O28">
-        <v>32.55788326773228</v>
+        <v>43.47031206773228</v>
       </c>
       <c r="P28">
-        <v>97.67364980319684</v>
+        <v>130.4109362031969</v>
       </c>
       <c r="Q28">
-        <v>1477.373649803197</v>
+        <v>1510.110936203197</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08035030654699821</v>
+        <v>0.08033417121321122</v>
       </c>
       <c r="T28">
         <v>0.6731352753645636</v>
       </c>
       <c r="U28">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.641769824952753</v>
+        <v>2.091698456459208</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08002053014983813</v>
+        <v>0.07547262192836252</v>
       </c>
       <c r="C29">
-        <v>3064.812017775375</v>
+        <v>3796.569722509711</v>
       </c>
       <c r="D29">
-        <v>4790.608017775375</v>
+        <v>5522.365722509711</v>
       </c>
       <c r="E29">
         <v>-3792.804</v>
@@ -3671,45 +3671,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M29">
-        <v>210.7304409318374</v>
+        <v>165.4018905318374</v>
       </c>
       <c r="N29">
-        <v>122.4267019253055</v>
+        <v>167.7552523253055</v>
       </c>
       <c r="O29">
-        <v>30.60667548132637</v>
+        <v>41.93881308132637</v>
       </c>
       <c r="P29">
-        <v>91.82002644397912</v>
+        <v>125.8164392439791</v>
       </c>
       <c r="Q29">
-        <v>1471.520026443979</v>
+        <v>1505.516439243979</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08072995243243147</v>
+        <v>0.0807136398002731</v>
       </c>
       <c r="T29">
         <v>0.6805318244309093</v>
       </c>
       <c r="U29">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.580963535139688</v>
+        <v>2.014228143257015</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08027519320570345</v>
+        <v>0.07854131690975458</v>
       </c>
       <c r="C30">
-        <v>2954.476518422428</v>
+        <v>3204.035456056627</v>
       </c>
       <c r="D30">
-        <v>4755.220518422428</v>
+        <v>5004.779456056627</v>
       </c>
       <c r="E30">
         <v>-3717.856</v>
@@ -3753,37 +3753,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M30">
-        <v>218.5352720774609</v>
+        <v>201.3272112774609</v>
       </c>
       <c r="N30">
-        <v>114.6218707796819</v>
+        <v>131.8299315796819</v>
       </c>
       <c r="O30">
-        <v>28.65546769492047</v>
+        <v>32.95748289492047</v>
       </c>
       <c r="P30">
-        <v>85.96640308476142</v>
+        <v>98.87244868476142</v>
       </c>
       <c r="Q30">
-        <v>1465.666403084761</v>
+        <v>1478.572448684761</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08112014403690457</v>
+        <v>0.08110364918142003</v>
       </c>
       <c r="T30">
         <v>0.6881338331935424</v>
       </c>
       <c r="U30">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.07810246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.524500551741842</v>
+        <v>1.654804339379635</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09612289244216141</v>
+        <v>0.07873451189114664</v>
       </c>
       <c r="C31">
-        <v>1382.0131547019</v>
+        <v>3099.729247345962</v>
       </c>
       <c r="D31">
-        <v>3257.7051547019</v>
+        <v>4975.421247345961</v>
       </c>
       <c r="E31">
         <v>-3642.908</v>
@@ -3835,45 +3835,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M31">
-        <v>368.4864800230845</v>
+        <v>208.5174688230845</v>
       </c>
       <c r="N31">
-        <v>-35.32933716594169</v>
+        <v>124.6396740340583</v>
       </c>
       <c r="O31">
-        <v>-8.832334291485424</v>
+        <v>31.15991850851458</v>
       </c>
       <c r="P31">
-        <v>-26.49700287445627</v>
+        <v>93.47975552554374</v>
       </c>
       <c r="Q31">
-        <v>1353.202997125544</v>
+        <v>1473.179755525544</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08178903757623361</v>
+        <v>0.08150464474231757</v>
       </c>
       <c r="T31">
-        <v>0.7011657244207115</v>
+        <v>0.6959499830480804</v>
       </c>
       <c r="U31">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V31">
-        <v>0.2260307778702434</v>
+        <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.1312161233208123</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>0.9041231114809737</v>
+        <v>1.597742120780337</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09736025860878675</v>
+        <v>0.07892770687253871</v>
       </c>
       <c r="C32">
-        <v>1228.885288114068</v>
+        <v>2995.765462492603</v>
       </c>
       <c r="D32">
-        <v>3179.525288114068</v>
+        <v>4946.405462492602</v>
       </c>
       <c r="E32">
         <v>-3567.96</v>
@@ -3917,45 +3917,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M32">
-        <v>381.1929103687081</v>
+        <v>215.7077263687081</v>
       </c>
       <c r="N32">
-        <v>-48.03576751156527</v>
+        <v>117.4494164884347</v>
       </c>
       <c r="O32">
-        <v>-12.00894187789132</v>
+        <v>29.36235412210868</v>
       </c>
       <c r="P32">
-        <v>-36.02682563367395</v>
+        <v>88.08706236632602</v>
       </c>
       <c r="Q32">
-        <v>1343.673174366326</v>
+        <v>1467.787062366326</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08230316668446552</v>
+        <v>0.08191709731924077</v>
       </c>
       <c r="T32">
-        <v>0.7111823776267215</v>
+        <v>0.7039894514698912</v>
       </c>
       <c r="U32">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V32">
-        <v>0.218496418607902</v>
+        <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.1324934730988696</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.8739856744316079</v>
+        <v>1.544484050087659</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09859762477541209</v>
+        <v>0.0931806305668422</v>
       </c>
       <c r="C33">
-        <v>1079.421871290351</v>
+        <v>1432.852047626835</v>
       </c>
       <c r="D33">
-        <v>3105.00987129035</v>
+        <v>3458.440047626834</v>
       </c>
       <c r="E33">
         <v>-3493.012</v>
@@ -3999,37 +3999,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M33">
-        <v>393.8993407143318</v>
+        <v>354.8664223143318</v>
       </c>
       <c r="N33">
-        <v>-60.74219785718896</v>
+        <v>-21.70927945718893</v>
       </c>
       <c r="O33">
-        <v>-15.18554946429724</v>
+        <v>-5.427319864297232</v>
       </c>
       <c r="P33">
-        <v>-45.55664839289172</v>
+        <v>-16.2819595928917</v>
       </c>
       <c r="Q33">
-        <v>1334.143351607108</v>
+        <v>1363.418040407108</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08283219808568965</v>
+        <v>0.08252930792834198</v>
       </c>
       <c r="T33">
-        <v>0.7214893686068189</v>
+        <v>0.7159225757482814</v>
       </c>
       <c r="U33">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V33">
-        <v>0.2114481470399051</v>
+        <v>0.2347060202853178</v>
       </c>
       <c r="W33">
-        <v>0.1336884132138266</v>
+        <v>0.1168884132138266</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8457925881596204</v>
+        <v>0.9388240811412712</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09983499094203743</v>
+        <v>0.09424999673346754</v>
       </c>
       <c r="C34">
-        <v>933.3711636782832</v>
+        <v>1281.570940803742</v>
       </c>
       <c r="D34">
-        <v>3033.907163678283</v>
+        <v>3382.106940803742</v>
       </c>
       <c r="E34">
         <v>-3418.064</v>
@@ -4081,37 +4081,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M34">
-        <v>406.6057710599554</v>
+        <v>366.3137262599553</v>
       </c>
       <c r="N34">
-        <v>-73.44862820281253</v>
+        <v>-33.15658340281249</v>
       </c>
       <c r="O34">
-        <v>-18.36215705070313</v>
+        <v>-8.289145850703122</v>
       </c>
       <c r="P34">
-        <v>-55.0864711521094</v>
+        <v>-24.86743755210937</v>
       </c>
       <c r="Q34">
-        <v>1324.613528847891</v>
+        <v>1354.832562447891</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08337678923400862</v>
+        <v>0.08306944480964112</v>
       </c>
       <c r="T34">
-        <v>0.7320995063804486</v>
+        <v>0.7264508489210503</v>
       </c>
       <c r="U34">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V34">
-        <v>0.2048403924449081</v>
+        <v>0.2273714571514017</v>
       </c>
       <c r="W34">
-        <v>0.1348086695715987</v>
+        <v>0.1180086695715987</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8193615697796324</v>
+        <v>0.9094858286056067</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1187203165199809</v>
+        <v>0.09531936290009288</v>
       </c>
       <c r="C35">
-        <v>72.68432855378569</v>
+        <v>1133.58664706747</v>
       </c>
       <c r="D35">
-        <v>2248.168328553785</v>
+        <v>3309.070647067469</v>
       </c>
       <c r="E35">
         <v>-3343.116</v>
@@ -4163,45 +4163,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M35">
-        <v>548.4176262055789</v>
+        <v>377.7610302055789</v>
       </c>
       <c r="N35">
-        <v>-215.2604833484361</v>
+        <v>-44.6038873484361</v>
       </c>
       <c r="O35">
-        <v>-53.81512083710902</v>
+        <v>-11.15097183710903</v>
       </c>
       <c r="P35">
-        <v>-161.4453625113271</v>
+        <v>-33.45291551132708</v>
       </c>
       <c r="Q35">
-        <v>1218.254637488673</v>
+        <v>1346.247084488673</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08456742700066269</v>
+        <v>0.08362570517993428</v>
       </c>
       <c r="T35">
-        <v>0.7552964143391646</v>
+        <v>0.7372933989049466</v>
       </c>
       <c r="U35">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V35">
-        <v>0.1518720072703572</v>
+        <v>0.2204814129952986</v>
       </c>
       <c r="W35">
-        <v>0.1880610316046573</v>
+        <v>0.1190610316046573</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.6074880290814287</v>
+        <v>0.8819256519811943</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1204796826866063</v>
+        <v>0.09638872906671822</v>
       </c>
       <c r="C36">
-        <v>-55.22789346540458</v>
+        <v>988.6900980877131</v>
       </c>
       <c r="D36">
-        <v>2195.204106534595</v>
+        <v>3239.122098087713</v>
       </c>
       <c r="E36">
         <v>-3268.168</v>
@@ -4245,45 +4245,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M36">
-        <v>565.0363421512026</v>
+        <v>389.2083341512026</v>
       </c>
       <c r="N36">
-        <v>-231.8791992940597</v>
+        <v>-56.05119129405978</v>
       </c>
       <c r="O36">
-        <v>-57.96979982351493</v>
+        <v>-14.01279782351494</v>
       </c>
       <c r="P36">
-        <v>-173.9093994705448</v>
+        <v>-42.03839347054483</v>
       </c>
       <c r="Q36">
-        <v>1205.790600529455</v>
+        <v>1337.661606529455</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.0851548122582485</v>
+        <v>0.08419882192508479</v>
       </c>
       <c r="T36">
-        <v>0.7667402994049095</v>
+        <v>0.748464511009567</v>
       </c>
       <c r="U36">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V36">
-        <v>0.1474051835271114</v>
+        <v>0.2139966655542603</v>
       </c>
       <c r="W36">
-        <v>0.1890514899887125</v>
+        <v>0.1200514899887125</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.5896207341084455</v>
+        <v>0.8559866622170413</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1222390488532316</v>
+        <v>0.09745809523334356</v>
       </c>
       <c r="C37">
-        <v>-180.7020040308271</v>
+        <v>846.6895370976649</v>
       </c>
       <c r="D37">
-        <v>2144.677995969173</v>
+        <v>3172.069537097665</v>
       </c>
       <c r="E37">
         <v>-3193.22</v>
@@ -4327,45 +4327,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M37">
-        <v>581.6550580968262</v>
+        <v>400.6556380968262</v>
       </c>
       <c r="N37">
-        <v>-248.4979152396834</v>
+        <v>-67.49849523968334</v>
       </c>
       <c r="O37">
-        <v>-62.12447880992084</v>
+        <v>-16.87462380992083</v>
       </c>
       <c r="P37">
-        <v>-186.3734364297625</v>
+        <v>-50.6238714297625</v>
       </c>
       <c r="Q37">
-        <v>1193.326563570238</v>
+        <v>1329.076128570238</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.0857602709083754</v>
+        <v>0.08478957303162457</v>
       </c>
       <c r="T37">
-        <v>0.7785363040111389</v>
+        <v>0.7599793496404833</v>
       </c>
       <c r="U37">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V37">
-        <v>0.1431936068549082</v>
+        <v>0.2078824751098529</v>
       </c>
       <c r="W37">
-        <v>0.1899853507508217</v>
+        <v>0.1209853507508217</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.5727744274196327</v>
+        <v>0.8315299004394117</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.123998415019857</v>
+        <v>0.0985274613999689</v>
       </c>
       <c r="C38">
-        <v>-303.9025664830942</v>
+        <v>707.4087634140619</v>
       </c>
       <c r="D38">
-        <v>2096.425433516905</v>
+        <v>3107.736763414061</v>
       </c>
       <c r="E38">
         <v>-3118.272</v>
@@ -4409,45 +4409,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M38">
-        <v>598.2737740424498</v>
+        <v>412.1029420424497</v>
       </c>
       <c r="N38">
-        <v>-265.1166311853069</v>
+        <v>-78.9457991853069</v>
       </c>
       <c r="O38">
-        <v>-66.27915779632673</v>
+        <v>-19.73644979632672</v>
       </c>
       <c r="P38">
-        <v>-198.8374733889802</v>
+        <v>-59.20934938898017</v>
       </c>
       <c r="Q38">
-        <v>1180.86252661102</v>
+        <v>1320.49065061102</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08638465014131876</v>
+        <v>0.08539878511024369</v>
       </c>
       <c r="T38">
-        <v>0.7907009337613129</v>
+        <v>0.7718540269786158</v>
       </c>
       <c r="U38">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V38">
-        <v>0.1392160066644941</v>
+        <v>0.202107961912357</v>
       </c>
       <c r="W38">
-        <v>0.1908673303594804</v>
+        <v>0.1218673303594804</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.5568640266579763</v>
+        <v>0.8084318476494281</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1257577811864823</v>
+        <v>0.120096262824777</v>
       </c>
       <c r="C39">
-        <v>-424.9796601604207</v>
+        <v>-269.740162744768</v>
       </c>
       <c r="D39">
-        <v>2050.296339839579</v>
+        <v>2205.535837255231</v>
       </c>
       <c r="E39">
         <v>-3043.324</v>
@@ -4491,37 +4491,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M39">
-        <v>614.8924899880733</v>
+        <v>573.2963499880733</v>
       </c>
       <c r="N39">
-        <v>-281.7353471309304</v>
+        <v>-240.1392071309305</v>
       </c>
       <c r="O39">
-        <v>-70.43383678273261</v>
+        <v>-60.03480178273261</v>
       </c>
       <c r="P39">
-        <v>-211.3015103481978</v>
+        <v>-180.1044053481978</v>
       </c>
       <c r="Q39">
-        <v>1168.398489651802</v>
+        <v>1199.595594651802</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08702885093721269</v>
+        <v>0.08685183766466456</v>
       </c>
       <c r="T39">
-        <v>0.8032517422337145</v>
+        <v>0.800176725829576</v>
       </c>
       <c r="U39">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V39">
-        <v>0.1354534118897781</v>
+        <v>0.1452813814635632</v>
       </c>
       <c r="W39">
-        <v>0.191701635394698</v>
+        <v>0.176701635394698</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5418136475591122</v>
+        <v>0.5811255258542527</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1275171473531076</v>
+        <v>0.1217056289914023</v>
       </c>
       <c r="C40">
-        <v>-544.0704395979174</v>
+        <v>-391.4503700134851</v>
       </c>
       <c r="D40">
-        <v>2006.153560402082</v>
+        <v>2158.773629986515</v>
       </c>
       <c r="E40">
         <v>-2968.376</v>
@@ -4573,37 +4573,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M40">
-        <v>631.5112059336971</v>
+        <v>588.790845933697</v>
       </c>
       <c r="N40">
-        <v>-298.3540630765542</v>
+        <v>-255.6337030765542</v>
       </c>
       <c r="O40">
-        <v>-74.58851576913855</v>
+        <v>-63.90842576913855</v>
       </c>
       <c r="P40">
-        <v>-223.7655473074157</v>
+        <v>-191.7252773074156</v>
       </c>
       <c r="Q40">
-        <v>1155.934452692584</v>
+        <v>1187.974722692584</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08769383240394193</v>
+        <v>0.08751396407861078</v>
       </c>
       <c r="T40">
-        <v>0.8162074154955488</v>
+        <v>0.8130828020526338</v>
       </c>
       <c r="U40">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V40">
-        <v>0.1318888484189944</v>
+        <v>0.141458187214522</v>
       </c>
       <c r="W40">
-        <v>0.1924920296385885</v>
+        <v>0.1774920296385885</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5275553936759775</v>
+        <v>0.5658327488580881</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.129276513519733</v>
+        <v>0.1233149951580276</v>
       </c>
       <c r="C41">
-        <v>-661.3004965550763</v>
+        <v>-511.2188235840531</v>
       </c>
       <c r="D41">
-        <v>1963.871503444924</v>
+        <v>2113.953176415946</v>
       </c>
       <c r="E41">
         <v>-2893.428</v>
@@ -4655,37 +4655,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M41">
-        <v>648.1299218793206</v>
+        <v>604.2853418793205</v>
       </c>
       <c r="N41">
-        <v>-314.9727790221777</v>
+        <v>-271.1281990221777</v>
       </c>
       <c r="O41">
-        <v>-78.74319475554444</v>
+        <v>-67.78204975554442</v>
       </c>
       <c r="P41">
-        <v>-236.2295842666333</v>
+        <v>-203.3461492666333</v>
       </c>
       <c r="Q41">
-        <v>1143.470415733367</v>
+        <v>1176.353850733367</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08838061654171148</v>
+        <v>0.08819779955530932</v>
       </c>
       <c r="T41">
-        <v>0.829587864929902</v>
+        <v>0.8264120283157916</v>
       </c>
       <c r="U41">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V41">
-        <v>0.1285070830749176</v>
+        <v>0.1378310542090215</v>
       </c>
       <c r="W41">
-        <v>0.1932418908443307</v>
+        <v>0.1782418908443306</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5140283322996704</v>
+        <v>0.5513242168360859</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1310358796863583</v>
+        <v>0.124924361324653</v>
       </c>
       <c r="C42">
-        <v>-776.7850533604337</v>
+        <v>-629.1640075486089</v>
       </c>
       <c r="D42">
-        <v>1923.334946639566</v>
+        <v>2070.955992451391</v>
       </c>
       <c r="E42">
         <v>-2818.48</v>
@@ -4737,37 +4737,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M42">
-        <v>664.7486378249442</v>
+        <v>619.7798378249443</v>
       </c>
       <c r="N42">
-        <v>-331.5914949678014</v>
+        <v>-286.6226949678014</v>
       </c>
       <c r="O42">
-        <v>-82.89787374195035</v>
+        <v>-71.65567374195035</v>
       </c>
       <c r="P42">
-        <v>-248.693621225851</v>
+        <v>-214.9670212258511</v>
       </c>
       <c r="Q42">
-        <v>1131.006378774149</v>
+        <v>1164.732978774149</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08909029348407334</v>
+        <v>0.0889044295478978</v>
       </c>
       <c r="T42">
-        <v>0.8434143293454004</v>
+        <v>0.8401855621210549</v>
       </c>
       <c r="U42">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V42">
-        <v>0.1252944059980447</v>
+        <v>0.1343852778537959</v>
       </c>
       <c r="W42">
-        <v>0.1939542589897858</v>
+        <v>0.1789542589897858</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5011776239921786</v>
+        <v>0.5375411114151837</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1452585655443182</v>
+        <v>0.1265337274912783</v>
       </c>
       <c r="C43">
-        <v>-1126.772096965997</v>
+        <v>-745.394958434053</v>
       </c>
       <c r="D43">
-        <v>1648.295903034003</v>
+        <v>2029.673041565947</v>
       </c>
       <c r="E43">
         <v>-2743.532</v>
@@ -4819,45 +4819,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M43">
-        <v>773.5533937705678</v>
+        <v>635.2743337705678</v>
       </c>
       <c r="N43">
-        <v>-440.396250913425</v>
+        <v>-302.1171909134249</v>
       </c>
       <c r="O43">
-        <v>-110.0990627283562</v>
+        <v>-75.52929772835623</v>
       </c>
       <c r="P43">
-        <v>-330.2971881850688</v>
+        <v>-226.5878931850687</v>
       </c>
       <c r="Q43">
-        <v>1049.402811814931</v>
+        <v>1153.112106814931</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09010084030809914</v>
+        <v>0.08963501309955708</v>
       </c>
       <c r="T43">
-        <v>0.8631025689774884</v>
+        <v>0.8544259953773439</v>
       </c>
       <c r="U43">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V43">
-        <v>0.1076710235970976</v>
+        <v>0.1311075881500448</v>
       </c>
       <c r="W43">
-        <v>0.2246318774696089</v>
+        <v>0.1796318774696089</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.4306840943883903</v>
+        <v>0.5244303526001792</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1473179317109435</v>
+        <v>0.1281430936579037</v>
       </c>
       <c r="C44">
-        <v>-1235.156995827969</v>
+        <v>-860.0121884483942</v>
       </c>
       <c r="D44">
-        <v>1614.859004172031</v>
+        <v>1990.003811551606</v>
       </c>
       <c r="E44">
         <v>-2668.584</v>
@@ -4901,45 +4901,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M44">
-        <v>792.4205497161914</v>
+        <v>650.7688297161914</v>
       </c>
       <c r="N44">
-        <v>-459.2634068590486</v>
+        <v>-317.6116868590485</v>
       </c>
       <c r="O44">
-        <v>-114.8158517147621</v>
+        <v>-79.40292171476213</v>
       </c>
       <c r="P44">
-        <v>-344.4475551442864</v>
+        <v>-238.2087651442864</v>
       </c>
       <c r="Q44">
-        <v>1035.252444855714</v>
+        <v>1141.491234855714</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.0908646478996181</v>
+        <v>0.09039078918748049</v>
       </c>
       <c r="T44">
-        <v>0.8779836477529623</v>
+        <v>0.8691574780562636</v>
       </c>
       <c r="U44">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V44">
-        <v>0.1051074277971667</v>
+        <v>0.1279859789083771</v>
       </c>
       <c r="W44">
-        <v>0.2252772284027738</v>
+        <v>0.1802772284027738</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.4204297111886667</v>
+        <v>0.5119439156335084</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1493772978775688</v>
+        <v>0.129752459824529</v>
       </c>
       <c r="C45">
-        <v>-1342.212282513446</v>
+        <v>-973.1085025354441</v>
       </c>
       <c r="D45">
-        <v>1582.751717486554</v>
+        <v>1951.855497464556</v>
       </c>
       <c r="E45">
         <v>-2593.636</v>
@@ -4983,45 +4983,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M45">
-        <v>811.287705661815</v>
+        <v>666.263325661815</v>
       </c>
       <c r="N45">
-        <v>-478.1305628046722</v>
+        <v>-333.1061828046721</v>
       </c>
       <c r="O45">
-        <v>-119.532640701168</v>
+        <v>-83.27654570116803</v>
       </c>
       <c r="P45">
-        <v>-358.5979221035042</v>
+        <v>-249.8296371035041</v>
       </c>
       <c r="Q45">
-        <v>1021.102077896496</v>
+        <v>1129.870362896496</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09165525575750613</v>
+        <v>0.09117308373462926</v>
       </c>
       <c r="T45">
-        <v>0.8933868696433651</v>
+        <v>0.8844058548642683</v>
       </c>
       <c r="U45">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V45">
-        <v>0.102663069011186</v>
+        <v>0.1250095607942288</v>
       </c>
       <c r="W45">
-        <v>0.2258925630134659</v>
+        <v>0.1808925630134659</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.4106522760447442</v>
+        <v>0.5000382431769151</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1514366640441942</v>
+        <v>0.1469745450664905</v>
       </c>
       <c r="C46">
-        <v>-1448.015718612756</v>
+        <v>-1380.304319762934</v>
       </c>
       <c r="D46">
-        <v>1551.896281387243</v>
+        <v>1619.607680237066</v>
       </c>
       <c r="E46">
         <v>-2518.688</v>
@@ -5065,37 +5065,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M46">
-        <v>830.1548616074385</v>
+        <v>797.1777416074385</v>
       </c>
       <c r="N46">
-        <v>-496.9977187502957</v>
+        <v>-464.0205987502957</v>
       </c>
       <c r="O46">
-        <v>-124.2494296875739</v>
+        <v>-116.0051496875739</v>
       </c>
       <c r="P46">
-        <v>-372.7482890627218</v>
+        <v>-348.0154490627218</v>
       </c>
       <c r="Q46">
-        <v>1006.951710937278</v>
+        <v>1031.684550937278</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09247409961031874</v>
+        <v>0.09236317286441928</v>
       </c>
       <c r="T46">
-        <v>0.9093402066012825</v>
+        <v>0.9076029071156079</v>
       </c>
       <c r="U46">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V46">
-        <v>0.10032981744275</v>
+        <v>0.1044801947760611</v>
       </c>
       <c r="W46">
-        <v>0.2264799278691265</v>
+        <v>0.2164799278691265</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4013192697710001</v>
+        <v>0.4179207791042445</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1534960302108195</v>
+        <v>0.1489339112331158</v>
       </c>
       <c r="C47">
-        <v>-1552.639117879976</v>
+        <v>-1486.022068082574</v>
       </c>
       <c r="D47">
-        <v>1522.220882120024</v>
+        <v>1588.837931917426</v>
       </c>
       <c r="E47">
         <v>-2443.74</v>
@@ -5147,37 +5147,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M47">
-        <v>849.0220175530623</v>
+        <v>815.2954175530622</v>
       </c>
       <c r="N47">
-        <v>-515.8648746959194</v>
+        <v>-482.1382746959193</v>
       </c>
       <c r="O47">
-        <v>-128.9662186739799</v>
+        <v>-120.5345686739798</v>
       </c>
       <c r="P47">
-        <v>-386.8986560219396</v>
+        <v>-361.6037060219395</v>
       </c>
       <c r="Q47">
-        <v>992.8013439780605</v>
+        <v>1018.096293978061</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09332271960323363</v>
+        <v>0.09320977600740871</v>
       </c>
       <c r="T47">
-        <v>0.9258736649031239</v>
+        <v>0.9241047781540734</v>
       </c>
       <c r="U47">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V47">
-        <v>0.09810026594402223</v>
+        <v>0.1021584126699264</v>
       </c>
       <c r="W47">
-        <v>0.2270411876200912</v>
+        <v>0.2170411876200911</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3924010637760889</v>
+        <v>0.4086336506797057</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1555553963774449</v>
+        <v>0.1508932773997411</v>
       </c>
       <c r="C48">
-        <v>-1656.148904236139</v>
+        <v>-1590.592469867691</v>
       </c>
       <c r="D48">
-        <v>1493.659095763861</v>
+        <v>1559.215530132309</v>
       </c>
       <c r="E48">
         <v>-2368.792</v>
@@ -5229,37 +5229,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M48">
-        <v>867.8891734986859</v>
+        <v>833.4130934986858</v>
       </c>
       <c r="N48">
-        <v>-534.732030641543</v>
+        <v>-500.255950641543</v>
       </c>
       <c r="O48">
-        <v>-133.6830076603858</v>
+        <v>-125.0639876603857</v>
       </c>
       <c r="P48">
-        <v>-401.0490229811572</v>
+        <v>-375.1919629811572</v>
       </c>
       <c r="Q48">
-        <v>978.6509770188428</v>
+        <v>1004.508037018843</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09420276996625648</v>
+        <v>0.09408773482236073</v>
       </c>
       <c r="T48">
-        <v>0.943019473512441</v>
+        <v>0.9412178296013712</v>
       </c>
       <c r="U48">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V48">
-        <v>0.09596765146697826</v>
+        <v>0.09993757761188456</v>
       </c>
       <c r="W48">
-        <v>0.2275780447731877</v>
+        <v>0.2175780447731877</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.383870605867913</v>
+        <v>0.3997503104475382</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1576147625440702</v>
+        <v>0.1528526435663665</v>
       </c>
       <c r="C49">
-        <v>-1758.606608109775</v>
+        <v>-1694.078524178551</v>
       </c>
       <c r="D49">
-        <v>1466.149391890225</v>
+        <v>1530.677475821449</v>
       </c>
       <c r="E49">
         <v>-2293.844</v>
@@ -5311,37 +5311,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M49">
-        <v>886.7563294443095</v>
+        <v>851.5307694443095</v>
       </c>
       <c r="N49">
-        <v>-553.5991865871666</v>
+        <v>-518.3736265871667</v>
       </c>
       <c r="O49">
-        <v>-138.3997966467917</v>
+        <v>-129.5934066467917</v>
       </c>
       <c r="P49">
-        <v>-415.199389940375</v>
+        <v>-388.780219940375</v>
       </c>
       <c r="Q49">
-        <v>964.500610059625</v>
+        <v>990.9197800596251</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09511602977694056</v>
+        <v>0.09499882415863169</v>
       </c>
       <c r="T49">
-        <v>0.9608122937673927</v>
+        <v>0.958976656574982</v>
       </c>
       <c r="U49">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V49">
-        <v>0.09392578654214893</v>
+        <v>0.09781124617333381</v>
       </c>
       <c r="W49">
-        <v>0.2280920569410462</v>
+        <v>0.2180920569410461</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3757031461685958</v>
+        <v>0.3912449846933352</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1596741287106955</v>
+        <v>0.1548120097329918</v>
       </c>
       <c r="C50">
-        <v>-1860.069308920771</v>
+        <v>-1796.538700731262</v>
       </c>
       <c r="D50">
-        <v>1439.634691079228</v>
+        <v>1503.165299268737</v>
       </c>
       <c r="E50">
         <v>-2218.896</v>
@@ -5393,37 +5393,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M50">
-        <v>905.623485389933</v>
+        <v>869.6484453899329</v>
       </c>
       <c r="N50">
-        <v>-572.4663425327901</v>
+        <v>-536.4913025327901</v>
       </c>
       <c r="O50">
-        <v>-143.1165856331975</v>
+        <v>-134.1228256331975</v>
       </c>
       <c r="P50">
-        <v>-429.3497568995926</v>
+        <v>-402.3684768995926</v>
       </c>
       <c r="Q50">
-        <v>950.3502431004074</v>
+        <v>977.3315231004075</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09606441496495866</v>
+        <v>0.09594495539245151</v>
       </c>
       <c r="T50">
-        <v>0.9792894532629196</v>
+        <v>0.97741851535527</v>
       </c>
       <c r="U50">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V50">
-        <v>0.09196899932252084</v>
+        <v>0.09577351187805604</v>
       </c>
       <c r="W50">
-        <v>0.2285846519352438</v>
+        <v>0.2185846519352438</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3678759972900834</v>
+        <v>0.3830940475122242</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1617334948773209</v>
+        <v>0.1567713758996171</v>
       </c>
       <c r="C51">
-        <v>-1960.59003040429</v>
+        <v>-1898.027339759624</v>
       </c>
       <c r="D51">
-        <v>1414.06196959571</v>
+        <v>1476.624660240376</v>
       </c>
       <c r="E51">
         <v>-2143.948</v>
@@ -5475,37 +5475,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M51">
-        <v>924.4906413355567</v>
+        <v>887.7661213355566</v>
       </c>
       <c r="N51">
-        <v>-591.3334984784138</v>
+        <v>-554.6089784784137</v>
       </c>
       <c r="O51">
-        <v>-147.8333746196035</v>
+        <v>-138.6522446196034</v>
       </c>
       <c r="P51">
-        <v>-443.5001238588104</v>
+        <v>-415.9567338588103</v>
       </c>
       <c r="Q51">
-        <v>936.1998761411896</v>
+        <v>963.7432661411897</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09704999172897745</v>
+        <v>0.09692818981191136</v>
       </c>
       <c r="T51">
-        <v>0.998491207248467</v>
+        <v>0.9965835842838047</v>
       </c>
       <c r="U51">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V51">
-        <v>0.090092080969</v>
+        <v>0.09381895041115693</v>
       </c>
       <c r="W51">
-        <v>0.229057141011311</v>
+        <v>0.219057141011311</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.360368323876</v>
+        <v>0.3752758016446277</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1637928610439462</v>
+        <v>0.1587307420662425</v>
       </c>
       <c r="C52">
-        <v>-2060.218094536411</v>
+        <v>-1998.595010250964</v>
       </c>
       <c r="D52">
-        <v>1389.381905463589</v>
+        <v>1451.004989749036</v>
       </c>
       <c r="E52">
         <v>-2069</v>
@@ -5557,37 +5557,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M52">
-        <v>943.3577972811802</v>
+        <v>905.8837972811801</v>
       </c>
       <c r="N52">
-        <v>-610.2006544240373</v>
+        <v>-572.7266544240373</v>
       </c>
       <c r="O52">
-        <v>-152.5501636060093</v>
+        <v>-143.1816636060093</v>
       </c>
       <c r="P52">
-        <v>-457.650490818028</v>
+        <v>-429.5449908180279</v>
       </c>
       <c r="Q52">
-        <v>922.0495091819721</v>
+        <v>950.1550091819721</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09807499156355701</v>
+        <v>0.09795075360814959</v>
       </c>
       <c r="T52">
-        <v>1.018461031393436</v>
+        <v>1.016515255969481</v>
       </c>
       <c r="U52">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V52">
-        <v>0.08829023934962001</v>
+        <v>0.0919425714029338</v>
       </c>
       <c r="W52">
-        <v>0.2295107305243354</v>
+        <v>0.2195107305243354</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3531609573984801</v>
+        <v>0.3677702856117352</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1658522272105716</v>
+        <v>0.1606901082328678</v>
       </c>
       <c r="C53">
-        <v>-2158.999439032507</v>
+        <v>-2098.288831525293</v>
       </c>
       <c r="D53">
-        <v>1365.548560967492</v>
+        <v>1426.259168474707</v>
       </c>
       <c r="E53">
         <v>-1994.052</v>
@@ -5639,37 +5639,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M53">
-        <v>962.2249532268038</v>
+        <v>924.0014732268038</v>
       </c>
       <c r="N53">
-        <v>-629.0678103696609</v>
+        <v>-590.844330369661</v>
       </c>
       <c r="O53">
-        <v>-157.2669525924152</v>
+        <v>-147.7110825924152</v>
       </c>
       <c r="P53">
-        <v>-471.8008577772457</v>
+        <v>-443.1332477772457</v>
       </c>
       <c r="Q53">
-        <v>907.8991422227543</v>
+        <v>936.5667522227543</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09914182812607858</v>
+        <v>0.09901505470219345</v>
       </c>
       <c r="T53">
-        <v>1.039245950401466</v>
+        <v>1.03726046527498</v>
       </c>
       <c r="U53">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V53">
-        <v>0.08655905818590197</v>
+        <v>0.09013977588522921</v>
       </c>
       <c r="W53">
-        <v>0.2299465322133197</v>
+        <v>0.2199465322133197</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3462362327436079</v>
+        <v>0.3605591035409168</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1679115933771969</v>
+        <v>0.1626494743994932</v>
       </c>
       <c r="C54">
-        <v>-2256.976902718676</v>
+        <v>-2197.152762460457</v>
       </c>
       <c r="D54">
-        <v>1342.519097281324</v>
+        <v>1402.343237539543</v>
       </c>
       <c r="E54">
         <v>-1919.104</v>
@@ -5721,37 +5721,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M54">
-        <v>981.0921091724275</v>
+        <v>942.1191491724275</v>
       </c>
       <c r="N54">
-        <v>-647.9349663152847</v>
+        <v>-608.9620063152846</v>
       </c>
       <c r="O54">
-        <v>-161.9837415788212</v>
+        <v>-152.2405015788212</v>
       </c>
       <c r="P54">
-        <v>-485.9512247364635</v>
+        <v>-456.7215047364634</v>
       </c>
       <c r="Q54">
-        <v>893.7487752635366</v>
+        <v>922.9784952635366</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1002531162120385</v>
+        <v>0.1001237016751558</v>
       </c>
       <c r="T54">
-        <v>1.060896907701496</v>
+        <v>1.058870058301543</v>
       </c>
       <c r="U54">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V54">
-        <v>0.08489446091309616</v>
+        <v>0.08840631865666711</v>
       </c>
       <c r="W54">
-        <v>0.2303655722988815</v>
+        <v>0.2203655722988815</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3395778436523846</v>
+        <v>0.3536252746266684</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1699709595438222</v>
+        <v>0.1646088405661185</v>
       </c>
       <c r="C55">
-        <v>-2354.190482505984</v>
+        <v>-2295.227862098313</v>
       </c>
       <c r="D55">
-        <v>1320.253517494016</v>
+        <v>1379.216137901686</v>
       </c>
       <c r="E55">
         <v>-1844.156</v>
@@ -5803,37 +5803,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M55">
-        <v>999.959265118051</v>
+        <v>960.236825118051</v>
       </c>
       <c r="N55">
-        <v>-666.8021222609082</v>
+        <v>-627.0796822609082</v>
       </c>
       <c r="O55">
-        <v>-166.700530565227</v>
+        <v>-156.769920565227</v>
       </c>
       <c r="P55">
-        <v>-500.1015916956811</v>
+        <v>-470.3097616956811</v>
       </c>
       <c r="Q55">
-        <v>879.5984083043189</v>
+        <v>909.3902383043189</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1014116931527202</v>
+        <v>0.1012795251150528</v>
       </c>
       <c r="T55">
-        <v>1.083469182333443</v>
+        <v>1.081399208478171</v>
       </c>
       <c r="U55">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V55">
-        <v>0.08329267863171699</v>
+        <v>0.0867382749084281</v>
       </c>
       <c r="W55">
-        <v>0.2307687995510259</v>
+        <v>0.2207687995510259</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.333170714526868</v>
+        <v>0.3469530996337125</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1720303257104476</v>
+        <v>0.1665682067327439</v>
       </c>
       <c r="C56">
-        <v>-2450.6775652105</v>
+        <v>-2392.552524882159</v>
       </c>
       <c r="D56">
-        <v>1298.714434789501</v>
+        <v>1356.839475117841</v>
       </c>
       <c r="E56">
         <v>-1769.208</v>
@@ -5885,37 +5885,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M56">
-        <v>1018.826421063675</v>
+        <v>978.3545010636747</v>
       </c>
       <c r="N56">
-        <v>-685.6692782065319</v>
+        <v>-645.1973582065318</v>
       </c>
       <c r="O56">
-        <v>-171.417319551633</v>
+        <v>-161.299339551633</v>
       </c>
       <c r="P56">
-        <v>-514.2519586548989</v>
+        <v>-483.8980186548989</v>
       </c>
       <c r="Q56">
-        <v>865.4480413451012</v>
+        <v>895.8019813451012</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1026206430038663</v>
+        <v>0.1024856017479887</v>
       </c>
       <c r="T56">
-        <v>1.107022860210257</v>
+        <v>1.104907886923349</v>
       </c>
       <c r="U56">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V56">
-        <v>0.08175022162001852</v>
+        <v>0.08513201055827202</v>
       </c>
       <c r="W56">
-        <v>0.2311570924604983</v>
+        <v>0.2211570924604983</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3270008864800741</v>
+        <v>0.3405280422330881</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1740896918770729</v>
+        <v>0.1685275728993692</v>
       </c>
       <c r="C57">
-        <v>-2546.473137045626</v>
+        <v>-2489.162693360529</v>
       </c>
       <c r="D57">
-        <v>1277.866862954374</v>
+        <v>1335.177306639471</v>
       </c>
       <c r="E57">
         <v>-1694.259999999999</v>
@@ -5967,37 +5967,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M57">
-        <v>1037.693577009298</v>
+        <v>996.4721770092984</v>
       </c>
       <c r="N57">
-        <v>-704.5364341521556</v>
+        <v>-663.3150341521556</v>
       </c>
       <c r="O57">
-        <v>-176.1341085380389</v>
+        <v>-165.8287585380389</v>
       </c>
       <c r="P57">
-        <v>-528.4023256141168</v>
+        <v>-497.4862756141167</v>
       </c>
       <c r="Q57">
-        <v>851.2976743858833</v>
+        <v>882.2137243858833</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1038833239595078</v>
+        <v>0.1037452817868329</v>
       </c>
       <c r="T57">
-        <v>1.131623368214929</v>
+        <v>1.129461395521646</v>
       </c>
       <c r="U57">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V57">
-        <v>0.08026385395419999</v>
+        <v>0.08358415582084888</v>
       </c>
       <c r="W57">
-        <v>0.231531265627808</v>
+        <v>0.221531265627808</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3210554158168</v>
+        <v>0.3343366232833955</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1761490580436983</v>
+        <v>0.1704869390659945</v>
       </c>
       <c r="C58">
-        <v>-2641.609973255993</v>
+        <v>-2585.092050836075</v>
       </c>
       <c r="D58">
-        <v>1257.678026744007</v>
+        <v>1314.195949163925</v>
       </c>
       <c r="E58">
         <v>-1619.312</v>
@@ -6049,37 +6049,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M58">
-        <v>1056.560732954922</v>
+        <v>1014.589852954922</v>
       </c>
       <c r="N58">
-        <v>-723.403590097779</v>
+        <v>-681.432710097779</v>
       </c>
       <c r="O58">
-        <v>-180.8508975244447</v>
+        <v>-170.3581775244448</v>
       </c>
       <c r="P58">
-        <v>-542.5526925733343</v>
+        <v>-511.0745325733343</v>
       </c>
       <c r="Q58">
-        <v>837.1473074266657</v>
+        <v>868.6254674266658</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.105203399504042</v>
+        <v>0.1050622200092609</v>
       </c>
       <c r="T58">
-        <v>1.157342081128905</v>
+        <v>1.155130972692592</v>
       </c>
       <c r="U58">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V58">
-        <v>0.07883057084787501</v>
+        <v>0.08209158160976231</v>
       </c>
       <c r="W58">
-        <v>0.2318920754677138</v>
+        <v>0.2218920754677139</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3153222833915</v>
+        <v>0.3283663264390493</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1782084242103236</v>
+        <v>0.1724463052326199</v>
       </c>
       <c r="C59">
-        <v>-2736.118810054947</v>
+        <v>-2680.372196131418</v>
       </c>
       <c r="D59">
-        <v>1238.117189945053</v>
+        <v>1293.863803868583</v>
       </c>
       <c r="E59">
         <v>-1544.364</v>
@@ -6131,37 +6131,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M59">
-        <v>1075.427888900546</v>
+        <v>1032.707528900546</v>
       </c>
       <c r="N59">
-        <v>-742.2707460434028</v>
+        <v>-699.5503860434028</v>
       </c>
       <c r="O59">
-        <v>-185.5676865108507</v>
+        <v>-174.8875965108507</v>
       </c>
       <c r="P59">
-        <v>-556.7030595325521</v>
+        <v>-524.6627895325521</v>
       </c>
       <c r="Q59">
-        <v>822.996940467448</v>
+        <v>855.0372104674479</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1065848739111128</v>
+        <v>0.106440411172267</v>
       </c>
       <c r="T59">
-        <v>1.184257013248182</v>
+        <v>1.181994483685443</v>
       </c>
       <c r="U59">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V59">
-        <v>0.07744757837685964</v>
+        <v>0.08065137842362612</v>
       </c>
       <c r="W59">
-        <v>0.232240225313237</v>
+        <v>0.222240225313237</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3097903135074386</v>
+        <v>0.3226055136945045</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1802677903769489</v>
+        <v>0.1744056713992452</v>
       </c>
       <c r="C60">
-        <v>-2830.028500762754</v>
+        <v>-2775.032802379171</v>
       </c>
       <c r="D60">
-        <v>1219.155499237246</v>
+        <v>1274.151197620829</v>
       </c>
       <c r="E60">
         <v>-1469.416</v>
@@ -6213,37 +6213,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M60">
-        <v>1094.295044846169</v>
+        <v>1050.825204846169</v>
       </c>
       <c r="N60">
-        <v>-761.1379019890262</v>
+        <v>-717.6680619890262</v>
       </c>
       <c r="O60">
-        <v>-190.2844754972566</v>
+        <v>-179.4170154972566</v>
       </c>
       <c r="P60">
-        <v>-570.8534264917696</v>
+        <v>-538.2510464917697</v>
       </c>
       <c r="Q60">
-        <v>808.8465735082304</v>
+        <v>841.4489535082304</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1080321328137583</v>
+        <v>0.1078842304858924</v>
       </c>
       <c r="T60">
-        <v>1.21245360880171</v>
+        <v>1.210137209487477</v>
       </c>
       <c r="U60">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V60">
-        <v>0.07611227530139655</v>
+        <v>0.07926083741632223</v>
       </c>
       <c r="W60">
-        <v>0.2325763699916732</v>
+        <v>0.2225763699916732</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3044491012055862</v>
+        <v>0.3170433496652889</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1823271565435743</v>
+        <v>0.1763650375658706</v>
       </c>
       <c r="C61">
-        <v>-2923.366157813753</v>
+        <v>-2869.101761514375</v>
       </c>
       <c r="D61">
-        <v>1200.765842186246</v>
+        <v>1255.030238485625</v>
       </c>
       <c r="E61">
         <v>-1394.468</v>
@@ -6295,37 +6295,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M61">
-        <v>1113.162200791793</v>
+        <v>1068.942880791793</v>
       </c>
       <c r="N61">
-        <v>-780.0050579346498</v>
+        <v>-735.7857379346499</v>
       </c>
       <c r="O61">
-        <v>-195.0012644836625</v>
+        <v>-183.9464344836625</v>
       </c>
       <c r="P61">
-        <v>-585.0037934509874</v>
+        <v>-551.8393034509875</v>
       </c>
       <c r="Q61">
-        <v>794.6962065490127</v>
+        <v>827.8606965490126</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1095499897116549</v>
+        <v>0.1093984800099385</v>
       </c>
       <c r="T61">
-        <v>1.242025648040776</v>
+        <v>1.239652751182294</v>
       </c>
       <c r="U61">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V61">
-        <v>0.07482223673696611</v>
+        <v>0.07791743339231677</v>
       </c>
       <c r="W61">
-        <v>0.2329011199352471</v>
+        <v>0.2229011199352471</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2992889469478645</v>
+        <v>0.3116697335692671</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1843865227101996</v>
+        <v>0.1783244037324959</v>
       </c>
       <c r="C62">
-        <v>-3016.157282102315</v>
+        <v>-2962.605315949044</v>
       </c>
       <c r="D62">
-        <v>1182.922717897684</v>
+        <v>1236.474684050956</v>
       </c>
       <c r="E62">
         <v>-1319.52</v>
@@ -6377,37 +6377,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M62">
-        <v>1132.029356737416</v>
+        <v>1087.060556737416</v>
       </c>
       <c r="N62">
-        <v>-798.8722138802734</v>
+        <v>-753.9034138802733</v>
       </c>
       <c r="O62">
-        <v>-199.7180534700684</v>
+        <v>-188.4758534700683</v>
       </c>
       <c r="P62">
-        <v>-599.1541604102051</v>
+        <v>-565.4275604102049</v>
       </c>
       <c r="Q62">
-        <v>780.5458395897949</v>
+        <v>814.2724395897951</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1111437394544462</v>
+        <v>0.110988442010187</v>
       </c>
       <c r="T62">
-        <v>1.273076289241795</v>
+        <v>1.270644069961851</v>
       </c>
       <c r="U62">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V62">
-        <v>0.07357519945801667</v>
+        <v>0.07661880950244483</v>
       </c>
       <c r="W62">
-        <v>0.2332150448807019</v>
+        <v>0.2232150448807019</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2943007978320666</v>
+        <v>0.3064752380097794</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.186445888876825</v>
+        <v>0.1802837698991213</v>
       </c>
       <c r="C63">
-        <v>-3108.425880965354</v>
+        <v>-3055.568178736096</v>
       </c>
       <c r="D63">
-        <v>1165.602119034646</v>
+        <v>1218.459821263903</v>
       </c>
       <c r="E63">
         <v>-1244.572</v>
@@ -6459,37 +6459,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M63">
-        <v>1150.89651268304</v>
+        <v>1105.17823268304</v>
       </c>
       <c r="N63">
-        <v>-817.739369825897</v>
+        <v>-772.021089825897</v>
       </c>
       <c r="O63">
-        <v>-204.4348424564743</v>
+        <v>-193.0052724564742</v>
       </c>
       <c r="P63">
-        <v>-613.3045273694228</v>
+        <v>-579.0158173694227</v>
       </c>
       <c r="Q63">
-        <v>766.3954726305773</v>
+        <v>800.6841826305773</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1128192199532782</v>
+        <v>0.1126599405232687</v>
       </c>
       <c r="T63">
-        <v>1.305719271017226</v>
+        <v>1.30322468714036</v>
       </c>
       <c r="U63">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V63">
-        <v>0.07236904864722951</v>
+        <v>0.07536276344502769</v>
       </c>
       <c r="W63">
-        <v>0.2335186772049942</v>
+        <v>0.2235186772049942</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.289476194588918</v>
+        <v>0.3014510537801108</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1885052550434503</v>
+        <v>0.1822431360657466</v>
       </c>
       <c r="C64">
-        <v>-3200.194575949263</v>
+        <v>-3148.013643379731</v>
       </c>
       <c r="D64">
-        <v>1148.781424050737</v>
+        <v>1200.962356620269</v>
       </c>
       <c r="E64">
         <v>-1169.624</v>
@@ -6541,37 +6541,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M64">
-        <v>1169.763668628663</v>
+        <v>1123.295908628663</v>
       </c>
       <c r="N64">
-        <v>-836.6065257715206</v>
+        <v>-790.1387657715206</v>
       </c>
       <c r="O64">
-        <v>-209.1516314428802</v>
+        <v>-197.5346914428802</v>
       </c>
       <c r="P64">
-        <v>-627.4548943286404</v>
+        <v>-592.6040743286405</v>
       </c>
       <c r="Q64">
-        <v>752.2451056713596</v>
+        <v>787.0959256713595</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1145828836362592</v>
+        <v>0.1144194126423021</v>
       </c>
       <c r="T64">
-        <v>1.340080304465048</v>
+        <v>1.337520073644054</v>
       </c>
       <c r="U64">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V64">
-        <v>0.07120180592711291</v>
+        <v>0.07414723500236596</v>
       </c>
       <c r="W64">
-        <v>0.2338125149381803</v>
+        <v>0.2238125149381803</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2848072237084517</v>
+        <v>0.2965889400094638</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1905646212100756</v>
+        <v>0.1842025022323719</v>
       </c>
       <c r="C65">
-        <v>-3291.484701378546</v>
+        <v>-3239.963684318279</v>
       </c>
       <c r="D65">
-        <v>1132.439298621454</v>
+        <v>1183.96031568172</v>
       </c>
       <c r="E65">
         <v>-1094.676</v>
@@ -6623,37 +6623,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M65">
-        <v>1188.630824574287</v>
+        <v>1141.413584574287</v>
       </c>
       <c r="N65">
-        <v>-855.4736817171442</v>
+        <v>-808.2564417171441</v>
       </c>
       <c r="O65">
-        <v>-213.8684204292861</v>
+        <v>-202.064110429286</v>
       </c>
       <c r="P65">
-        <v>-641.6052612878582</v>
+        <v>-606.192331287858</v>
       </c>
       <c r="Q65">
-        <v>738.0947387121419</v>
+        <v>773.507668712142</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1164418804912932</v>
+        <v>0.1162739913623643</v>
       </c>
       <c r="T65">
-        <v>1.376298691072211</v>
+        <v>1.373669264823623</v>
       </c>
       <c r="U65">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V65">
-        <v>0.07007161853144445</v>
+        <v>0.07297029476423318</v>
       </c>
       <c r="W65">
-        <v>0.2340970244893605</v>
+        <v>0.2240970244893605</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2802864741257778</v>
+        <v>0.2918811790569327</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.192623987376701</v>
+        <v>0.1861618683989973</v>
       </c>
       <c r="C66">
-        <v>-3382.316394629258</v>
+        <v>-3331.439048990994</v>
       </c>
       <c r="D66">
-        <v>1116.555605370741</v>
+        <v>1167.432951009006</v>
       </c>
       <c r="E66">
         <v>-1019.728</v>
@@ -6705,37 +6705,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M66">
-        <v>1207.497980519911</v>
+        <v>1159.531260519911</v>
       </c>
       <c r="N66">
-        <v>-874.3408376627679</v>
+        <v>-826.3741176627677</v>
       </c>
       <c r="O66">
-        <v>-218.585209415692</v>
+        <v>-206.5935294156919</v>
       </c>
       <c r="P66">
-        <v>-655.7556282470759</v>
+        <v>-619.7805882470758</v>
       </c>
       <c r="Q66">
-        <v>723.9443717529241</v>
+        <v>759.9194117529242</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1184041549493847</v>
+        <v>0.1182316022335411</v>
       </c>
       <c r="T66">
-        <v>1.414529210268662</v>
+        <v>1.411826744402057</v>
       </c>
       <c r="U66">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V66">
-        <v>0.06897674949189063</v>
+        <v>0.07183013390854202</v>
       </c>
       <c r="W66">
-        <v>0.2343726431170664</v>
+        <v>0.2243726431170664</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2759069979675625</v>
+        <v>0.2873205356341682</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1946833535433263</v>
+        <v>0.1881212345656226</v>
       </c>
       <c r="C67">
-        <v>-3472.708678910424</v>
+        <v>-3422.459342299804</v>
       </c>
       <c r="D67">
-        <v>1101.111321089576</v>
+        <v>1151.360657700196</v>
       </c>
       <c r="E67">
         <v>-944.7799999999997</v>
@@ -6787,37 +6787,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M67">
-        <v>1226.365136465534</v>
+        <v>1177.648936465534</v>
       </c>
       <c r="N67">
-        <v>-893.2079936083915</v>
+        <v>-844.4917936083914</v>
       </c>
       <c r="O67">
-        <v>-223.3019984020979</v>
+        <v>-211.1229484020978</v>
       </c>
       <c r="P67">
-        <v>-669.9059952062936</v>
+        <v>-633.3688452062936</v>
       </c>
       <c r="Q67">
-        <v>709.7940047937064</v>
+        <v>746.3311547937064</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.12047855937651</v>
+        <v>0.1203010765830708</v>
       </c>
       <c r="T67">
-        <v>1.454944330562052</v>
+        <v>1.452164651384973</v>
       </c>
       <c r="U67">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V67">
-        <v>0.06791556873047692</v>
+        <v>0.07072505492533369</v>
       </c>
       <c r="W67">
-        <v>0.234639781171612</v>
+        <v>0.224639781171612</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2716622749219078</v>
+        <v>0.2829002197013347</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1967427197099517</v>
+        <v>0.190080600732248</v>
       </c>
       <c r="C68">
-        <v>-3562.679539268957</v>
+        <v>-3513.043104189011</v>
       </c>
       <c r="D68">
-        <v>1086.088460731042</v>
+        <v>1135.724895810989</v>
       </c>
       <c r="E68">
         <v>-869.8320000000003</v>
@@ -6869,37 +6869,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M68">
-        <v>1245.232292411158</v>
+        <v>1195.766612411158</v>
       </c>
       <c r="N68">
-        <v>-912.0751495540151</v>
+        <v>-862.609469554015</v>
       </c>
       <c r="O68">
-        <v>-228.0187873885038</v>
+        <v>-215.6523673885038</v>
       </c>
       <c r="P68">
-        <v>-684.0563621655112</v>
+        <v>-646.9571021655113</v>
       </c>
       <c r="Q68">
-        <v>695.6436378344888</v>
+        <v>732.7428978344888</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1226749875934662</v>
+        <v>0.1224922847178671</v>
       </c>
       <c r="T68">
-        <v>1.4977368108727</v>
+        <v>1.494875376425707</v>
       </c>
       <c r="U68">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V68">
-        <v>0.06688654496183334</v>
+        <v>0.06965346318404075</v>
       </c>
       <c r="W68">
-        <v>0.2348988241335957</v>
+        <v>0.2248988241335957</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2675461798473333</v>
+        <v>0.278613852736163</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.198802085876577</v>
+        <v>0.1920399668988733</v>
       </c>
       <c r="C69">
-        <v>-3652.245992456557</v>
+        <v>-3603.207880988372</v>
       </c>
       <c r="D69">
-        <v>1071.470007543443</v>
+        <v>1120.508119011628</v>
       </c>
       <c r="E69">
         <v>-794.884</v>
@@ -6951,37 +6951,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M69">
-        <v>1264.099448356782</v>
+        <v>1213.884288356782</v>
       </c>
       <c r="N69">
-        <v>-930.9423054996387</v>
+        <v>-880.7271454996387</v>
       </c>
       <c r="O69">
-        <v>-232.7355763749097</v>
+        <v>-220.1817863749097</v>
       </c>
       <c r="P69">
-        <v>-698.206729124729</v>
+        <v>-660.545359124729</v>
       </c>
       <c r="Q69">
-        <v>681.493270875271</v>
+        <v>719.1546408752711</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1250045326720561</v>
+        <v>0.1248162933456812</v>
       </c>
       <c r="T69">
-        <v>1.54312277483854</v>
+        <v>1.540174630256789</v>
       </c>
       <c r="U69">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V69">
-        <v>0.06588823832061194</v>
+        <v>0.06861385925592074</v>
       </c>
       <c r="W69">
-        <v>0.2351501344698485</v>
+        <v>0.2251501344698485</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2635529532824478</v>
+        <v>0.2744554370236829</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2008614520432024</v>
+        <v>0.1939993330654987</v>
       </c>
       <c r="C70">
-        <v>-3741.424151229183</v>
+        <v>-3692.97029109675</v>
       </c>
       <c r="D70">
-        <v>1057.239848770817</v>
+        <v>1105.69370890325</v>
       </c>
       <c r="E70">
         <v>-719.9359999999997</v>
@@ -7033,37 +7033,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M70">
-        <v>1282.966604302405</v>
+        <v>1232.001964302405</v>
       </c>
       <c r="N70">
-        <v>-949.8094614452623</v>
+        <v>-898.8448214452624</v>
       </c>
       <c r="O70">
-        <v>-237.4523653613156</v>
+        <v>-224.7112053613156</v>
       </c>
       <c r="P70">
-        <v>-712.3570960839468</v>
+        <v>-674.1336160839468</v>
       </c>
       <c r="Q70">
-        <v>667.3429039160533</v>
+        <v>705.5663839160533</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1274796743180578</v>
+        <v>0.1272855525127337</v>
       </c>
       <c r="T70">
-        <v>1.591345361552244</v>
+        <v>1.588305087452314</v>
       </c>
       <c r="U70">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V70">
-        <v>0.06491929363942647</v>
+        <v>0.0676048319139219</v>
       </c>
       <c r="W70">
-        <v>0.2353940533256233</v>
+        <v>0.2253940533256233</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2596771745577059</v>
+        <v>0.2704193276556875</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2029208182098277</v>
+        <v>0.195958699232124</v>
       </c>
       <c r="C71">
-        <v>-3830.229283589958</v>
+        <v>-3782.346085523275</v>
       </c>
       <c r="D71">
-        <v>1043.382716410042</v>
+        <v>1091.265914476725</v>
       </c>
       <c r="E71">
         <v>-644.9879999999994</v>
@@ -7115,37 +7115,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M71">
-        <v>1301.833760248029</v>
+        <v>1250.119640248029</v>
       </c>
       <c r="N71">
-        <v>-968.6766173908861</v>
+        <v>-916.962497390886</v>
       </c>
       <c r="O71">
-        <v>-242.1691543477215</v>
+        <v>-229.2406243477215</v>
       </c>
       <c r="P71">
-        <v>-726.5074630431645</v>
+        <v>-687.7218730431646</v>
       </c>
       <c r="Q71">
-        <v>653.1925369568355</v>
+        <v>691.9781269568355</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1301145025218662</v>
+        <v>0.1299141187228219</v>
       </c>
       <c r="T71">
-        <v>1.64267908289264</v>
+        <v>1.639540735434647</v>
       </c>
       <c r="U71">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V71">
-        <v>0.06397843431131883</v>
+        <v>0.06662505174125637</v>
       </c>
       <c r="W71">
-        <v>0.2356309020696365</v>
+        <v>0.2256309020696365</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2559137372452753</v>
+        <v>0.2665002069650254</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.204980184376453</v>
+        <v>0.1979180653987493</v>
       </c>
       <c r="C72">
-        <v>-3918.675867433377</v>
+        <v>-3871.350203749682</v>
       </c>
       <c r="D72">
-        <v>1029.884132566623</v>
+        <v>1077.209796250318</v>
       </c>
       <c r="E72">
         <v>-570.04</v>
@@ -7197,37 +7197,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M72">
-        <v>1320.700916193652</v>
+        <v>1268.237316193652</v>
       </c>
       <c r="N72">
-        <v>-987.5437733365095</v>
+        <v>-935.0801733365095</v>
       </c>
       <c r="O72">
-        <v>-246.8859433341274</v>
+        <v>-233.7700433341274</v>
       </c>
       <c r="P72">
-        <v>-740.6578300023821</v>
+        <v>-701.310130002382</v>
       </c>
       <c r="Q72">
-        <v>639.042169997618</v>
+        <v>678.389869997618</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1329249859392617</v>
+        <v>0.1327179226802493</v>
       </c>
       <c r="T72">
-        <v>1.697435052322394</v>
+        <v>1.694192093282469</v>
       </c>
       <c r="U72">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V72">
-        <v>0.0630644566783</v>
+        <v>0.06567326528780985</v>
       </c>
       <c r="W72">
-        <v>0.2358609837066779</v>
+        <v>0.2258609837066779</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2522578267132</v>
+        <v>0.2626930611512394</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2070395505430784</v>
+        <v>0.1998774315653746</v>
       </c>
       <c r="C73">
-        <v>-4006.77764100201</v>
+        <v>-3959.996825330317</v>
       </c>
       <c r="D73">
-        <v>1016.730358997989</v>
+        <v>1063.511174669683</v>
       </c>
       <c r="E73">
         <v>-495.0920000000006</v>
@@ -7279,37 +7279,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M73">
-        <v>1339.568072139276</v>
+        <v>1286.354992139276</v>
       </c>
       <c r="N73">
-        <v>-1006.410929282133</v>
+        <v>-953.1978492821329</v>
       </c>
       <c r="O73">
-        <v>-251.6027323205332</v>
+        <v>-238.2994623205332</v>
       </c>
       <c r="P73">
-        <v>-754.8081969615996</v>
+        <v>-714.8983869615997</v>
       </c>
       <c r="Q73">
-        <v>624.8918030384004</v>
+        <v>664.8016130384003</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1359292957992362</v>
+        <v>0.1357150924278441</v>
       </c>
       <c r="T73">
-        <v>1.755967295505925</v>
+        <v>1.752612510292208</v>
       </c>
       <c r="U73">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V73">
-        <v>0.0621762248940986</v>
+        <v>0.06474828972037591</v>
       </c>
       <c r="W73">
-        <v>0.2360845841708449</v>
+        <v>0.2260845841708449</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2487048995763944</v>
+        <v>0.2589931588815036</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2090989167097037</v>
+        <v>0.201836797732</v>
       </c>
       <c r="C74">
-        <v>-4094.547649525334</v>
+        <v>-4048.299417604474</v>
       </c>
       <c r="D74">
-        <v>1003.908350474666</v>
+        <v>1050.156582395525</v>
       </c>
       <c r="E74">
         <v>-420.1440000000002</v>
@@ -7361,37 +7361,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M74">
-        <v>1358.4352280849</v>
+        <v>1304.472668084899</v>
       </c>
       <c r="N74">
-        <v>-1025.278085227757</v>
+        <v>-971.3155252277566</v>
       </c>
       <c r="O74">
-        <v>-256.3195213069392</v>
+        <v>-242.8288813069391</v>
       </c>
       <c r="P74">
-        <v>-768.9585639208176</v>
+        <v>-728.4866439208174</v>
       </c>
       <c r="Q74">
-        <v>610.7414360791824</v>
+        <v>651.2133560791826</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1391481992206375</v>
+        <v>0.1389263457288386</v>
       </c>
       <c r="T74">
-        <v>1.818680413202565</v>
+        <v>1.815205814231216</v>
       </c>
       <c r="U74">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V74">
-        <v>0.06131266621501389</v>
+        <v>0.06384900791870403</v>
       </c>
       <c r="W74">
-        <v>0.2363019735110073</v>
+        <v>0.2263019735110072</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2452506648600555</v>
+        <v>0.2553960316748161</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2111582828763291</v>
+        <v>0.2037961638986253</v>
       </c>
       <c r="C75">
-        <v>-4181.998288373528</v>
+        <v>-4136.270779858539</v>
       </c>
       <c r="D75">
-        <v>991.4057116264715</v>
+        <v>1037.133220141461</v>
       </c>
       <c r="E75">
         <v>-345.1959999999999</v>
@@ -7443,37 +7443,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M75">
-        <v>1377.302384030523</v>
+        <v>1322.590344030523</v>
       </c>
       <c r="N75">
-        <v>-1044.14524117338</v>
+        <v>-989.4332011733802</v>
       </c>
       <c r="O75">
-        <v>-261.0363102933451</v>
+        <v>-247.3583002933451</v>
       </c>
       <c r="P75">
-        <v>-783.1089308800352</v>
+        <v>-742.0749008800351</v>
       </c>
       <c r="Q75">
-        <v>596.5910691199648</v>
+        <v>637.6250991199649</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1426055399325129</v>
+        <v>0.1423754696447214</v>
       </c>
       <c r="T75">
-        <v>1.886038947024882</v>
+        <v>1.882435659202742</v>
       </c>
       <c r="U75">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V75">
-        <v>0.06047276667782192</v>
+        <v>0.06297436397461219</v>
       </c>
       <c r="W75">
-        <v>0.2365134069788364</v>
+        <v>0.2265134069788364</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2418910667112877</v>
+        <v>0.2518974558984487</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2132176490429544</v>
+        <v>0.2057555300652507</v>
       </c>
       <c r="C76">
-        <v>-4269.141343026331</v>
+        <v>-4223.923084242386</v>
       </c>
       <c r="D76">
-        <v>979.2106569736682</v>
+        <v>1024.428915757613</v>
       </c>
       <c r="E76">
         <v>-270.2480000000005</v>
@@ -7525,37 +7525,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M76">
-        <v>1396.169539976147</v>
+        <v>1340.708019976147</v>
       </c>
       <c r="N76">
-        <v>-1063.012397119004</v>
+        <v>-1007.550877119004</v>
       </c>
       <c r="O76">
-        <v>-265.7530992797509</v>
+        <v>-251.887719279751</v>
       </c>
       <c r="P76">
-        <v>-797.2592978392528</v>
+        <v>-755.6631578392529</v>
       </c>
       <c r="Q76">
-        <v>582.4407021607473</v>
+        <v>624.0368421607471</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1463288299299173</v>
+        <v>0.146089910784903</v>
       </c>
       <c r="T76">
-        <v>1.958578906525839</v>
+        <v>1.95483703071054</v>
       </c>
       <c r="U76">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V76">
-        <v>0.05965556712812163</v>
+        <v>0.06212335905603635</v>
       </c>
       <c r="W76">
-        <v>0.2367191260286161</v>
+        <v>0.2267191260286161</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2386222685124866</v>
+        <v>0.2484934362241453</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2152770152095798</v>
+        <v>0.2077148962318761</v>
       </c>
       <c r="C77">
-        <v>-4355.988026127853</v>
+        <v>-4311.26791371491</v>
       </c>
       <c r="D77">
-        <v>967.3119738721466</v>
+        <v>1012.032086285089</v>
       </c>
       <c r="E77">
         <v>-195.3000000000002</v>
@@ -7607,37 +7607,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M77">
-        <v>1415.03669592177</v>
+        <v>1358.82569592177</v>
       </c>
       <c r="N77">
-        <v>-1081.879553064628</v>
+        <v>-1025.668553064628</v>
       </c>
       <c r="O77">
-        <v>-270.4698882661569</v>
+        <v>-256.4171382661569</v>
       </c>
       <c r="P77">
-        <v>-811.4096647984707</v>
+        <v>-769.2514147984707</v>
       </c>
       <c r="Q77">
-        <v>568.2903352015294</v>
+        <v>610.4485852015293</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.150349983127114</v>
+        <v>0.1501015072162992</v>
       </c>
       <c r="T77">
-        <v>2.036922062786873</v>
+        <v>2.033030511938962</v>
       </c>
       <c r="U77">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V77">
-        <v>0.05886015956641334</v>
+        <v>0.06129504760195586</v>
       </c>
       <c r="W77">
-        <v>0.2369193592370683</v>
+        <v>0.2269193592370683</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2354406382656533</v>
+        <v>0.2451801904078235</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2173363813762051</v>
+        <v>0.2096742623985014</v>
       </c>
       <c r="C78">
-        <v>-4442.54901187223</v>
+        <v>-4398.31629726742</v>
       </c>
       <c r="D78">
-        <v>955.6989881277699</v>
+        <v>999.9317027325797</v>
       </c>
       <c r="E78">
         <v>-120.3519999999999</v>
@@ -7689,37 +7689,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M78">
-        <v>1433.903851867394</v>
+        <v>1376.943371867394</v>
       </c>
       <c r="N78">
-        <v>-1100.746709010251</v>
+        <v>-1043.786229010251</v>
       </c>
       <c r="O78">
-        <v>-275.1866772525628</v>
+        <v>-260.9465572525628</v>
       </c>
       <c r="P78">
-        <v>-825.5600317576884</v>
+        <v>-782.8396717576884</v>
       </c>
       <c r="Q78">
-        <v>554.1399682423116</v>
+        <v>596.8603282423117</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1547062324240771</v>
+        <v>0.1544474033503117</v>
       </c>
       <c r="T78">
-        <v>2.121793815402993</v>
+        <v>2.117740116603085</v>
       </c>
       <c r="U78">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V78">
-        <v>0.05808568378264474</v>
+        <v>0.0604885338177196</v>
       </c>
       <c r="W78">
-        <v>0.2371143231505613</v>
+        <v>0.2271143231505613</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2323427351305789</v>
+        <v>0.2419541352708784</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2193957475428304</v>
+        <v>0.2116336285651267</v>
       </c>
       <c r="C79">
-        <v>-4528.834467941784</v>
+        <v>-4485.078742649954</v>
       </c>
       <c r="D79">
-        <v>944.3615320582148</v>
+        <v>988.117257350046</v>
       </c>
       <c r="E79">
         <v>-45.40400000000045</v>
@@ -7771,37 +7771,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M79">
-        <v>1452.771007813017</v>
+        <v>1395.061047813017</v>
       </c>
       <c r="N79">
-        <v>-1119.613864955875</v>
+        <v>-1061.903904955875</v>
       </c>
       <c r="O79">
-        <v>-279.9034662389686</v>
+        <v>-265.4759762389687</v>
       </c>
       <c r="P79">
-        <v>-839.710398716906</v>
+        <v>-796.427928716906</v>
       </c>
       <c r="Q79">
-        <v>539.9896012830941</v>
+        <v>583.2720712830941</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1594412860077326</v>
+        <v>0.1591712034959774</v>
       </c>
       <c r="T79">
-        <v>2.214045720420514</v>
+        <v>2.209815773846698</v>
       </c>
       <c r="U79">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V79">
-        <v>0.05733132425300001</v>
+        <v>0.0597029684434635</v>
       </c>
       <c r="W79">
-        <v>0.2373042230663012</v>
+        <v>0.2273042230663012</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.229325297012</v>
+        <v>0.238811873773854</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2214551137094558</v>
+        <v>0.2135929947317521</v>
       </c>
       <c r="C80">
-        <v>-4614.854085198542</v>
+        <v>-4571.565266804706</v>
       </c>
       <c r="D80">
-        <v>933.2899148014583</v>
+        <v>976.5787331952937</v>
       </c>
       <c r="E80">
         <v>29.54399999999987</v>
@@ -7853,37 +7853,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M80">
-        <v>1471.638163758641</v>
+        <v>1413.178723758641</v>
       </c>
       <c r="N80">
-        <v>-1138.481020901498</v>
+        <v>-1080.021580901498</v>
       </c>
       <c r="O80">
-        <v>-284.6202552253746</v>
+        <v>-270.0053952253746</v>
       </c>
       <c r="P80">
-        <v>-853.8607656761237</v>
+        <v>-810.0161856761238</v>
       </c>
       <c r="Q80">
-        <v>525.8392343238763</v>
+        <v>569.6838143238763</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1646067990080841</v>
+        <v>0.1643244400185218</v>
       </c>
       <c r="T80">
-        <v>2.31468416225781</v>
+        <v>2.310261945385184</v>
       </c>
       <c r="U80">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V80">
-        <v>0.05659630727539744</v>
+        <v>0.0589375457711114</v>
       </c>
       <c r="W80">
-        <v>0.2374892537534324</v>
+        <v>0.2274892537534324</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2263852291015898</v>
+        <v>0.2357501830844456</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2235144798760811</v>
+        <v>0.2155523608983774</v>
       </c>
       <c r="C81">
-        <v>-4700.617105311337</v>
+        <v>-4657.785424191748</v>
       </c>
       <c r="D81">
-        <v>922.4748946886631</v>
+        <v>965.3065758082522</v>
       </c>
       <c r="E81">
         <v>104.4920000000002</v>
@@ -7935,37 +7935,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M81">
-        <v>1490.505319704265</v>
+        <v>1431.296399704265</v>
       </c>
       <c r="N81">
-        <v>-1157.348176847122</v>
+        <v>-1098.139256847122</v>
       </c>
       <c r="O81">
-        <v>-289.3370442117805</v>
+        <v>-274.5348142117805</v>
       </c>
       <c r="P81">
-        <v>-868.0111326353415</v>
+        <v>-823.6044426353415</v>
       </c>
       <c r="Q81">
-        <v>511.6888673646586</v>
+        <v>556.0955573646586</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1702642656275167</v>
+        <v>0.1699684609717848</v>
       </c>
       <c r="T81">
-        <v>2.42490721760342</v>
+        <v>2.420274418974955</v>
       </c>
       <c r="U81">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V81">
-        <v>0.05587989832254431</v>
+        <v>0.05819150088793278</v>
       </c>
       <c r="W81">
-        <v>0.2376696001193704</v>
+        <v>0.2276696001193704</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2235195932901772</v>
+        <v>0.2327660035517312</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2255738460427064</v>
+        <v>0.2175117270650027</v>
       </c>
       <c r="C82">
-        <v>-4786.132346484071</v>
+        <v>-4743.748333175477</v>
       </c>
       <c r="D82">
-        <v>911.9076535159297</v>
+        <v>954.2916668245232</v>
       </c>
       <c r="E82">
         <v>179.4400000000005</v>
@@ -8017,37 +8017,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M82">
-        <v>1509.372475649888</v>
+        <v>1449.414075649888</v>
       </c>
       <c r="N82">
-        <v>-1176.215332792746</v>
+        <v>-1116.256932792746</v>
       </c>
       <c r="O82">
-        <v>-294.0538331981864</v>
+        <v>-279.0642331981864</v>
       </c>
       <c r="P82">
-        <v>-882.1614995945592</v>
+        <v>-837.1926995945591</v>
       </c>
       <c r="Q82">
-        <v>497.5385004054408</v>
+        <v>542.5073004054409</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1764874789088925</v>
+        <v>0.176176884020374</v>
       </c>
       <c r="T82">
-        <v>2.546152578483591</v>
+        <v>2.541288139923703</v>
       </c>
       <c r="U82">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V82">
-        <v>0.0551813995935125</v>
+        <v>0.05746410712683361</v>
       </c>
       <c r="W82">
-        <v>0.2378454378261599</v>
+        <v>0.2278454378261599</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.22072559837405</v>
+        <v>0.2298564285073345</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2276332122093318</v>
+        <v>0.2194710932316281</v>
       </c>
       <c r="C83">
-        <v>-4871.408227435628</v>
+        <v>-4829.462700624862</v>
       </c>
       <c r="D83">
-        <v>901.5797725643716</v>
+        <v>943.5252993751374</v>
       </c>
       <c r="E83">
         <v>254.3879999999999</v>
@@ -8099,37 +8099,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M83">
-        <v>1528.239631595512</v>
+        <v>1467.531751595512</v>
       </c>
       <c r="N83">
-        <v>-1195.082488738369</v>
+        <v>-1134.374608738369</v>
       </c>
       <c r="O83">
-        <v>-298.7706221845923</v>
+        <v>-283.5936521845923</v>
       </c>
       <c r="P83">
-        <v>-896.3118665537769</v>
+        <v>-850.7809565537768</v>
       </c>
       <c r="Q83">
-        <v>483.3881334462232</v>
+        <v>528.9190434462232</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1833657672725185</v>
+        <v>0.1830388252846042</v>
       </c>
       <c r="T83">
-        <v>2.680160608930096</v>
+        <v>2.675040147288108</v>
       </c>
       <c r="U83">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V83">
-        <v>0.05450014774667902</v>
+        <v>0.05675467370551469</v>
       </c>
       <c r="W83">
-        <v>0.2380169338611769</v>
+        <v>0.2280169338611769</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2180005909867161</v>
+        <v>0.2270186948220587</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2296925783759572</v>
+        <v>0.2214304593982534</v>
       </c>
       <c r="C84">
-        <v>-4956.45278976854</v>
+        <v>-4914.936844867068</v>
       </c>
       <c r="D84">
-        <v>891.4832102314592</v>
+        <v>932.9991551329309</v>
       </c>
       <c r="E84">
         <v>329.3360000000002</v>
@@ -8181,37 +8181,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M84">
-        <v>1547.106787541136</v>
+        <v>1485.649427541136</v>
       </c>
       <c r="N84">
-        <v>-1213.949644683993</v>
+        <v>-1152.492284683993</v>
       </c>
       <c r="O84">
-        <v>-303.4874111709982</v>
+        <v>-288.1230711709982</v>
       </c>
       <c r="P84">
-        <v>-910.4622335129945</v>
+        <v>-864.3692135129945</v>
       </c>
       <c r="Q84">
-        <v>469.2377664870055</v>
+        <v>515.3307864870055</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1910083098987695</v>
+        <v>0.1906632044670822</v>
       </c>
       <c r="T84">
-        <v>2.829058420537324</v>
+        <v>2.823653488804115</v>
       </c>
       <c r="U84">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V84">
-        <v>0.05383551179854878</v>
+        <v>0.05606254353837426</v>
       </c>
       <c r="W84">
-        <v>0.2381842470660715</v>
+        <v>0.2281842470660715</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2153420471941951</v>
+        <v>0.224250174153497</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2317519445425825</v>
+        <v>0.2233898255648788</v>
       </c>
       <c r="C85">
-        <v>-5041.273718851274</v>
+        <v>-5000.178717121533</v>
       </c>
       <c r="D85">
-        <v>881.6102811487261</v>
+        <v>922.7052828784671</v>
       </c>
       <c r="E85">
         <v>404.2840000000006</v>
@@ -8263,37 +8263,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M85">
-        <v>1565.973943486759</v>
+        <v>1503.767103486759</v>
       </c>
       <c r="N85">
-        <v>-1232.816800629617</v>
+        <v>-1170.609960629617</v>
       </c>
       <c r="O85">
-        <v>-308.2042001574042</v>
+        <v>-292.6524901574041</v>
       </c>
       <c r="P85">
-        <v>-924.6126004722125</v>
+        <v>-877.9574704722124</v>
       </c>
       <c r="Q85">
-        <v>455.0873995277875</v>
+        <v>501.7425295277876</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1995499751869324</v>
+        <v>0.1991845694357341</v>
       </c>
       <c r="T85">
-        <v>2.995473621745402</v>
+        <v>2.989750752851415</v>
       </c>
       <c r="U85">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V85">
-        <v>0.05318689117446988</v>
+        <v>0.05538709120658661</v>
       </c>
       <c r="W85">
-        <v>0.2383475286274747</v>
+        <v>0.2283475286274747</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2127475646978795</v>
+        <v>0.2215483648263464</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2338113107092078</v>
+        <v>0.2253491917315041</v>
       </c>
       <c r="C86">
-        <v>-5125.878363328131</v>
+        <v>-5085.195921530662</v>
       </c>
       <c r="D86">
-        <v>871.953636671869</v>
+        <v>912.636078469338</v>
       </c>
       <c r="E86">
         <v>479.232</v>
@@ -8345,37 +8345,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M86">
-        <v>1584.841099432383</v>
+        <v>1521.884779432383</v>
       </c>
       <c r="N86">
-        <v>-1251.68395657524</v>
+        <v>-1188.72763657524</v>
       </c>
       <c r="O86">
-        <v>-312.92098914381</v>
+        <v>-297.18190914381</v>
       </c>
       <c r="P86">
-        <v>-938.7629674314301</v>
+        <v>-891.54572743143</v>
       </c>
       <c r="Q86">
-        <v>440.93703256857</v>
+        <v>488.15427256857</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2091593486361156</v>
+        <v>0.2087711050254674</v>
       </c>
       <c r="T86">
-        <v>3.182690723104488</v>
+        <v>3.176610174904627</v>
       </c>
       <c r="U86">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V86">
-        <v>0.05255371389858333</v>
+        <v>0.05472772107317487</v>
       </c>
       <c r="W86">
-        <v>0.238506922532654</v>
+        <v>0.2285069225326539</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2102148555943333</v>
+        <v>0.2189108842926994</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2358706768758332</v>
+        <v>0.2273085578981295</v>
       </c>
       <c r="C87">
-        <v>-5210.273753360843</v>
+        <v>-5169.995733893129</v>
       </c>
       <c r="D87">
-        <v>862.5062466391552</v>
+        <v>902.7842661068695</v>
       </c>
       <c r="E87">
         <v>554.1799999999994</v>
@@ -8427,37 +8427,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M87">
-        <v>1603.708255378006</v>
+        <v>1540.002455378006</v>
       </c>
       <c r="N87">
-        <v>-1270.551112520863</v>
+        <v>-1206.845312520863</v>
       </c>
       <c r="O87">
-        <v>-317.6377781302158</v>
+        <v>-301.7113281302159</v>
       </c>
       <c r="P87">
-        <v>-952.9133343906476</v>
+        <v>-905.1339843906476</v>
       </c>
       <c r="Q87">
-        <v>426.7866656093524</v>
+        <v>474.5660156093525</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2200499718785233</v>
+        <v>0.2196358453604986</v>
       </c>
       <c r="T87">
-        <v>3.394870104644787</v>
+        <v>3.388384186564936</v>
       </c>
       <c r="U87">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V87">
-        <v>0.05193543491154119</v>
+        <v>0.05408386553113752</v>
       </c>
       <c r="W87">
-        <v>0.2386625659930055</v>
+        <v>0.2286625659930055</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2077417396461647</v>
+        <v>0.2163354621245501</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2379300430424585</v>
+        <v>0.2292679240647548</v>
       </c>
       <c r="C88">
-        <v>-5294.466617697023</v>
+        <v>-5254.585119196791</v>
       </c>
       <c r="D88">
-        <v>853.2613823029762</v>
+        <v>893.142880803208</v>
       </c>
       <c r="E88">
         <v>629.1279999999997</v>
@@ -8509,37 +8509,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M88">
-        <v>1622.57541132363</v>
+        <v>1558.12013132363</v>
       </c>
       <c r="N88">
-        <v>-1289.418268466487</v>
+        <v>-1224.962988466487</v>
       </c>
       <c r="O88">
-        <v>-322.3545671166218</v>
+        <v>-306.2407471166218</v>
       </c>
       <c r="P88">
-        <v>-967.0637013498654</v>
+        <v>-918.7222413498653</v>
       </c>
       <c r="Q88">
-        <v>412.6362986501347</v>
+        <v>460.9777586501348</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.232496398441275</v>
+        <v>0.2320526914576771</v>
       </c>
       <c r="T88">
-        <v>3.63736082640513</v>
+        <v>3.630411628462431</v>
       </c>
       <c r="U88">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V88">
-        <v>0.05133153450559302</v>
+        <v>0.05345498337379872</v>
       </c>
       <c r="W88">
-        <v>0.238814589838</v>
+        <v>0.228814589838</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2053261380223721</v>
+        <v>0.2138199334951949</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2399894092090838</v>
+        <v>0.2312272902313801</v>
       </c>
       <c r="C89">
-        <v>-5378.463399652535</v>
+        <v>-5338.970748040013</v>
       </c>
       <c r="D89">
-        <v>844.2126003474641</v>
+        <v>883.7052519599864</v>
       </c>
       <c r="E89">
         <v>704.076</v>
@@ -8591,37 +8591,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M89">
-        <v>1641.442567269254</v>
+        <v>1576.237807269254</v>
       </c>
       <c r="N89">
-        <v>-1308.285424412111</v>
+        <v>-1243.080664412111</v>
       </c>
       <c r="O89">
-        <v>-327.0713561030277</v>
+        <v>-310.7701661030277</v>
       </c>
       <c r="P89">
-        <v>-981.2140683090831</v>
+        <v>-932.3104983090831</v>
       </c>
       <c r="Q89">
-        <v>398.4859316909169</v>
+        <v>447.389501690917</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2468576598598346</v>
+        <v>0.2463798215698061</v>
       </c>
       <c r="T89">
-        <v>3.917157813051678</v>
+        <v>3.90967406142108</v>
       </c>
       <c r="U89">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V89">
-        <v>0.0507415168675977</v>
+        <v>0.05284055827754815</v>
       </c>
       <c r="W89">
-        <v>0.2389631188819601</v>
+        <v>0.2289631188819601</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2029660674703908</v>
+        <v>0.2113622331101926</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2420487753757092</v>
+        <v>0.2331866563980055</v>
       </c>
       <c r="C90">
-        <v>-5462.270272087617</v>
+        <v>-5423.159012022747</v>
       </c>
       <c r="D90">
-        <v>835.3537279123826</v>
+        <v>874.4649879772514</v>
       </c>
       <c r="E90">
         <v>779.0239999999994</v>
@@ -8673,37 +8673,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M90">
-        <v>1660.309723214877</v>
+        <v>1594.355483214877</v>
       </c>
       <c r="N90">
-        <v>-1327.152580357734</v>
+        <v>-1261.198340357734</v>
       </c>
       <c r="O90">
-        <v>-331.7881450894336</v>
+        <v>-315.2995850894335</v>
       </c>
       <c r="P90">
-        <v>-995.3644352683007</v>
+        <v>-945.8987552683006</v>
       </c>
       <c r="Q90">
-        <v>384.3355647316994</v>
+        <v>433.8012447316994</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2636124648481541</v>
+        <v>0.2630948067006233</v>
       </c>
       <c r="T90">
-        <v>4.243587630805985</v>
+        <v>4.235480233206171</v>
       </c>
       <c r="U90">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V90">
-        <v>0.05016490872137501</v>
+        <v>0.05224009738803057</v>
       </c>
       <c r="W90">
-        <v>0.2391082722658303</v>
+        <v>0.2291082722658303</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2006596348855</v>
+        <v>0.2089603895521223</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2441081415423345</v>
+        <v>0.2351460225646308</v>
       </c>
       <c r="C91">
-        <v>-5545.893151449844</v>
+        <v>-5507.156038182018</v>
       </c>
       <c r="D91">
-        <v>826.6788485501563</v>
+        <v>865.4159618179816</v>
       </c>
       <c r="E91">
         <v>853.9719999999998</v>
@@ -8755,37 +8755,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M91">
-        <v>1679.176879160501</v>
+        <v>1612.473159160501</v>
       </c>
       <c r="N91">
-        <v>-1346.019736303358</v>
+        <v>-1279.316016303358</v>
       </c>
       <c r="O91">
-        <v>-336.5049340758395</v>
+        <v>-319.8290040758395</v>
       </c>
       <c r="P91">
-        <v>-1009.514802227519</v>
+        <v>-959.4870122275183</v>
       </c>
       <c r="Q91">
-        <v>370.1851977724815</v>
+        <v>420.2129877724817</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2834135980161682</v>
+        <v>0.2828488800370436</v>
       </c>
       <c r="T91">
-        <v>4.62936832451562</v>
+        <v>4.620523890770368</v>
       </c>
       <c r="U91">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.04960125806158427</v>
+        <v>0.0516531300016482</v>
       </c>
       <c r="W91">
-        <v>0.2392501637759057</v>
+        <v>0.2292501637759056</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1984050322463371</v>
+        <v>0.2066125200065928</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2461675077089598</v>
+        <v>0.2371053887312561</v>
       </c>
       <c r="C92">
-        <v>-5629.337710951107</v>
+        <v>-5590.967702540295</v>
       </c>
       <c r="D92">
-        <v>818.182289048893</v>
+        <v>856.5522974597042</v>
       </c>
       <c r="E92">
         <v>928.9200000000001</v>
@@ -8837,37 +8837,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M92">
-        <v>1698.044035106125</v>
+        <v>1630.590835106124</v>
       </c>
       <c r="N92">
-        <v>-1364.886892248982</v>
+        <v>-1297.433692248982</v>
       </c>
       <c r="O92">
-        <v>-341.2217230622454</v>
+        <v>-324.3584230622454</v>
       </c>
       <c r="P92">
-        <v>-1023.665169186736</v>
+        <v>-973.0752691867361</v>
       </c>
       <c r="Q92">
-        <v>356.0348308132639</v>
+        <v>406.6247308132639</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.307174957817785</v>
+        <v>0.306553768040748</v>
       </c>
       <c r="T92">
-        <v>5.092305156967183</v>
+        <v>5.082576279847405</v>
       </c>
       <c r="U92">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.04905013297201111</v>
+        <v>0.05107920633496322</v>
       </c>
       <c r="W92">
-        <v>0.2393889021413126</v>
+        <v>0.2293889021413126</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1962005318880444</v>
+        <v>0.2043168253398528</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2482268738755852</v>
+        <v>0.2390647548978815</v>
       </c>
       <c r="C93">
-        <v>-5712.609392940262</v>
+        <v>-5674.599642829743</v>
       </c>
       <c r="D93">
-        <v>809.8586070597369</v>
+        <v>847.8683571702562</v>
       </c>
       <c r="E93">
         <v>1003.867999999999</v>
@@ -8919,37 +8919,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M93">
-        <v>1716.911191051748</v>
+        <v>1648.708511051748</v>
       </c>
       <c r="N93">
-        <v>-1383.754048194605</v>
+        <v>-1315.551368194605</v>
       </c>
       <c r="O93">
-        <v>-345.9385120486513</v>
+        <v>-328.8878420486512</v>
       </c>
       <c r="P93">
-        <v>-1037.815536145954</v>
+        <v>-986.6635261459537</v>
       </c>
       <c r="Q93">
-        <v>341.8844638540463</v>
+        <v>393.0364738540463</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.336216619797539</v>
+        <v>0.3355264089341644</v>
       </c>
       <c r="T93">
-        <v>5.658116841074648</v>
+        <v>5.647306977608228</v>
       </c>
       <c r="U93">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.04851112052176924</v>
+        <v>0.05051789637523835</v>
       </c>
       <c r="W93">
-        <v>0.2395245913118755</v>
+        <v>0.2295245913118755</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1940444820870769</v>
+        <v>0.2020715855009534</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2502862400422106</v>
+        <v>0.2410241210645068</v>
       </c>
       <c r="C94">
-        <v>-5795.713420528158</v>
+        <v>-5758.057270450207</v>
       </c>
       <c r="D94">
-        <v>801.7025794718418</v>
+        <v>839.3587295497917</v>
       </c>
       <c r="E94">
         <v>1078.816</v>
@@ -9001,37 +9001,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M94">
-        <v>1735.778346997372</v>
+        <v>1666.826186997372</v>
       </c>
       <c r="N94">
-        <v>-1402.621204140229</v>
+        <v>-1333.669044140229</v>
       </c>
       <c r="O94">
-        <v>-350.6553010350572</v>
+        <v>-333.4172610350572</v>
       </c>
       <c r="P94">
-        <v>-1051.965903105172</v>
+        <v>-1000.251783105172</v>
       </c>
       <c r="Q94">
-        <v>327.7340968948283</v>
+        <v>379.4482168948284</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3725186972722314</v>
+        <v>0.3717422100509351</v>
       </c>
       <c r="T94">
-        <v>6.36538144620898</v>
+        <v>6.353220349809259</v>
       </c>
       <c r="U94">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.04798382573348913</v>
+        <v>0.04996878880594228</v>
       </c>
       <c r="W94">
-        <v>0.2396573307178609</v>
+        <v>0.2296573307178609</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1919353029339566</v>
+        <v>0.1998751552237691</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2523456062088359</v>
+        <v>0.2429834872311322</v>
       </c>
       <c r="C95">
-        <v>-5878.654808517207</v>
+        <v>-5841.345781714286</v>
       </c>
       <c r="D95">
-        <v>793.7091914827928</v>
+        <v>831.0182182857136</v>
       </c>
       <c r="E95">
         <v>1153.764</v>
@@ -9083,37 +9083,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M95">
-        <v>1754.645502942995</v>
+        <v>1684.943862942995</v>
       </c>
       <c r="N95">
-        <v>-1421.488360085852</v>
+        <v>-1351.786720085852</v>
       </c>
       <c r="O95">
-        <v>-355.3720900214631</v>
+        <v>-337.9466800214631</v>
       </c>
       <c r="P95">
-        <v>-1066.116270064389</v>
+        <v>-1013.840040064389</v>
       </c>
       <c r="Q95">
-        <v>313.5837299356106</v>
+        <v>365.8599599356107</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4191927968825503</v>
+        <v>0.4183053829153544</v>
       </c>
       <c r="T95">
-        <v>7.274721652810265</v>
+        <v>7.260823256924867</v>
       </c>
       <c r="U95">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.04746787061807527</v>
+        <v>0.0494314900015773</v>
       </c>
       <c r="W95">
-        <v>0.2397872155129649</v>
+        <v>0.2297872155129649</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1898714824723011</v>
+        <v>0.1977259600063093</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2544049723754612</v>
+        <v>0.2449428533977575</v>
       </c>
       <c r="C96">
-        <v>-5961.438373683589</v>
+        <v>-5924.470168428533</v>
       </c>
       <c r="D96">
-        <v>785.8736263164114</v>
+        <v>822.8418315714675</v>
       </c>
       <c r="E96">
         <v>1228.712</v>
@@ -9165,37 +9165,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M96">
-        <v>1773.512658888619</v>
+        <v>1703.061538888619</v>
       </c>
       <c r="N96">
-        <v>-1440.355516031476</v>
+        <v>-1369.904396031476</v>
       </c>
       <c r="O96">
-        <v>-360.088879007869</v>
+        <v>-342.476099007869</v>
       </c>
       <c r="P96">
-        <v>-1080.266637023607</v>
+        <v>-1027.428297023607</v>
       </c>
       <c r="Q96">
-        <v>299.433362976393</v>
+        <v>352.2717029763928</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4814249296963087</v>
+        <v>0.480389613401247</v>
       </c>
       <c r="T96">
-        <v>8.487175261611977</v>
+        <v>8.470960466412349</v>
       </c>
       <c r="U96">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.04696289327107447</v>
+        <v>0.04890562308666691</v>
       </c>
       <c r="W96">
-        <v>0.2399143368017901</v>
+        <v>0.2299143368017901</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1878515730842979</v>
+        <v>0.1956224923466676</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2564643385420866</v>
+        <v>0.2469022195643829</v>
       </c>
       <c r="C97">
-        <v>-6044.068744456352</v>
+        <v>-6007.435227856107</v>
       </c>
       <c r="D97">
-        <v>778.191255543648</v>
+        <v>814.8247721438922</v>
       </c>
       <c r="E97">
         <v>1303.66</v>
@@ -9247,37 +9247,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M97">
-        <v>1792.379814834243</v>
+        <v>1721.179214834242</v>
       </c>
       <c r="N97">
-        <v>-1459.2226719771</v>
+        <v>-1388.0220719771</v>
       </c>
       <c r="O97">
-        <v>-364.8056679942749</v>
+        <v>-347.0055179942749</v>
       </c>
       <c r="P97">
-        <v>-1094.417003982825</v>
+        <v>-1041.016553982825</v>
       </c>
       <c r="Q97">
-        <v>285.2829960171753</v>
+        <v>338.6834460171754</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5685499156355706</v>
+        <v>0.5673075360814966</v>
       </c>
       <c r="T97">
-        <v>10.18461031393438</v>
+        <v>10.16515255969482</v>
       </c>
       <c r="U97">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.04646854702611579</v>
+        <v>0.04839082705417568</v>
       </c>
       <c r="W97">
-        <v>0.2400387818529559</v>
+        <v>0.2300387818529559</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1858741881044632</v>
+        <v>0.1935633082167028</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2585237047087119</v>
+        <v>0.2488615857310082</v>
       </c>
       <c r="C98">
-        <v>-6126.550370034303</v>
+        <v>-6090.245572102655</v>
       </c>
       <c r="D98">
-        <v>770.6576299656958</v>
+        <v>806.9624278973438</v>
       </c>
       <c r="E98">
         <v>1378.607999999999</v>
@@ -9329,37 +9329,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M98">
-        <v>1811.246970779866</v>
+        <v>1739.296890779866</v>
       </c>
       <c r="N98">
-        <v>-1478.089827922723</v>
+        <v>-1406.139747922723</v>
       </c>
       <c r="O98">
-        <v>-369.5224569806808</v>
+        <v>-351.5349369806808</v>
       </c>
       <c r="P98">
-        <v>-1108.567370942042</v>
+        <v>-1054.604810942042</v>
       </c>
       <c r="Q98">
-        <v>271.1326290579577</v>
+        <v>325.0951890579579</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6992373945444619</v>
+        <v>0.6976844201018693</v>
       </c>
       <c r="T98">
-        <v>12.73076289241794</v>
+        <v>12.7064406996185</v>
       </c>
       <c r="U98">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.04598449966126042</v>
+        <v>0.04788675593902802</v>
       </c>
       <c r="W98">
-        <v>0.240160634298889</v>
+        <v>0.2301606342988889</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1839379986450417</v>
+        <v>0.1915470237561121</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2605830708753372</v>
+        <v>0.2508209518976335</v>
       </c>
       <c r="C99">
-        <v>-6208.887528978418</v>
+        <v>-6172.905636963954</v>
       </c>
       <c r="D99">
-        <v>763.2684710215808</v>
+        <v>799.2503630360452</v>
       </c>
       <c r="E99">
         <v>1453.556</v>
@@ -9411,37 +9411,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M99">
-        <v>1830.11412672549</v>
+        <v>1757.41456672549</v>
       </c>
       <c r="N99">
-        <v>-1496.956983868347</v>
+        <v>-1424.257423868347</v>
       </c>
       <c r="O99">
-        <v>-374.2392459670867</v>
+        <v>-356.0643559670867</v>
       </c>
       <c r="P99">
-        <v>-1122.71773790126</v>
+        <v>-1068.19306790126</v>
       </c>
       <c r="Q99">
-        <v>256.98226209874</v>
+        <v>311.50693209874</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.9170498593926159</v>
+        <v>0.9149792268024924</v>
       </c>
       <c r="T99">
-        <v>16.97435052322393</v>
+        <v>16.94192093282467</v>
       </c>
       <c r="U99">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.0455104326544433</v>
+        <v>0.04739307804274938</v>
       </c>
       <c r="W99">
-        <v>0.2402799743232564</v>
+        <v>0.2302799743232564</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1820417306177732</v>
+        <v>0.1895723121709976</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2626424370419626</v>
+        <v>0.2527803180642589</v>
       </c>
       <c r="C100">
-        <v>-6291.084337314628</v>
+        <v>-6255.419690271059</v>
       </c>
       <c r="D100">
-        <v>756.0196626853716</v>
+        <v>791.6843097289402</v>
       </c>
       <c r="E100">
         <v>1528.504</v>
@@ -9493,37 +9493,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M100">
-        <v>1848.981282671113</v>
+        <v>1775.532242671113</v>
       </c>
       <c r="N100">
-        <v>-1515.824139813971</v>
+        <v>-1442.37509981397</v>
       </c>
       <c r="O100">
-        <v>-378.9560349534926</v>
+        <v>-360.5937749534926</v>
       </c>
       <c r="P100">
-        <v>-1136.868104860478</v>
+        <v>-1081.781324860478</v>
       </c>
       <c r="Q100">
-        <v>242.8318951395222</v>
+        <v>297.9186751395223</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.352674789088924</v>
+        <v>1.349568840203739</v>
       </c>
       <c r="T100">
-        <v>25.46152578483589</v>
+        <v>25.412881399237</v>
       </c>
       <c r="U100">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.0450460404845</v>
+        <v>0.04690947520557846</v>
       </c>
       <c r="W100">
-        <v>0.2403968788369225</v>
+        <v>0.2303968788369225</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.180184161938</v>
+        <v>0.1876379008223139</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2647018032085879</v>
+        <v>0.2547396842308842</v>
       </c>
       <c r="C101">
-        <v>-6373.144756179237</v>
+        <v>-6337.791839765881</v>
       </c>
       <c r="D101">
-        <v>748.9072438207626</v>
+        <v>784.2601602341177</v>
       </c>
       <c r="E101">
         <v>1603.451999999999</v>
@@ -9575,37 +9575,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M101">
-        <v>1867.848438616737</v>
+        <v>1793.649918616737</v>
       </c>
       <c r="N101">
-        <v>-1534.691295759594</v>
+        <v>-1460.492775759594</v>
       </c>
       <c r="O101">
-        <v>-383.6728239398985</v>
+        <v>-365.1231939398984</v>
       </c>
       <c r="P101">
-        <v>-1151.018471819695</v>
+        <v>-1095.369581819695</v>
       </c>
       <c r="Q101">
-        <v>228.6815281803047</v>
+        <v>284.3304181803048</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.659549578177848</v>
+        <v>2.653337680407477</v>
       </c>
       <c r="T101">
-        <v>50.92305156967178</v>
+        <v>50.825762798474</v>
       </c>
       <c r="U101">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V101">
-        <v>0.04459102997455556</v>
+        <v>0.04643564212269384</v>
       </c>
       <c r="W101">
-        <v>0.2405114216432419</v>
+        <v>0.2305114216432418</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.1783641198982222</v>
+        <v>0.1857425684907753</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/belgium/belgium_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_telecom_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0731318574307768</v>
+        <v>0.07302730241216886</v>
       </c>
       <c r="C2">
-        <v>6293.114100009267</v>
+        <v>6241.188585593691</v>
       </c>
       <c r="D2">
-        <v>5995.314100009266</v>
+        <v>6018.336585593691</v>
       </c>
       <c r="E2">
-        <v>-5816.4</v>
+        <v>-5741.451999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>74.94799999999999</v>
       </c>
       <c r="G2">
         <v>297.8</v>
@@ -1457,28 +1457,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.214821945623606</v>
       </c>
       <c r="N2">
-        <v>333.1571428571428</v>
+        <v>328.9423209115192</v>
       </c>
       <c r="O2">
-        <v>83.28928571428571</v>
+        <v>82.23558022787981</v>
       </c>
       <c r="P2">
-        <v>249.8678571428571</v>
+        <v>246.7067406836394</v>
       </c>
       <c r="Q2">
-        <v>1629.567857142857</v>
+        <v>1626.40674068364</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0731318574307768</v>
+        <v>0.07333891695676753</v>
       </c>
       <c r="T2">
-        <v>0.5327487740853231</v>
+        <v>0.5367847496465755</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>79.04417960124539</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07302730241216886</v>
+        <v>0.07292274739356093</v>
       </c>
       <c r="C3">
-        <v>6241.188585593691</v>
+        <v>6189.44056915601</v>
       </c>
       <c r="D3">
-        <v>6018.336585593691</v>
+        <v>6041.536569156009</v>
       </c>
       <c r="E3">
-        <v>-5741.451999999999</v>
+        <v>-5666.504</v>
       </c>
       <c r="F3">
-        <v>74.94799999999999</v>
+        <v>149.896</v>
       </c>
       <c r="G3">
         <v>297.8</v>
@@ -1539,28 +1539,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M3">
-        <v>4.214821945623606</v>
+        <v>8.429643891247212</v>
       </c>
       <c r="N3">
-        <v>328.9423209115192</v>
+        <v>324.7274989658956</v>
       </c>
       <c r="O3">
-        <v>82.23558022787981</v>
+        <v>81.18187474147391</v>
       </c>
       <c r="P3">
-        <v>246.7067406836394</v>
+        <v>243.5456242244217</v>
       </c>
       <c r="Q3">
-        <v>1626.40674068364</v>
+        <v>1623.245624224422</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07333891695676753</v>
+        <v>0.07355020218737032</v>
       </c>
       <c r="T3">
-        <v>0.5367847496465755</v>
+        <v>0.5409030920560168</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>79.04417960124539</v>
+        <v>39.52208980062269</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07292274739356093</v>
+        <v>0.07281819237495298</v>
       </c>
       <c r="C4">
-        <v>6189.44056915601</v>
+        <v>6137.872111341605</v>
       </c>
       <c r="D4">
-        <v>6041.536569156009</v>
+        <v>6064.916111341605</v>
       </c>
       <c r="E4">
-        <v>-5666.504</v>
+        <v>-5591.556</v>
       </c>
       <c r="F4">
-        <v>149.896</v>
+        <v>224.844</v>
       </c>
       <c r="G4">
         <v>297.8</v>
@@ -1621,28 +1621,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M4">
-        <v>8.429643891247212</v>
+        <v>12.64446583687081</v>
       </c>
       <c r="N4">
-        <v>324.7274989658956</v>
+        <v>320.512677020272</v>
       </c>
       <c r="O4">
-        <v>81.18187474147391</v>
+        <v>80.128169255068</v>
       </c>
       <c r="P4">
-        <v>243.5456242244217</v>
+        <v>240.384507765204</v>
       </c>
       <c r="Q4">
-        <v>1623.245624224422</v>
+        <v>1620.084507765204</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07355020218737032</v>
+        <v>0.07376584381448037</v>
       </c>
       <c r="T4">
-        <v>0.5409030920560168</v>
+        <v>0.5451063487419413</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>39.52208980062269</v>
+        <v>26.3480598670818</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07281819237495298</v>
+        <v>0.07271363735634505</v>
       </c>
       <c r="C5">
-        <v>6137.872111341605</v>
+        <v>6086.485304816902</v>
       </c>
       <c r="D5">
-        <v>6064.916111341605</v>
+        <v>6088.477304816903</v>
       </c>
       <c r="E5">
-        <v>-5591.556</v>
+        <v>-5516.607999999999</v>
       </c>
       <c r="F5">
-        <v>224.844</v>
+        <v>299.792</v>
       </c>
       <c r="G5">
         <v>297.8</v>
@@ -1703,28 +1703,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M5">
-        <v>12.64446583687081</v>
+        <v>16.85928778249442</v>
       </c>
       <c r="N5">
-        <v>320.512677020272</v>
+        <v>316.2978550746484</v>
       </c>
       <c r="O5">
-        <v>80.128169255068</v>
+        <v>79.0744637686621</v>
       </c>
       <c r="P5">
-        <v>240.384507765204</v>
+        <v>237.2233913059863</v>
       </c>
       <c r="Q5">
-        <v>1620.084507765204</v>
+        <v>1616.923391305986</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07376584381448037</v>
+        <v>0.07398597797548857</v>
       </c>
       <c r="T5">
-        <v>0.5451063487419413</v>
+        <v>0.5493971732754894</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>26.3480598670818</v>
+        <v>19.76104490031135</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07271363735634505</v>
+        <v>0.07260908233773712</v>
       </c>
       <c r="C6">
-        <v>6086.485304816902</v>
+        <v>6035.282274893816</v>
       </c>
       <c r="D6">
-        <v>6088.477304816903</v>
+        <v>6112.222274893816</v>
       </c>
       <c r="E6">
-        <v>-5516.607999999999</v>
+        <v>-5441.66</v>
       </c>
       <c r="F6">
-        <v>299.792</v>
+        <v>374.74</v>
       </c>
       <c r="G6">
         <v>297.8</v>
@@ -1785,28 +1785,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M6">
-        <v>16.85928778249442</v>
+        <v>21.07410972811803</v>
       </c>
       <c r="N6">
-        <v>316.2978550746484</v>
+        <v>312.0830331290248</v>
       </c>
       <c r="O6">
-        <v>79.0744637686621</v>
+        <v>78.02075828225621</v>
       </c>
       <c r="P6">
-        <v>237.2233913059863</v>
+        <v>234.0622748467686</v>
       </c>
       <c r="Q6">
-        <v>1616.923391305986</v>
+        <v>1613.762274846769</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07398597797548857</v>
+        <v>0.07421074653988641</v>
       </c>
       <c r="T6">
-        <v>0.5493971732754894</v>
+        <v>0.5537783309571122</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.76104490031135</v>
+        <v>15.80883592024908</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07260908233773712</v>
+        <v>0.07250452731912917</v>
       </c>
       <c r="C7">
-        <v>6035.282274893816</v>
+        <v>5984.265180168806</v>
       </c>
       <c r="D7">
-        <v>6112.222274893816</v>
+        <v>6136.153180168806</v>
       </c>
       <c r="E7">
-        <v>-5441.66</v>
+        <v>-5366.712</v>
       </c>
       <c r="F7">
-        <v>374.74</v>
+        <v>449.688</v>
       </c>
       <c r="G7">
         <v>297.8</v>
@@ -1867,28 +1867,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M7">
-        <v>21.07410972811803</v>
+        <v>25.28893167374163</v>
       </c>
       <c r="N7">
-        <v>312.0830331290248</v>
+        <v>307.8682111834012</v>
       </c>
       <c r="O7">
-        <v>78.02075828225621</v>
+        <v>76.96705279585031</v>
       </c>
       <c r="P7">
-        <v>234.0622748467686</v>
+        <v>230.9011583875509</v>
       </c>
       <c r="Q7">
-        <v>1613.762274846769</v>
+        <v>1610.601158387551</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07421074653988641</v>
+        <v>0.07444029741416504</v>
       </c>
       <c r="T7">
-        <v>0.5537783309571122</v>
+        <v>0.5582527047596204</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.80883592024908</v>
+        <v>13.1740299335409</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07250452731912915</v>
+        <v>0.07247872230052123</v>
       </c>
       <c r="C8">
-        <v>5984.265180168809</v>
+        <v>5915.252379958803</v>
       </c>
       <c r="D8">
-        <v>6136.153180168809</v>
+        <v>6142.088379958802</v>
       </c>
       <c r="E8">
-        <v>-5366.712</v>
+        <v>-5291.764</v>
       </c>
       <c r="F8">
-        <v>449.6879999999999</v>
+        <v>524.6359999999999</v>
       </c>
       <c r="G8">
         <v>297.8</v>
@@ -1949,45 +1949,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M8">
-        <v>25.28893167374163</v>
+        <v>30.29070761936523</v>
       </c>
       <c r="N8">
-        <v>307.8682111834012</v>
+        <v>302.8664352377776</v>
       </c>
       <c r="O8">
-        <v>76.96705279585031</v>
+        <v>75.71660880944441</v>
       </c>
       <c r="P8">
-        <v>230.9011583875509</v>
+        <v>227.1498264283332</v>
       </c>
       <c r="Q8">
-        <v>1610.601158387551</v>
+        <v>1606.849826428333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07444029741416504</v>
+        <v>0.07467478486638515</v>
       </c>
       <c r="T8">
-        <v>0.5582527047596204</v>
+        <v>0.5628233016546558</v>
       </c>
       <c r="U8">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04217746249690058</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.1740299335409</v>
+        <v>10.99865830285692</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07247872230052123</v>
+        <v>0.07248741728191331</v>
       </c>
       <c r="C9">
-        <v>5915.252379958802</v>
+        <v>5838.30323673808</v>
       </c>
       <c r="D9">
-        <v>6142.088379958802</v>
+        <v>6140.08723673808</v>
       </c>
       <c r="E9">
-        <v>-5291.763999999999</v>
+        <v>-5216.816</v>
       </c>
       <c r="F9">
-        <v>524.636</v>
+        <v>599.5839999999999</v>
       </c>
       <c r="G9">
         <v>297.8</v>
@@ -2031,45 +2031,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M9">
-        <v>30.29070761936524</v>
+        <v>35.63724436498884</v>
       </c>
       <c r="N9">
-        <v>302.8664352377776</v>
+        <v>297.519898492154</v>
       </c>
       <c r="O9">
-        <v>75.71660880944441</v>
+        <v>74.37997462303851</v>
       </c>
       <c r="P9">
-        <v>227.1498264283332</v>
+        <v>223.1399238691155</v>
       </c>
       <c r="Q9">
-        <v>1606.849826428333</v>
+        <v>1602.839923869116</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07467478486638515</v>
+        <v>0.07491436987191441</v>
       </c>
       <c r="T9">
-        <v>0.5628233016546558</v>
+        <v>0.5674932593517572</v>
       </c>
       <c r="U9">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04330246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.99865830285692</v>
+        <v>9.348566332599134</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07248741728191331</v>
+        <v>0.07240686226330538</v>
       </c>
       <c r="C10">
-        <v>5838.30323673808</v>
+        <v>5781.944983876055</v>
       </c>
       <c r="D10">
-        <v>6140.08723673808</v>
+        <v>6158.676983876055</v>
       </c>
       <c r="E10">
-        <v>-5216.816</v>
+        <v>-5141.867999999999</v>
       </c>
       <c r="F10">
-        <v>599.5839999999999</v>
+        <v>674.5319999999999</v>
       </c>
       <c r="G10">
         <v>297.8</v>
@@ -2113,28 +2113,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M10">
-        <v>35.63724436498884</v>
+        <v>40.09189991061244</v>
       </c>
       <c r="N10">
-        <v>297.519898492154</v>
+        <v>293.0652429465304</v>
       </c>
       <c r="O10">
-        <v>74.37997462303851</v>
+        <v>73.2663107366326</v>
       </c>
       <c r="P10">
-        <v>223.1399238691155</v>
+        <v>219.7989322098978</v>
       </c>
       <c r="Q10">
-        <v>1602.839923869116</v>
+        <v>1599.498932209898</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07491436987191441</v>
+        <v>0.07515922048196079</v>
       </c>
       <c r="T10">
-        <v>0.5674932593517572</v>
+        <v>0.5722658534817618</v>
       </c>
       <c r="U10">
         <v>0.05943661666253409</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.348566332599134</v>
+        <v>8.309836740088119</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07240686226330538</v>
+        <v>0.07238630724469744</v>
       </c>
       <c r="C11">
-        <v>5781.944983876055</v>
+        <v>5711.758522168633</v>
       </c>
       <c r="D11">
-        <v>6158.676983876055</v>
+        <v>6163.438522168633</v>
       </c>
       <c r="E11">
-        <v>-5141.867999999999</v>
+        <v>-5066.92</v>
       </c>
       <c r="F11">
-        <v>674.5319999999999</v>
+        <v>749.4799999999999</v>
       </c>
       <c r="G11">
         <v>297.8</v>
@@ -2195,45 +2195,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M11">
-        <v>40.09189991061244</v>
+        <v>45.14613945623605</v>
       </c>
       <c r="N11">
-        <v>293.0652429465304</v>
+        <v>288.0110034009068</v>
       </c>
       <c r="O11">
-        <v>73.2663107366326</v>
+        <v>72.0027508502267</v>
       </c>
       <c r="P11">
-        <v>219.7989322098978</v>
+        <v>216.0082525506801</v>
       </c>
       <c r="Q11">
-        <v>1599.498932209898</v>
+        <v>1595.70825255068</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07515922048196079</v>
+        <v>0.07540951221667486</v>
       </c>
       <c r="T11">
-        <v>0.5722658534817618</v>
+        <v>0.5771445052591</v>
       </c>
       <c r="U11">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04457746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.309836740088119</v>
+        <v>7.379526729635434</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07238630724469744</v>
+        <v>0.0723117522260895</v>
       </c>
       <c r="C12">
-        <v>5711.758522168633</v>
+        <v>5654.143034549951</v>
       </c>
       <c r="D12">
-        <v>6163.438522168633</v>
+        <v>6180.771034549951</v>
       </c>
       <c r="E12">
-        <v>-5066.92</v>
+        <v>-4991.972</v>
       </c>
       <c r="F12">
-        <v>749.48</v>
+        <v>824.4279999999999</v>
       </c>
       <c r="G12">
         <v>297.8</v>
@@ -2277,28 +2277,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M12">
-        <v>45.14613945623606</v>
+        <v>49.66075340185965</v>
       </c>
       <c r="N12">
-        <v>288.0110034009068</v>
+        <v>283.4963894552832</v>
       </c>
       <c r="O12">
-        <v>72.0027508502267</v>
+        <v>70.87409736382079</v>
       </c>
       <c r="P12">
-        <v>216.0082525506801</v>
+        <v>212.6222920914624</v>
       </c>
       <c r="Q12">
-        <v>1595.70825255068</v>
+        <v>1592.322292091462</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07540951221667486</v>
+        <v>0.0756654284847533</v>
       </c>
       <c r="T12">
-        <v>0.5771445052591</v>
+        <v>0.582132789660648</v>
       </c>
       <c r="U12">
         <v>0.0602366166625341</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.379526729635433</v>
+        <v>6.70866066330494</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0723117522260895</v>
+        <v>0.07223719720748156</v>
       </c>
       <c r="C13">
-        <v>5654.143034549951</v>
+        <v>5596.625305084147</v>
       </c>
       <c r="D13">
-        <v>6180.771034549951</v>
+        <v>6198.201305084147</v>
       </c>
       <c r="E13">
-        <v>-4991.972</v>
+        <v>-4917.023999999999</v>
       </c>
       <c r="F13">
-        <v>824.4279999999999</v>
+        <v>899.3759999999999</v>
       </c>
       <c r="G13">
         <v>297.8</v>
@@ -2359,28 +2359,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M13">
-        <v>49.66075340185965</v>
+        <v>54.17536734748326</v>
       </c>
       <c r="N13">
-        <v>283.4963894552832</v>
+        <v>278.9817755096596</v>
       </c>
       <c r="O13">
-        <v>70.87409736382079</v>
+        <v>69.7454438774149</v>
       </c>
       <c r="P13">
-        <v>212.6222920914624</v>
+        <v>209.2363316322447</v>
       </c>
       <c r="Q13">
-        <v>1592.322292091462</v>
+        <v>1588.936331632245</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0756654284847533</v>
+        <v>0.0759271610316517</v>
       </c>
       <c r="T13">
-        <v>0.582132789660648</v>
+        <v>0.5872344441622311</v>
       </c>
       <c r="U13">
         <v>0.0602366166625341</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.70866066330494</v>
+        <v>6.149605608029528</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07223719720748156</v>
+        <v>0.07226014218887362</v>
       </c>
       <c r="C14">
-        <v>5596.625305084147</v>
+        <v>5516.302518637641</v>
       </c>
       <c r="D14">
-        <v>6198.201305084147</v>
+        <v>6192.82651863764</v>
       </c>
       <c r="E14">
-        <v>-4917.023999999999</v>
+        <v>-4842.076</v>
       </c>
       <c r="F14">
-        <v>899.3759999999999</v>
+        <v>974.324</v>
       </c>
       <c r="G14">
         <v>297.8</v>
@@ -2441,45 +2441,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M14">
-        <v>54.17536734748326</v>
+        <v>59.66430529310687</v>
       </c>
       <c r="N14">
-        <v>278.9817755096596</v>
+        <v>273.492837564036</v>
       </c>
       <c r="O14">
-        <v>69.7454438774149</v>
+        <v>68.373209391009</v>
       </c>
       <c r="P14">
-        <v>209.2363316322447</v>
+        <v>205.119628173027</v>
       </c>
       <c r="Q14">
-        <v>1588.936331632245</v>
+        <v>1584.819628173027</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0759271610316517</v>
+        <v>0.07619491041870868</v>
       </c>
       <c r="T14">
-        <v>0.5872344441622311</v>
+        <v>0.5924533780776438</v>
       </c>
       <c r="U14">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04517746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.149605608029528</v>
+        <v>5.583860253135859</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07226014218887362</v>
+        <v>0.07219308717026569</v>
       </c>
       <c r="C15">
-        <v>5516.302518637641</v>
+        <v>5457.088187638316</v>
       </c>
       <c r="D15">
-        <v>6192.82651863764</v>
+        <v>6208.560187638315</v>
       </c>
       <c r="E15">
-        <v>-4842.076</v>
+        <v>-4767.128</v>
       </c>
       <c r="F15">
-        <v>974.324</v>
+        <v>1049.272</v>
       </c>
       <c r="G15">
         <v>297.8</v>
@@ -2523,28 +2523,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M15">
-        <v>59.66430529310687</v>
+        <v>64.25386723873048</v>
       </c>
       <c r="N15">
-        <v>273.492837564036</v>
+        <v>268.9032756184124</v>
       </c>
       <c r="O15">
-        <v>68.373209391009</v>
+        <v>67.22581890460309</v>
       </c>
       <c r="P15">
-        <v>205.119628173027</v>
+        <v>201.6774567138092</v>
       </c>
       <c r="Q15">
-        <v>1584.819628173027</v>
+        <v>1581.377456713809</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07619491041870868</v>
+        <v>0.07646888653569722</v>
       </c>
       <c r="T15">
-        <v>0.5924533780776438</v>
+        <v>0.5977936825492288</v>
       </c>
       <c r="U15">
         <v>0.0612366166625341</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.583860253135859</v>
+        <v>5.185013092197582</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07219308717026569</v>
+        <v>0.07212603215165775</v>
       </c>
       <c r="C16">
-        <v>5457.088187638316</v>
+        <v>5397.954007074239</v>
       </c>
       <c r="D16">
-        <v>6208.560187638315</v>
+        <v>6224.374007074239</v>
       </c>
       <c r="E16">
-        <v>-4767.128</v>
+        <v>-4692.179999999999</v>
       </c>
       <c r="F16">
-        <v>1049.272</v>
+        <v>1124.22</v>
       </c>
       <c r="G16">
         <v>297.8</v>
@@ -2605,28 +2605,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M16">
-        <v>64.25386723873048</v>
+        <v>68.84342918435408</v>
       </c>
       <c r="N16">
-        <v>268.9032756184124</v>
+        <v>264.3137136727888</v>
       </c>
       <c r="O16">
-        <v>67.22581890460309</v>
+        <v>66.07842841819719</v>
       </c>
       <c r="P16">
-        <v>201.6774567138092</v>
+        <v>198.2352852545916</v>
       </c>
       <c r="Q16">
-        <v>1581.377456713809</v>
+        <v>1577.935285254592</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07646888653569722</v>
+        <v>0.07674930914955608</v>
       </c>
       <c r="T16">
-        <v>0.5977936825492288</v>
+        <v>0.6032596412436746</v>
       </c>
       <c r="U16">
         <v>0.0612366166625341</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.185013092197582</v>
+        <v>4.839345552717743</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07212603215165775</v>
+        <v>0.0720589771330498</v>
       </c>
       <c r="C17">
-        <v>5397.954007074239</v>
+        <v>5338.900590962729</v>
       </c>
       <c r="D17">
-        <v>6224.374007074239</v>
+        <v>6240.268590962728</v>
       </c>
       <c r="E17">
-        <v>-4692.18</v>
+        <v>-4617.232</v>
       </c>
       <c r="F17">
-        <v>1124.22</v>
+        <v>1199.168</v>
       </c>
       <c r="G17">
         <v>297.8</v>
@@ -2687,28 +2687,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M17">
-        <v>68.84342918435406</v>
+        <v>73.43299112997768</v>
       </c>
       <c r="N17">
-        <v>264.3137136727888</v>
+        <v>259.7241517271652</v>
       </c>
       <c r="O17">
-        <v>66.07842841819719</v>
+        <v>64.93103793179129</v>
       </c>
       <c r="P17">
-        <v>198.2352852545916</v>
+        <v>194.7931137953739</v>
       </c>
       <c r="Q17">
-        <v>1577.935285254592</v>
+        <v>1574.493113795374</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07674930914955608</v>
+        <v>0.07703640849231634</v>
       </c>
       <c r="T17">
-        <v>0.6032596412436746</v>
+        <v>0.6088557418117978</v>
       </c>
       <c r="U17">
         <v>0.0612366166625341</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.839345552717745</v>
+        <v>4.536886455672885</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0720589771330498</v>
+        <v>0.07231067211444187</v>
       </c>
       <c r="C18">
-        <v>5338.900590962729</v>
+        <v>5204.706854751152</v>
       </c>
       <c r="D18">
-        <v>6240.268590962728</v>
+        <v>6181.022854751151</v>
       </c>
       <c r="E18">
-        <v>-4617.232</v>
+        <v>-4542.284</v>
       </c>
       <c r="F18">
-        <v>1199.168</v>
+        <v>1274.116</v>
       </c>
       <c r="G18">
         <v>297.8</v>
@@ -2769,45 +2769,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M18">
-        <v>73.43299112997768</v>
+        <v>81.20784307560129</v>
       </c>
       <c r="N18">
-        <v>259.7241517271652</v>
+        <v>251.9492997815416</v>
       </c>
       <c r="O18">
-        <v>64.93103793179129</v>
+        <v>62.98732494538539</v>
       </c>
       <c r="P18">
-        <v>194.7931137953739</v>
+        <v>188.9619748361562</v>
       </c>
       <c r="Q18">
-        <v>1574.493113795374</v>
+        <v>1568.661974836156</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07703640849231634</v>
+        <v>0.07733042589152865</v>
       </c>
       <c r="T18">
-        <v>0.6088557418117978</v>
+        <v>0.6145866881767432</v>
       </c>
       <c r="U18">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04592746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.536886455672885</v>
+        <v>4.10252421735899</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07231067211444187</v>
+        <v>0.07273486709583393</v>
       </c>
       <c r="C19">
-        <v>5204.706854751152</v>
+        <v>5032.41443996246</v>
       </c>
       <c r="D19">
-        <v>6181.022854751151</v>
+        <v>6083.67843996246</v>
       </c>
       <c r="E19">
-        <v>-4542.284</v>
+        <v>-4467.335999999999</v>
       </c>
       <c r="F19">
-        <v>1274.116</v>
+        <v>1349.064</v>
       </c>
       <c r="G19">
         <v>297.8</v>
@@ -2851,45 +2851,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M19">
-        <v>81.20784307560129</v>
+        <v>90.7064990212249</v>
       </c>
       <c r="N19">
-        <v>251.9492997815416</v>
+        <v>242.450643835918</v>
       </c>
       <c r="O19">
-        <v>62.98732494538539</v>
+        <v>60.61266095897949</v>
       </c>
       <c r="P19">
-        <v>188.9619748361562</v>
+        <v>181.8379828769385</v>
       </c>
       <c r="Q19">
-        <v>1568.661974836156</v>
+        <v>1561.537982876938</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07733042589152865</v>
+        <v>0.07763161444681932</v>
       </c>
       <c r="T19">
-        <v>0.6145866881767432</v>
+        <v>0.6204574137213213</v>
       </c>
       <c r="U19">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04780246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.10252421735899</v>
+        <v>3.672913699151652</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07273486709583395</v>
+        <v>0.07311181207722603</v>
       </c>
       <c r="C20">
-        <v>5032.414439962458</v>
+        <v>4873.50232766325</v>
       </c>
       <c r="D20">
-        <v>6083.678439962458</v>
+        <v>5999.71432766325</v>
       </c>
       <c r="E20">
-        <v>-4467.335999999999</v>
+        <v>-4392.388</v>
       </c>
       <c r="F20">
-        <v>1349.064</v>
+        <v>1424.012</v>
       </c>
       <c r="G20">
         <v>297.8</v>
@@ -2933,45 +2933,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M20">
-        <v>90.70649902122489</v>
+        <v>99.73298256684849</v>
       </c>
       <c r="N20">
-        <v>242.450643835918</v>
+        <v>233.4241602902944</v>
       </c>
       <c r="O20">
-        <v>60.61266095897949</v>
+        <v>58.35604007257359</v>
       </c>
       <c r="P20">
-        <v>181.8379828769385</v>
+        <v>175.0681202177208</v>
       </c>
       <c r="Q20">
-        <v>1561.537982876938</v>
+        <v>1554.768120217721</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07763161444681932</v>
+        <v>0.07794023975656161</v>
       </c>
       <c r="T20">
-        <v>0.6204574137213213</v>
+        <v>0.6264730954521855</v>
       </c>
       <c r="U20">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.05042746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.672913699151652</v>
+        <v>3.340491122220636</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07311181207722603</v>
+        <v>0.07311075705861808</v>
       </c>
       <c r="C21">
-        <v>4873.50232766325</v>
+        <v>4798.78609752025</v>
       </c>
       <c r="D21">
-        <v>5999.71432766325</v>
+        <v>5999.94609752025</v>
       </c>
       <c r="E21">
-        <v>-4392.388</v>
+        <v>-4317.44</v>
       </c>
       <c r="F21">
-        <v>1424.012</v>
+        <v>1498.96</v>
       </c>
       <c r="G21">
         <v>297.8</v>
@@ -3015,28 +3015,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M21">
-        <v>99.73298256684849</v>
+        <v>104.9820869124721</v>
       </c>
       <c r="N21">
-        <v>233.4241602902944</v>
+        <v>228.1750559446707</v>
       </c>
       <c r="O21">
-        <v>58.35604007257359</v>
+        <v>57.04376398616768</v>
       </c>
       <c r="P21">
-        <v>175.0681202177208</v>
+        <v>171.1312919585031</v>
       </c>
       <c r="Q21">
-        <v>1554.768120217721</v>
+        <v>1550.831291958503</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07794023975656161</v>
+        <v>0.07825658069904745</v>
       </c>
       <c r="T21">
-        <v>0.6264730954521855</v>
+        <v>0.6326391692263211</v>
       </c>
       <c r="U21">
         <v>0.07003661666253409</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.340491122220636</v>
+        <v>3.173466566109604</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07311075705861808</v>
+        <v>0.07310970204001013</v>
       </c>
       <c r="C22">
-        <v>4798.78609752025</v>
+        <v>4724.069885284551</v>
       </c>
       <c r="D22">
-        <v>5999.94609752025</v>
+        <v>6000.177885284551</v>
       </c>
       <c r="E22">
-        <v>-4317.44</v>
+        <v>-4242.492</v>
       </c>
       <c r="F22">
-        <v>1498.96</v>
+        <v>1573.908</v>
       </c>
       <c r="G22">
         <v>297.8</v>
@@ -3097,28 +3097,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M22">
-        <v>104.9820869124721</v>
+        <v>110.2311912580957</v>
       </c>
       <c r="N22">
-        <v>228.1750559446707</v>
+        <v>222.9259515990472</v>
       </c>
       <c r="O22">
-        <v>57.04376398616768</v>
+        <v>55.73148789976179</v>
       </c>
       <c r="P22">
-        <v>171.1312919585031</v>
+        <v>167.1944636992854</v>
       </c>
       <c r="Q22">
-        <v>1550.831291958503</v>
+        <v>1546.894463699285</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07825658069904745</v>
+        <v>0.07858093027298862</v>
       </c>
       <c r="T22">
-        <v>0.6326391692263211</v>
+        <v>0.6389613461339793</v>
       </c>
       <c r="U22">
         <v>0.07003661666253409</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.173466566109604</v>
+        <v>3.022349110580576</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07310970204001013</v>
+        <v>0.07439564702140219</v>
       </c>
       <c r="C23">
-        <v>4724.069885284551</v>
+        <v>4379.294151249844</v>
       </c>
       <c r="D23">
-        <v>6000.177885284551</v>
+        <v>5730.350151249843</v>
       </c>
       <c r="E23">
-        <v>-4242.492</v>
+        <v>-4167.544</v>
       </c>
       <c r="F23">
-        <v>1573.908</v>
+        <v>1648.856</v>
       </c>
       <c r="G23">
         <v>297.8</v>
@@ -3179,45 +3179,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M23">
-        <v>110.2311912580957</v>
+        <v>128.3413724037193</v>
       </c>
       <c r="N23">
-        <v>222.9259515990472</v>
+        <v>204.8157704534235</v>
       </c>
       <c r="O23">
-        <v>55.73148789976179</v>
+        <v>51.20394261335588</v>
       </c>
       <c r="P23">
-        <v>167.1944636992854</v>
+        <v>153.6118278400676</v>
       </c>
       <c r="Q23">
-        <v>1546.894463699285</v>
+        <v>1533.311827840068</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07858093027298862</v>
+        <v>0.07891359650267188</v>
       </c>
       <c r="T23">
-        <v>0.6389613461339793</v>
+        <v>0.6454456301418336</v>
       </c>
       <c r="U23">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.05252746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.022349110580576</v>
+        <v>2.595867074018354</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07439564702140219</v>
+        <v>0.07512584200279426</v>
       </c>
       <c r="C24">
-        <v>4379.294151249844</v>
+        <v>4161.664044401446</v>
       </c>
       <c r="D24">
-        <v>5730.350151249843</v>
+        <v>5587.668044401446</v>
       </c>
       <c r="E24">
-        <v>-4167.544</v>
+        <v>-4092.596</v>
       </c>
       <c r="F24">
-        <v>1648.856</v>
+        <v>1723.804</v>
       </c>
       <c r="G24">
         <v>297.8</v>
@@ -3261,45 +3261,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M24">
-        <v>128.3413724037193</v>
+        <v>140.8979067493429</v>
       </c>
       <c r="N24">
-        <v>204.8157704534235</v>
+        <v>192.2592361077999</v>
       </c>
       <c r="O24">
-        <v>51.20394261335588</v>
+        <v>48.06480902694998</v>
       </c>
       <c r="P24">
-        <v>153.6118278400676</v>
+        <v>144.1944270808499</v>
       </c>
       <c r="Q24">
-        <v>1533.311827840068</v>
+        <v>1523.89442708085</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07891359650267188</v>
+        <v>0.07925490341364562</v>
       </c>
       <c r="T24">
-        <v>0.6454456301418336</v>
+        <v>0.6520983371109311</v>
       </c>
       <c r="U24">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.05837746249690058</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.595867074018354</v>
+        <v>2.36452868991041</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07512584200279426</v>
+        <v>0.07521253698418633</v>
       </c>
       <c r="C25">
-        <v>4161.664044401446</v>
+        <v>4070.246102437756</v>
       </c>
       <c r="D25">
-        <v>5587.668044401446</v>
+        <v>5571.198102437756</v>
       </c>
       <c r="E25">
-        <v>-4092.596</v>
+        <v>-4017.648</v>
       </c>
       <c r="F25">
-        <v>1723.804</v>
+        <v>1798.752</v>
       </c>
       <c r="G25">
         <v>297.8</v>
@@ -3343,28 +3343,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M25">
-        <v>140.8979067493429</v>
+        <v>147.0239026949665</v>
       </c>
       <c r="N25">
-        <v>192.2592361077999</v>
+        <v>186.1332401621763</v>
       </c>
       <c r="O25">
-        <v>48.06480902694998</v>
+        <v>46.53331004054408</v>
       </c>
       <c r="P25">
-        <v>144.1944270808499</v>
+        <v>139.5999301216322</v>
       </c>
       <c r="Q25">
-        <v>1523.89442708085</v>
+        <v>1519.299930121632</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07925490341364562</v>
+        <v>0.07960519208543446</v>
       </c>
       <c r="T25">
-        <v>0.6520983371109311</v>
+        <v>0.6589261153160575</v>
       </c>
       <c r="U25">
         <v>0.0817366166625341</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.36452868991041</v>
+        <v>2.266006661164142</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07521253698418633</v>
+        <v>0.07529923196557839</v>
       </c>
       <c r="C26">
-        <v>4070.246102437756</v>
+        <v>3978.924967151186</v>
       </c>
       <c r="D26">
-        <v>5571.198102437756</v>
+        <v>5554.824967151186</v>
       </c>
       <c r="E26">
-        <v>-4017.648</v>
+        <v>-3942.7</v>
       </c>
       <c r="F26">
-        <v>1798.752</v>
+        <v>1873.7</v>
       </c>
       <c r="G26">
         <v>297.8</v>
@@ -3425,28 +3425,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M26">
-        <v>147.0239026949665</v>
+        <v>153.1498986405901</v>
       </c>
       <c r="N26">
-        <v>186.1332401621763</v>
+        <v>180.0072442165527</v>
       </c>
       <c r="O26">
-        <v>46.53331004054409</v>
+        <v>45.00181105413818</v>
       </c>
       <c r="P26">
-        <v>139.5999301216323</v>
+        <v>135.0054331624145</v>
       </c>
       <c r="Q26">
-        <v>1519.299930121632</v>
+        <v>1514.705433162414</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07960519208543446</v>
+        <v>0.079964821788471</v>
       </c>
       <c r="T26">
-        <v>0.6589261153160575</v>
+        <v>0.6659359676066539</v>
       </c>
       <c r="U26">
         <v>0.0817366166625341</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.266006661164143</v>
+        <v>2.175366394717577</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07529923196557839</v>
+        <v>0.07538592694697045</v>
       </c>
       <c r="C27">
-        <v>3978.924967151186</v>
+        <v>3887.699787530399</v>
       </c>
       <c r="D27">
-        <v>5554.824967151186</v>
+        <v>5538.547787530399</v>
       </c>
       <c r="E27">
-        <v>-3942.7</v>
+        <v>-3867.751999999999</v>
       </c>
       <c r="F27">
-        <v>1873.7</v>
+        <v>1948.648</v>
       </c>
       <c r="G27">
         <v>297.8</v>
@@ -3507,28 +3507,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M27">
-        <v>153.1498986405901</v>
+        <v>159.2758945862137</v>
       </c>
       <c r="N27">
-        <v>180.0072442165527</v>
+        <v>173.8812482709291</v>
       </c>
       <c r="O27">
-        <v>45.00181105413818</v>
+        <v>43.47031206773228</v>
       </c>
       <c r="P27">
-        <v>135.0054331624145</v>
+        <v>130.4109362031969</v>
       </c>
       <c r="Q27">
-        <v>1514.705433162414</v>
+        <v>1510.110936203197</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.079964821788471</v>
+        <v>0.08033417121321122</v>
       </c>
       <c r="T27">
-        <v>0.6659359676066539</v>
+        <v>0.6731352753645636</v>
       </c>
       <c r="U27">
         <v>0.0817366166625341</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.175366394717577</v>
+        <v>2.091698456459208</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07538592694697045</v>
+        <v>0.07547262192836252</v>
       </c>
       <c r="C28">
-        <v>3887.699787530399</v>
+        <v>3796.569722509711</v>
       </c>
       <c r="D28">
-        <v>5538.547787530399</v>
+        <v>5522.365722509711</v>
       </c>
       <c r="E28">
-        <v>-3867.751999999999</v>
+        <v>-3792.804</v>
       </c>
       <c r="F28">
-        <v>1948.648</v>
+        <v>2023.596</v>
       </c>
       <c r="G28">
         <v>297.8</v>
@@ -3589,28 +3589,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M28">
-        <v>159.2758945862137</v>
+        <v>165.4018905318374</v>
       </c>
       <c r="N28">
-        <v>173.8812482709291</v>
+        <v>167.7552523253055</v>
       </c>
       <c r="O28">
-        <v>43.47031206773228</v>
+        <v>41.93881308132637</v>
       </c>
       <c r="P28">
-        <v>130.4109362031969</v>
+        <v>125.8164392439791</v>
       </c>
       <c r="Q28">
-        <v>1510.110936203197</v>
+        <v>1505.516439243979</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08033417121321122</v>
+        <v>0.0807136398002731</v>
       </c>
       <c r="T28">
-        <v>0.6731352753645636</v>
+        <v>0.6805318244309093</v>
       </c>
       <c r="U28">
         <v>0.0817366166625341</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.091698456459208</v>
+        <v>2.014228143257015</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07547262192836252</v>
+        <v>0.07854131690975458</v>
       </c>
       <c r="C29">
-        <v>3796.569722509711</v>
+        <v>3204.035456056627</v>
       </c>
       <c r="D29">
-        <v>5522.365722509711</v>
+        <v>5004.779456056627</v>
       </c>
       <c r="E29">
-        <v>-3792.804</v>
+        <v>-3717.856</v>
       </c>
       <c r="F29">
-        <v>2023.596</v>
+        <v>2098.544</v>
       </c>
       <c r="G29">
         <v>297.8</v>
@@ -3671,45 +3671,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M29">
-        <v>165.4018905318374</v>
+        <v>201.3272112774609</v>
       </c>
       <c r="N29">
-        <v>167.7552523253055</v>
+        <v>131.8299315796819</v>
       </c>
       <c r="O29">
-        <v>41.93881308132637</v>
+        <v>32.95748289492047</v>
       </c>
       <c r="P29">
-        <v>125.8164392439791</v>
+        <v>98.87244868476142</v>
       </c>
       <c r="Q29">
-        <v>1505.516439243979</v>
+        <v>1478.572448684761</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0807136398002731</v>
+        <v>0.08110364918142003</v>
       </c>
       <c r="T29">
-        <v>0.6805318244309093</v>
+        <v>0.6881338331935424</v>
       </c>
       <c r="U29">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.06130246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.014228143257015</v>
+        <v>1.654804339379635</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07854131690975458</v>
+        <v>0.07873451189114664</v>
       </c>
       <c r="C30">
-        <v>3204.035456056627</v>
+        <v>3099.729247345961</v>
       </c>
       <c r="D30">
-        <v>5004.779456056627</v>
+        <v>4975.421247345961</v>
       </c>
       <c r="E30">
-        <v>-3717.856</v>
+        <v>-3642.907999999999</v>
       </c>
       <c r="F30">
-        <v>2098.544</v>
+        <v>2173.492</v>
       </c>
       <c r="G30">
         <v>297.8</v>
@@ -3753,28 +3753,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M30">
-        <v>201.3272112774609</v>
+        <v>208.5174688230846</v>
       </c>
       <c r="N30">
-        <v>131.8299315796819</v>
+        <v>124.6396740340583</v>
       </c>
       <c r="O30">
-        <v>32.95748289492047</v>
+        <v>31.15991850851456</v>
       </c>
       <c r="P30">
-        <v>98.87244868476142</v>
+        <v>93.47975552554369</v>
       </c>
       <c r="Q30">
-        <v>1478.572448684761</v>
+        <v>1473.179755525544</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08110364918142003</v>
+        <v>0.08150464474231757</v>
       </c>
       <c r="T30">
-        <v>0.6881338331935424</v>
+        <v>0.6959499830480804</v>
       </c>
       <c r="U30">
         <v>0.0959366166625341</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.654804339379635</v>
+        <v>1.597742120780336</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07873451189114664</v>
+        <v>0.07892770687253871</v>
       </c>
       <c r="C31">
-        <v>3099.729247345962</v>
+        <v>2995.765462492603</v>
       </c>
       <c r="D31">
-        <v>4975.421247345961</v>
+        <v>4946.405462492602</v>
       </c>
       <c r="E31">
-        <v>-3642.908</v>
+        <v>-3567.96</v>
       </c>
       <c r="F31">
-        <v>2173.492</v>
+        <v>2248.44</v>
       </c>
       <c r="G31">
         <v>297.8</v>
@@ -3835,28 +3835,28 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M31">
-        <v>208.5174688230845</v>
+        <v>215.7077263687081</v>
       </c>
       <c r="N31">
-        <v>124.6396740340583</v>
+        <v>117.4494164884347</v>
       </c>
       <c r="O31">
-        <v>31.15991850851458</v>
+        <v>29.36235412210868</v>
       </c>
       <c r="P31">
-        <v>93.47975552554374</v>
+        <v>88.08706236632602</v>
       </c>
       <c r="Q31">
-        <v>1473.179755525544</v>
+        <v>1467.787062366326</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08150464474231757</v>
+        <v>0.08191709731924077</v>
       </c>
       <c r="T31">
-        <v>0.6959499830480804</v>
+        <v>0.7039894514698912</v>
       </c>
       <c r="U31">
         <v>0.0959366166625341</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.597742120780337</v>
+        <v>1.544484050087659</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07892770687253871</v>
+        <v>0.0931806305668422</v>
       </c>
       <c r="C32">
-        <v>2995.765462492603</v>
+        <v>1432.852047626835</v>
       </c>
       <c r="D32">
-        <v>4946.405462492602</v>
+        <v>3458.440047626834</v>
       </c>
       <c r="E32">
-        <v>-3567.96</v>
+        <v>-3493.012</v>
       </c>
       <c r="F32">
-        <v>2248.44</v>
+        <v>2323.388</v>
       </c>
       <c r="G32">
         <v>297.8</v>
@@ -3917,45 +3917,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M32">
-        <v>215.7077263687081</v>
+        <v>354.8664223143318</v>
       </c>
       <c r="N32">
-        <v>117.4494164884347</v>
+        <v>-21.70927945718893</v>
       </c>
       <c r="O32">
-        <v>29.36235412210868</v>
+        <v>-5.427319864297232</v>
       </c>
       <c r="P32">
-        <v>88.08706236632602</v>
+        <v>-16.2819595928917</v>
       </c>
       <c r="Q32">
-        <v>1467.787062366326</v>
+        <v>1363.418040407108</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08191709731924077</v>
+        <v>0.08252930792834198</v>
       </c>
       <c r="T32">
-        <v>0.7039894514698912</v>
+        <v>0.7159225757482814</v>
       </c>
       <c r="U32">
-        <v>0.0959366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V32">
-        <v>0.25</v>
+        <v>0.2347060202853178</v>
       </c>
       <c r="W32">
-        <v>0.07195246249690057</v>
+        <v>0.1168884132138266</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.544484050087659</v>
+        <v>0.9388240811412712</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0931806305668422</v>
+        <v>0.09424999673346754</v>
       </c>
       <c r="C33">
-        <v>1432.852047626835</v>
+        <v>1281.570940803742</v>
       </c>
       <c r="D33">
-        <v>3458.440047626834</v>
+        <v>3382.106940803742</v>
       </c>
       <c r="E33">
-        <v>-3493.012</v>
+        <v>-3418.064</v>
       </c>
       <c r="F33">
-        <v>2323.388</v>
+        <v>2398.336</v>
       </c>
       <c r="G33">
         <v>297.8</v>
@@ -3999,37 +3999,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M33">
-        <v>354.8664223143318</v>
+        <v>366.3137262599553</v>
       </c>
       <c r="N33">
-        <v>-21.70927945718893</v>
+        <v>-33.15658340281249</v>
       </c>
       <c r="O33">
-        <v>-5.427319864297232</v>
+        <v>-8.289145850703122</v>
       </c>
       <c r="P33">
-        <v>-16.2819595928917</v>
+        <v>-24.86743755210937</v>
       </c>
       <c r="Q33">
-        <v>1363.418040407108</v>
+        <v>1354.832562447891</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08252930792834198</v>
+        <v>0.08306944480964112</v>
       </c>
       <c r="T33">
-        <v>0.7159225757482814</v>
+        <v>0.7264508489210503</v>
       </c>
       <c r="U33">
         <v>0.1527366166625341</v>
       </c>
       <c r="V33">
-        <v>0.2347060202853178</v>
+        <v>0.2273714571514017</v>
       </c>
       <c r="W33">
-        <v>0.1168884132138266</v>
+        <v>0.1180086695715987</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9388240811412712</v>
+        <v>0.9094858286056067</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09424999673346754</v>
+        <v>0.09531936290009288</v>
       </c>
       <c r="C34">
-        <v>1281.570940803742</v>
+        <v>1133.58664706747</v>
       </c>
       <c r="D34">
-        <v>3382.106940803742</v>
+        <v>3309.070647067469</v>
       </c>
       <c r="E34">
-        <v>-3418.064</v>
+        <v>-3343.116</v>
       </c>
       <c r="F34">
-        <v>2398.336</v>
+        <v>2473.284</v>
       </c>
       <c r="G34">
         <v>297.8</v>
@@ -4081,37 +4081,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M34">
-        <v>366.3137262599553</v>
+        <v>377.7610302055789</v>
       </c>
       <c r="N34">
-        <v>-33.15658340281249</v>
+        <v>-44.6038873484361</v>
       </c>
       <c r="O34">
-        <v>-8.289145850703122</v>
+        <v>-11.15097183710903</v>
       </c>
       <c r="P34">
-        <v>-24.86743755210937</v>
+        <v>-33.45291551132708</v>
       </c>
       <c r="Q34">
-        <v>1354.832562447891</v>
+        <v>1346.247084488673</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08306944480964112</v>
+        <v>0.08362570517993428</v>
       </c>
       <c r="T34">
-        <v>0.7264508489210503</v>
+        <v>0.7372933989049466</v>
       </c>
       <c r="U34">
         <v>0.1527366166625341</v>
       </c>
       <c r="V34">
-        <v>0.2273714571514017</v>
+        <v>0.2204814129952986</v>
       </c>
       <c r="W34">
-        <v>0.1180086695715987</v>
+        <v>0.1190610316046573</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.9094858286056067</v>
+        <v>0.8819256519811943</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09531936290009288</v>
+        <v>0.09638872906671822</v>
       </c>
       <c r="C35">
-        <v>1133.58664706747</v>
+        <v>988.6900980877131</v>
       </c>
       <c r="D35">
-        <v>3309.070647067469</v>
+        <v>3239.122098087713</v>
       </c>
       <c r="E35">
-        <v>-3343.116</v>
+        <v>-3268.168</v>
       </c>
       <c r="F35">
-        <v>2473.284</v>
+        <v>2548.232</v>
       </c>
       <c r="G35">
         <v>297.8</v>
@@ -4163,37 +4163,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M35">
-        <v>377.7610302055789</v>
+        <v>389.2083341512026</v>
       </c>
       <c r="N35">
-        <v>-44.6038873484361</v>
+        <v>-56.05119129405978</v>
       </c>
       <c r="O35">
-        <v>-11.15097183710903</v>
+        <v>-14.01279782351494</v>
       </c>
       <c r="P35">
-        <v>-33.45291551132708</v>
+        <v>-42.03839347054483</v>
       </c>
       <c r="Q35">
-        <v>1346.247084488673</v>
+        <v>1337.661606529455</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08362570517993428</v>
+        <v>0.08419882192508479</v>
       </c>
       <c r="T35">
-        <v>0.7372933989049466</v>
+        <v>0.748464511009567</v>
       </c>
       <c r="U35">
         <v>0.1527366166625341</v>
       </c>
       <c r="V35">
-        <v>0.2204814129952986</v>
+        <v>0.2139966655542603</v>
       </c>
       <c r="W35">
-        <v>0.1190610316046573</v>
+        <v>0.1200514899887125</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8819256519811943</v>
+        <v>0.8559866622170413</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09638872906671822</v>
+        <v>0.09745809523334356</v>
       </c>
       <c r="C36">
-        <v>988.6900980877131</v>
+        <v>846.6895370976649</v>
       </c>
       <c r="D36">
-        <v>3239.122098087713</v>
+        <v>3172.069537097665</v>
       </c>
       <c r="E36">
-        <v>-3268.168</v>
+        <v>-3193.22</v>
       </c>
       <c r="F36">
-        <v>2548.232</v>
+        <v>2623.18</v>
       </c>
       <c r="G36">
         <v>297.8</v>
@@ -4245,37 +4245,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M36">
-        <v>389.2083341512026</v>
+        <v>400.6556380968262</v>
       </c>
       <c r="N36">
-        <v>-56.05119129405978</v>
+        <v>-67.49849523968334</v>
       </c>
       <c r="O36">
-        <v>-14.01279782351494</v>
+        <v>-16.87462380992083</v>
       </c>
       <c r="P36">
-        <v>-42.03839347054483</v>
+        <v>-50.6238714297625</v>
       </c>
       <c r="Q36">
-        <v>1337.661606529455</v>
+        <v>1329.076128570238</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08419882192508479</v>
+        <v>0.08478957303162457</v>
       </c>
       <c r="T36">
-        <v>0.748464511009567</v>
+        <v>0.7599793496404833</v>
       </c>
       <c r="U36">
         <v>0.1527366166625341</v>
       </c>
       <c r="V36">
-        <v>0.2139966655542603</v>
+        <v>0.2078824751098529</v>
       </c>
       <c r="W36">
-        <v>0.1200514899887125</v>
+        <v>0.1209853507508217</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8559866622170413</v>
+        <v>0.8315299004394117</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09745809523334356</v>
+        <v>0.09852746139996892</v>
       </c>
       <c r="C37">
-        <v>846.6895370976649</v>
+        <v>707.4087634140606</v>
       </c>
       <c r="D37">
-        <v>3172.069537097665</v>
+        <v>3107.736763414061</v>
       </c>
       <c r="E37">
-        <v>-3193.22</v>
+        <v>-3118.271999999999</v>
       </c>
       <c r="F37">
-        <v>2623.18</v>
+        <v>2698.128</v>
       </c>
       <c r="G37">
         <v>297.8</v>
@@ -4327,37 +4327,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M37">
-        <v>400.6556380968262</v>
+        <v>412.1029420424499</v>
       </c>
       <c r="N37">
-        <v>-67.49849523968334</v>
+        <v>-78.94579918530701</v>
       </c>
       <c r="O37">
-        <v>-16.87462380992083</v>
+        <v>-19.73644979632675</v>
       </c>
       <c r="P37">
-        <v>-50.6238714297625</v>
+        <v>-59.20934938898026</v>
       </c>
       <c r="Q37">
-        <v>1329.076128570238</v>
+        <v>1320.49065061102</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08478957303162457</v>
+        <v>0.08539878511024371</v>
       </c>
       <c r="T37">
-        <v>0.7599793496404833</v>
+        <v>0.7718540269786159</v>
       </c>
       <c r="U37">
         <v>0.1527366166625341</v>
       </c>
       <c r="V37">
-        <v>0.2078824751098529</v>
+        <v>0.202107961912357</v>
       </c>
       <c r="W37">
-        <v>0.1209853507508217</v>
+        <v>0.1218673303594804</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8315299004394117</v>
+        <v>0.8084318476494279</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0985274613999689</v>
+        <v>0.120096262824777</v>
       </c>
       <c r="C38">
-        <v>707.4087634140619</v>
+        <v>-269.740162744768</v>
       </c>
       <c r="D38">
-        <v>3107.736763414061</v>
+        <v>2205.535837255231</v>
       </c>
       <c r="E38">
-        <v>-3118.272</v>
+        <v>-3043.324</v>
       </c>
       <c r="F38">
-        <v>2698.128</v>
+        <v>2773.076</v>
       </c>
       <c r="G38">
         <v>297.8</v>
@@ -4409,45 +4409,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M38">
-        <v>412.1029420424497</v>
+        <v>573.2963499880733</v>
       </c>
       <c r="N38">
-        <v>-78.9457991853069</v>
+        <v>-240.1392071309305</v>
       </c>
       <c r="O38">
-        <v>-19.73644979632672</v>
+        <v>-60.03480178273261</v>
       </c>
       <c r="P38">
-        <v>-59.20934938898017</v>
+        <v>-180.1044053481978</v>
       </c>
       <c r="Q38">
-        <v>1320.49065061102</v>
+        <v>1199.595594651802</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08539878511024369</v>
+        <v>0.08685183766466456</v>
       </c>
       <c r="T38">
-        <v>0.7718540269786158</v>
+        <v>0.800176725829576</v>
       </c>
       <c r="U38">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V38">
-        <v>0.202107961912357</v>
+        <v>0.1452813814635632</v>
       </c>
       <c r="W38">
-        <v>0.1218673303594804</v>
+        <v>0.176701635394698</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8084318476494281</v>
+        <v>0.5811255258542527</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.120096262824777</v>
+        <v>0.1217056289914023</v>
       </c>
       <c r="C39">
-        <v>-269.740162744768</v>
+        <v>-391.4503700134851</v>
       </c>
       <c r="D39">
-        <v>2205.535837255231</v>
+        <v>2158.773629986515</v>
       </c>
       <c r="E39">
-        <v>-3043.324</v>
+        <v>-2968.376</v>
       </c>
       <c r="F39">
-        <v>2773.076</v>
+        <v>2848.024</v>
       </c>
       <c r="G39">
         <v>297.8</v>
@@ -4491,37 +4491,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M39">
-        <v>573.2963499880733</v>
+        <v>588.790845933697</v>
       </c>
       <c r="N39">
-        <v>-240.1392071309305</v>
+        <v>-255.6337030765542</v>
       </c>
       <c r="O39">
-        <v>-60.03480178273261</v>
+        <v>-63.90842576913855</v>
       </c>
       <c r="P39">
-        <v>-180.1044053481978</v>
+        <v>-191.7252773074156</v>
       </c>
       <c r="Q39">
-        <v>1199.595594651802</v>
+        <v>1187.974722692584</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08685183766466456</v>
+        <v>0.08751396407861078</v>
       </c>
       <c r="T39">
-        <v>0.800176725829576</v>
+        <v>0.8130828020526338</v>
       </c>
       <c r="U39">
         <v>0.2067366166625341</v>
       </c>
       <c r="V39">
-        <v>0.1452813814635632</v>
+        <v>0.141458187214522</v>
       </c>
       <c r="W39">
-        <v>0.176701635394698</v>
+        <v>0.1774920296385885</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5811255258542527</v>
+        <v>0.5658327488580881</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1217056289914023</v>
+        <v>0.1233149951580276</v>
       </c>
       <c r="C40">
-        <v>-391.4503700134851</v>
+        <v>-511.2188235840531</v>
       </c>
       <c r="D40">
-        <v>2158.773629986515</v>
+        <v>2113.953176415946</v>
       </c>
       <c r="E40">
-        <v>-2968.376</v>
+        <v>-2893.428</v>
       </c>
       <c r="F40">
-        <v>2848.024</v>
+        <v>2922.972</v>
       </c>
       <c r="G40">
         <v>297.8</v>
@@ -4573,37 +4573,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M40">
-        <v>588.790845933697</v>
+        <v>604.2853418793205</v>
       </c>
       <c r="N40">
-        <v>-255.6337030765542</v>
+        <v>-271.1281990221777</v>
       </c>
       <c r="O40">
-        <v>-63.90842576913855</v>
+        <v>-67.78204975554442</v>
       </c>
       <c r="P40">
-        <v>-191.7252773074156</v>
+        <v>-203.3461492666333</v>
       </c>
       <c r="Q40">
-        <v>1187.974722692584</v>
+        <v>1176.353850733367</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08751396407861078</v>
+        <v>0.08819779955530932</v>
       </c>
       <c r="T40">
-        <v>0.8130828020526338</v>
+        <v>0.8264120283157916</v>
       </c>
       <c r="U40">
         <v>0.2067366166625341</v>
       </c>
       <c r="V40">
-        <v>0.141458187214522</v>
+        <v>0.1378310542090215</v>
       </c>
       <c r="W40">
-        <v>0.1774920296385885</v>
+        <v>0.1782418908443306</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5658327488580881</v>
+        <v>0.5513242168360859</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1233149951580276</v>
+        <v>0.124924361324653</v>
       </c>
       <c r="C41">
-        <v>-511.2188235840531</v>
+        <v>-629.1640075486089</v>
       </c>
       <c r="D41">
-        <v>2113.953176415946</v>
+        <v>2070.955992451391</v>
       </c>
       <c r="E41">
-        <v>-2893.428</v>
+        <v>-2818.48</v>
       </c>
       <c r="F41">
-        <v>2922.972</v>
+        <v>2997.92</v>
       </c>
       <c r="G41">
         <v>297.8</v>
@@ -4655,37 +4655,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M41">
-        <v>604.2853418793205</v>
+        <v>619.7798378249443</v>
       </c>
       <c r="N41">
-        <v>-271.1281990221777</v>
+        <v>-286.6226949678014</v>
       </c>
       <c r="O41">
-        <v>-67.78204975554442</v>
+        <v>-71.65567374195035</v>
       </c>
       <c r="P41">
-        <v>-203.3461492666333</v>
+        <v>-214.9670212258511</v>
       </c>
       <c r="Q41">
-        <v>1176.353850733367</v>
+        <v>1164.732978774149</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08819779955530932</v>
+        <v>0.0889044295478978</v>
       </c>
       <c r="T41">
-        <v>0.8264120283157916</v>
+        <v>0.8401855621210549</v>
       </c>
       <c r="U41">
         <v>0.2067366166625341</v>
       </c>
       <c r="V41">
-        <v>0.1378310542090215</v>
+        <v>0.1343852778537959</v>
       </c>
       <c r="W41">
-        <v>0.1782418908443306</v>
+        <v>0.1789542589897858</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5513242168360859</v>
+        <v>0.5375411114151837</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.124924361324653</v>
+        <v>0.1265337274912783</v>
       </c>
       <c r="C42">
-        <v>-629.1640075486089</v>
+        <v>-745.394958434053</v>
       </c>
       <c r="D42">
-        <v>2070.955992451391</v>
+        <v>2029.673041565947</v>
       </c>
       <c r="E42">
-        <v>-2818.48</v>
+        <v>-2743.532</v>
       </c>
       <c r="F42">
-        <v>2997.92</v>
+        <v>3072.868</v>
       </c>
       <c r="G42">
         <v>297.8</v>
@@ -4737,37 +4737,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M42">
-        <v>619.7798378249443</v>
+        <v>635.2743337705678</v>
       </c>
       <c r="N42">
-        <v>-286.6226949678014</v>
+        <v>-302.1171909134249</v>
       </c>
       <c r="O42">
-        <v>-71.65567374195035</v>
+        <v>-75.52929772835623</v>
       </c>
       <c r="P42">
-        <v>-214.9670212258511</v>
+        <v>-226.5878931850687</v>
       </c>
       <c r="Q42">
-        <v>1164.732978774149</v>
+        <v>1153.112106814931</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0889044295478978</v>
+        <v>0.08963501309955708</v>
       </c>
       <c r="T42">
-        <v>0.8401855621210549</v>
+        <v>0.8544259953773439</v>
       </c>
       <c r="U42">
         <v>0.2067366166625341</v>
       </c>
       <c r="V42">
-        <v>0.1343852778537959</v>
+        <v>0.1311075881500448</v>
       </c>
       <c r="W42">
-        <v>0.1789542589897858</v>
+        <v>0.1796318774696089</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5375411114151837</v>
+        <v>0.5244303526001792</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1265337274912783</v>
+        <v>0.1281430936579037</v>
       </c>
       <c r="C43">
-        <v>-745.394958434053</v>
+        <v>-860.0121884483942</v>
       </c>
       <c r="D43">
-        <v>2029.673041565947</v>
+        <v>1990.003811551606</v>
       </c>
       <c r="E43">
-        <v>-2743.532</v>
+        <v>-2668.584</v>
       </c>
       <c r="F43">
-        <v>3072.868</v>
+        <v>3147.816</v>
       </c>
       <c r="G43">
         <v>297.8</v>
@@ -4819,37 +4819,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M43">
-        <v>635.2743337705678</v>
+        <v>650.7688297161914</v>
       </c>
       <c r="N43">
-        <v>-302.1171909134249</v>
+        <v>-317.6116868590485</v>
       </c>
       <c r="O43">
-        <v>-75.52929772835623</v>
+        <v>-79.40292171476213</v>
       </c>
       <c r="P43">
-        <v>-226.5878931850687</v>
+        <v>-238.2087651442864</v>
       </c>
       <c r="Q43">
-        <v>1153.112106814931</v>
+        <v>1141.491234855714</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08963501309955708</v>
+        <v>0.09039078918748049</v>
       </c>
       <c r="T43">
-        <v>0.8544259953773439</v>
+        <v>0.8691574780562636</v>
       </c>
       <c r="U43">
         <v>0.2067366166625341</v>
       </c>
       <c r="V43">
-        <v>0.1311075881500448</v>
+        <v>0.1279859789083771</v>
       </c>
       <c r="W43">
-        <v>0.1796318774696089</v>
+        <v>0.1802772284027738</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5244303526001792</v>
+        <v>0.5119439156335084</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1281430936579037</v>
+        <v>0.129752459824529</v>
       </c>
       <c r="C44">
-        <v>-860.0121884483942</v>
+        <v>-973.1085025354441</v>
       </c>
       <c r="D44">
-        <v>1990.003811551606</v>
+        <v>1951.855497464556</v>
       </c>
       <c r="E44">
-        <v>-2668.584</v>
+        <v>-2593.636</v>
       </c>
       <c r="F44">
-        <v>3147.816</v>
+        <v>3222.764</v>
       </c>
       <c r="G44">
         <v>297.8</v>
@@ -4901,37 +4901,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M44">
-        <v>650.7688297161914</v>
+        <v>666.263325661815</v>
       </c>
       <c r="N44">
-        <v>-317.6116868590485</v>
+        <v>-333.1061828046721</v>
       </c>
       <c r="O44">
-        <v>-79.40292171476213</v>
+        <v>-83.27654570116803</v>
       </c>
       <c r="P44">
-        <v>-238.2087651442864</v>
+        <v>-249.8296371035041</v>
       </c>
       <c r="Q44">
-        <v>1141.491234855714</v>
+        <v>1129.870362896496</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09039078918748049</v>
+        <v>0.09117308373462926</v>
       </c>
       <c r="T44">
-        <v>0.8691574780562636</v>
+        <v>0.8844058548642683</v>
       </c>
       <c r="U44">
         <v>0.2067366166625341</v>
       </c>
       <c r="V44">
-        <v>0.1279859789083771</v>
+        <v>0.1250095607942288</v>
       </c>
       <c r="W44">
-        <v>0.1802772284027738</v>
+        <v>0.1808925630134659</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5119439156335084</v>
+        <v>0.5000382431769151</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.129752459824529</v>
+        <v>0.1469745450664905</v>
       </c>
       <c r="C45">
-        <v>-973.1085025354441</v>
+        <v>-1380.304319762934</v>
       </c>
       <c r="D45">
-        <v>1951.855497464556</v>
+        <v>1619.607680237066</v>
       </c>
       <c r="E45">
-        <v>-2593.636</v>
+        <v>-2518.688</v>
       </c>
       <c r="F45">
-        <v>3222.764</v>
+        <v>3297.712</v>
       </c>
       <c r="G45">
         <v>297.8</v>
@@ -4983,45 +4983,45 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M45">
-        <v>666.263325661815</v>
+        <v>797.1777416074385</v>
       </c>
       <c r="N45">
-        <v>-333.1061828046721</v>
+        <v>-464.0205987502957</v>
       </c>
       <c r="O45">
-        <v>-83.27654570116803</v>
+        <v>-116.0051496875739</v>
       </c>
       <c r="P45">
-        <v>-249.8296371035041</v>
+        <v>-348.0154490627218</v>
       </c>
       <c r="Q45">
-        <v>1129.870362896496</v>
+        <v>1031.684550937278</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09117308373462926</v>
+        <v>0.09236317286441928</v>
       </c>
       <c r="T45">
-        <v>0.8844058548642683</v>
+        <v>0.9076029071156079</v>
       </c>
       <c r="U45">
-        <v>0.2067366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V45">
-        <v>0.1250095607942288</v>
+        <v>0.1044801947760611</v>
       </c>
       <c r="W45">
-        <v>0.1808925630134659</v>
+        <v>0.2164799278691265</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.5000382431769151</v>
+        <v>0.4179207791042445</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1469745450664905</v>
+        <v>0.1489339112331158</v>
       </c>
       <c r="C46">
-        <v>-1380.304319762934</v>
+        <v>-1486.022068082574</v>
       </c>
       <c r="D46">
-        <v>1619.607680237066</v>
+        <v>1588.837931917426</v>
       </c>
       <c r="E46">
-        <v>-2518.688</v>
+        <v>-2443.74</v>
       </c>
       <c r="F46">
-        <v>3297.712</v>
+        <v>3372.66</v>
       </c>
       <c r="G46">
         <v>297.8</v>
@@ -5065,37 +5065,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M46">
-        <v>797.1777416074385</v>
+        <v>815.2954175530622</v>
       </c>
       <c r="N46">
-        <v>-464.0205987502957</v>
+        <v>-482.1382746959193</v>
       </c>
       <c r="O46">
-        <v>-116.0051496875739</v>
+        <v>-120.5345686739798</v>
       </c>
       <c r="P46">
-        <v>-348.0154490627218</v>
+        <v>-361.6037060219395</v>
       </c>
       <c r="Q46">
-        <v>1031.684550937278</v>
+        <v>1018.096293978061</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09236317286441928</v>
+        <v>0.09320977600740871</v>
       </c>
       <c r="T46">
-        <v>0.9076029071156079</v>
+        <v>0.9241047781540734</v>
       </c>
       <c r="U46">
         <v>0.2417366166625341</v>
       </c>
       <c r="V46">
-        <v>0.1044801947760611</v>
+        <v>0.1021584126699264</v>
       </c>
       <c r="W46">
-        <v>0.2164799278691265</v>
+        <v>0.2170411876200911</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4179207791042445</v>
+        <v>0.4086336506797057</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1489339112331158</v>
+        <v>0.1508932773997411</v>
       </c>
       <c r="C47">
-        <v>-1486.022068082574</v>
+        <v>-1590.592469867691</v>
       </c>
       <c r="D47">
-        <v>1588.837931917426</v>
+        <v>1559.215530132309</v>
       </c>
       <c r="E47">
-        <v>-2443.74</v>
+        <v>-2368.792</v>
       </c>
       <c r="F47">
-        <v>3372.66</v>
+        <v>3447.608</v>
       </c>
       <c r="G47">
         <v>297.8</v>
@@ -5147,37 +5147,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M47">
-        <v>815.2954175530622</v>
+        <v>833.4130934986858</v>
       </c>
       <c r="N47">
-        <v>-482.1382746959193</v>
+        <v>-500.255950641543</v>
       </c>
       <c r="O47">
-        <v>-120.5345686739798</v>
+        <v>-125.0639876603857</v>
       </c>
       <c r="P47">
-        <v>-361.6037060219395</v>
+        <v>-375.1919629811572</v>
       </c>
       <c r="Q47">
-        <v>1018.096293978061</v>
+        <v>1004.508037018843</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09320977600740871</v>
+        <v>0.09408773482236073</v>
       </c>
       <c r="T47">
-        <v>0.9241047781540734</v>
+        <v>0.9412178296013712</v>
       </c>
       <c r="U47">
         <v>0.2417366166625341</v>
       </c>
       <c r="V47">
-        <v>0.1021584126699264</v>
+        <v>0.09993757761188456</v>
       </c>
       <c r="W47">
-        <v>0.2170411876200911</v>
+        <v>0.2175780447731877</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4086336506797057</v>
+        <v>0.3997503104475382</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1508932773997411</v>
+        <v>0.1528526435663665</v>
       </c>
       <c r="C48">
-        <v>-1590.592469867691</v>
+        <v>-1694.078524178551</v>
       </c>
       <c r="D48">
-        <v>1559.215530132309</v>
+        <v>1530.677475821449</v>
       </c>
       <c r="E48">
-        <v>-2368.792</v>
+        <v>-2293.844</v>
       </c>
       <c r="F48">
-        <v>3447.608</v>
+        <v>3522.556</v>
       </c>
       <c r="G48">
         <v>297.8</v>
@@ -5229,37 +5229,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M48">
-        <v>833.4130934986858</v>
+        <v>851.5307694443095</v>
       </c>
       <c r="N48">
-        <v>-500.255950641543</v>
+        <v>-518.3736265871667</v>
       </c>
       <c r="O48">
-        <v>-125.0639876603857</v>
+        <v>-129.5934066467917</v>
       </c>
       <c r="P48">
-        <v>-375.1919629811572</v>
+        <v>-388.780219940375</v>
       </c>
       <c r="Q48">
-        <v>1004.508037018843</v>
+        <v>990.9197800596251</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09408773482236073</v>
+        <v>0.09499882415863169</v>
       </c>
       <c r="T48">
-        <v>0.9412178296013712</v>
+        <v>0.958976656574982</v>
       </c>
       <c r="U48">
         <v>0.2417366166625341</v>
       </c>
       <c r="V48">
-        <v>0.09993757761188456</v>
+        <v>0.09781124617333381</v>
       </c>
       <c r="W48">
-        <v>0.2175780447731877</v>
+        <v>0.2180920569410461</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3997503104475382</v>
+        <v>0.3912449846933352</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1528526435663665</v>
+        <v>0.1548120097329918</v>
       </c>
       <c r="C49">
-        <v>-1694.078524178551</v>
+        <v>-1796.538700731263</v>
       </c>
       <c r="D49">
-        <v>1530.677475821449</v>
+        <v>1503.165299268737</v>
       </c>
       <c r="E49">
-        <v>-2293.844</v>
+        <v>-2218.896</v>
       </c>
       <c r="F49">
-        <v>3522.556</v>
+        <v>3597.504</v>
       </c>
       <c r="G49">
         <v>297.8</v>
@@ -5311,37 +5311,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M49">
-        <v>851.5307694443095</v>
+        <v>869.648445389933</v>
       </c>
       <c r="N49">
-        <v>-518.3736265871667</v>
+        <v>-536.4913025327902</v>
       </c>
       <c r="O49">
-        <v>-129.5934066467917</v>
+        <v>-134.1228256331976</v>
       </c>
       <c r="P49">
-        <v>-388.780219940375</v>
+        <v>-402.3684768995927</v>
       </c>
       <c r="Q49">
-        <v>990.9197800596251</v>
+        <v>977.3315231004074</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09499882415863169</v>
+        <v>0.09594495539245153</v>
       </c>
       <c r="T49">
-        <v>0.958976656574982</v>
+        <v>0.9774185153552701</v>
       </c>
       <c r="U49">
         <v>0.2417366166625341</v>
       </c>
       <c r="V49">
-        <v>0.09781124617333381</v>
+        <v>0.09577351187805602</v>
       </c>
       <c r="W49">
-        <v>0.2180920569410461</v>
+        <v>0.2185846519352438</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3912449846933352</v>
+        <v>0.3830940475122241</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1548120097329918</v>
+        <v>0.1567713758996171</v>
       </c>
       <c r="C50">
-        <v>-1796.538700731262</v>
+        <v>-1898.027339759624</v>
       </c>
       <c r="D50">
-        <v>1503.165299268737</v>
+        <v>1476.624660240376</v>
       </c>
       <c r="E50">
-        <v>-2218.896</v>
+        <v>-2143.948</v>
       </c>
       <c r="F50">
-        <v>3597.503999999999</v>
+        <v>3672.452</v>
       </c>
       <c r="G50">
         <v>297.8</v>
@@ -5393,37 +5393,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M50">
-        <v>869.6484453899329</v>
+        <v>887.7661213355566</v>
       </c>
       <c r="N50">
-        <v>-536.4913025327901</v>
+        <v>-554.6089784784137</v>
       </c>
       <c r="O50">
-        <v>-134.1228256331975</v>
+        <v>-138.6522446196034</v>
       </c>
       <c r="P50">
-        <v>-402.3684768995926</v>
+        <v>-415.9567338588103</v>
       </c>
       <c r="Q50">
-        <v>977.3315231004075</v>
+        <v>963.7432661411897</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09594495539245151</v>
+        <v>0.09692818981191136</v>
       </c>
       <c r="T50">
-        <v>0.97741851535527</v>
+        <v>0.9965835842838047</v>
       </c>
       <c r="U50">
         <v>0.2417366166625341</v>
       </c>
       <c r="V50">
-        <v>0.09577351187805604</v>
+        <v>0.09381895041115693</v>
       </c>
       <c r="W50">
-        <v>0.2185846519352438</v>
+        <v>0.219057141011311</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3830940475122242</v>
+        <v>0.3752758016446277</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1567713758996171</v>
+        <v>0.1587307420662425</v>
       </c>
       <c r="C51">
-        <v>-1898.027339759624</v>
+        <v>-1998.595010250964</v>
       </c>
       <c r="D51">
-        <v>1476.624660240376</v>
+        <v>1451.004989749036</v>
       </c>
       <c r="E51">
-        <v>-2143.948</v>
+        <v>-2069</v>
       </c>
       <c r="F51">
-        <v>3672.452</v>
+        <v>3747.4</v>
       </c>
       <c r="G51">
         <v>297.8</v>
@@ -5475,37 +5475,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M51">
-        <v>887.7661213355566</v>
+        <v>905.8837972811801</v>
       </c>
       <c r="N51">
-        <v>-554.6089784784137</v>
+        <v>-572.7266544240373</v>
       </c>
       <c r="O51">
-        <v>-138.6522446196034</v>
+        <v>-143.1816636060093</v>
       </c>
       <c r="P51">
-        <v>-415.9567338588103</v>
+        <v>-429.5449908180279</v>
       </c>
       <c r="Q51">
-        <v>963.7432661411897</v>
+        <v>950.1550091819721</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09692818981191136</v>
+        <v>0.09795075360814959</v>
       </c>
       <c r="T51">
-        <v>0.9965835842838047</v>
+        <v>1.016515255969481</v>
       </c>
       <c r="U51">
         <v>0.2417366166625341</v>
       </c>
       <c r="V51">
-        <v>0.09381895041115693</v>
+        <v>0.0919425714029338</v>
       </c>
       <c r="W51">
-        <v>0.219057141011311</v>
+        <v>0.2195107305243354</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3752758016446277</v>
+        <v>0.3677702856117352</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1587307420662425</v>
+        <v>0.1606901082328678</v>
       </c>
       <c r="C52">
-        <v>-1998.595010250964</v>
+        <v>-2098.288831525293</v>
       </c>
       <c r="D52">
-        <v>1451.004989749036</v>
+        <v>1426.259168474707</v>
       </c>
       <c r="E52">
-        <v>-2069</v>
+        <v>-1994.052</v>
       </c>
       <c r="F52">
-        <v>3747.4</v>
+        <v>3822.348</v>
       </c>
       <c r="G52">
         <v>297.8</v>
@@ -5557,37 +5557,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M52">
-        <v>905.8837972811801</v>
+        <v>924.0014732268038</v>
       </c>
       <c r="N52">
-        <v>-572.7266544240373</v>
+        <v>-590.844330369661</v>
       </c>
       <c r="O52">
-        <v>-143.1816636060093</v>
+        <v>-147.7110825924152</v>
       </c>
       <c r="P52">
-        <v>-429.5449908180279</v>
+        <v>-443.1332477772457</v>
       </c>
       <c r="Q52">
-        <v>950.1550091819721</v>
+        <v>936.5667522227543</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09795075360814959</v>
+        <v>0.09901505470219345</v>
       </c>
       <c r="T52">
-        <v>1.016515255969481</v>
+        <v>1.03726046527498</v>
       </c>
       <c r="U52">
         <v>0.2417366166625341</v>
       </c>
       <c r="V52">
-        <v>0.0919425714029338</v>
+        <v>0.09013977588522921</v>
       </c>
       <c r="W52">
-        <v>0.2195107305243354</v>
+        <v>0.2199465322133197</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3677702856117352</v>
+        <v>0.3605591035409168</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1606901082328678</v>
+        <v>0.1626494743994932</v>
       </c>
       <c r="C53">
-        <v>-2098.288831525293</v>
+        <v>-2197.152762460457</v>
       </c>
       <c r="D53">
-        <v>1426.259168474707</v>
+        <v>1402.343237539543</v>
       </c>
       <c r="E53">
-        <v>-1994.052</v>
+        <v>-1919.104</v>
       </c>
       <c r="F53">
-        <v>3822.348</v>
+        <v>3897.296</v>
       </c>
       <c r="G53">
         <v>297.8</v>
@@ -5639,37 +5639,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M53">
-        <v>924.0014732268038</v>
+        <v>942.1191491724275</v>
       </c>
       <c r="N53">
-        <v>-590.844330369661</v>
+        <v>-608.9620063152846</v>
       </c>
       <c r="O53">
-        <v>-147.7110825924152</v>
+        <v>-152.2405015788212</v>
       </c>
       <c r="P53">
-        <v>-443.1332477772457</v>
+        <v>-456.7215047364634</v>
       </c>
       <c r="Q53">
-        <v>936.5667522227543</v>
+        <v>922.9784952635366</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09901505470219345</v>
+        <v>0.1001237016751558</v>
       </c>
       <c r="T53">
-        <v>1.03726046527498</v>
+        <v>1.058870058301543</v>
       </c>
       <c r="U53">
         <v>0.2417366166625341</v>
       </c>
       <c r="V53">
-        <v>0.09013977588522921</v>
+        <v>0.08840631865666711</v>
       </c>
       <c r="W53">
-        <v>0.2199465322133197</v>
+        <v>0.2203655722988815</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3605591035409168</v>
+        <v>0.3536252746266684</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1626494743994932</v>
+        <v>0.1646088405661185</v>
       </c>
       <c r="C54">
-        <v>-2197.152762460457</v>
+        <v>-2295.227862098313</v>
       </c>
       <c r="D54">
-        <v>1402.343237539543</v>
+        <v>1379.216137901686</v>
       </c>
       <c r="E54">
-        <v>-1919.104</v>
+        <v>-1844.156</v>
       </c>
       <c r="F54">
-        <v>3897.296</v>
+        <v>3972.244</v>
       </c>
       <c r="G54">
         <v>297.8</v>
@@ -5721,37 +5721,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M54">
-        <v>942.1191491724275</v>
+        <v>960.236825118051</v>
       </c>
       <c r="N54">
-        <v>-608.9620063152846</v>
+        <v>-627.0796822609082</v>
       </c>
       <c r="O54">
-        <v>-152.2405015788212</v>
+        <v>-156.769920565227</v>
       </c>
       <c r="P54">
-        <v>-456.7215047364634</v>
+        <v>-470.3097616956811</v>
       </c>
       <c r="Q54">
-        <v>922.9784952635366</v>
+        <v>909.3902383043189</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1001237016751558</v>
+        <v>0.1012795251150528</v>
       </c>
       <c r="T54">
-        <v>1.058870058301543</v>
+        <v>1.081399208478171</v>
       </c>
       <c r="U54">
         <v>0.2417366166625341</v>
       </c>
       <c r="V54">
-        <v>0.08840631865666711</v>
+        <v>0.0867382749084281</v>
       </c>
       <c r="W54">
-        <v>0.2203655722988815</v>
+        <v>0.2207687995510259</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3536252746266684</v>
+        <v>0.3469530996337125</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1646088405661185</v>
+        <v>0.1665682067327439</v>
       </c>
       <c r="C55">
-        <v>-2295.227862098313</v>
+        <v>-2392.552524882159</v>
       </c>
       <c r="D55">
-        <v>1379.216137901686</v>
+        <v>1356.839475117841</v>
       </c>
       <c r="E55">
-        <v>-1844.156</v>
+        <v>-1769.208</v>
       </c>
       <c r="F55">
-        <v>3972.244</v>
+        <v>4047.192</v>
       </c>
       <c r="G55">
         <v>297.8</v>
@@ -5803,37 +5803,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M55">
-        <v>960.236825118051</v>
+        <v>978.3545010636747</v>
       </c>
       <c r="N55">
-        <v>-627.0796822609082</v>
+        <v>-645.1973582065318</v>
       </c>
       <c r="O55">
-        <v>-156.769920565227</v>
+        <v>-161.299339551633</v>
       </c>
       <c r="P55">
-        <v>-470.3097616956811</v>
+        <v>-483.8980186548989</v>
       </c>
       <c r="Q55">
-        <v>909.3902383043189</v>
+        <v>895.8019813451012</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1012795251150528</v>
+        <v>0.1024856017479887</v>
       </c>
       <c r="T55">
-        <v>1.081399208478171</v>
+        <v>1.104907886923349</v>
       </c>
       <c r="U55">
         <v>0.2417366166625341</v>
       </c>
       <c r="V55">
-        <v>0.0867382749084281</v>
+        <v>0.08513201055827202</v>
       </c>
       <c r="W55">
-        <v>0.2207687995510259</v>
+        <v>0.2211570924604983</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3469530996337125</v>
+        <v>0.3405280422330881</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1665682067327439</v>
+        <v>0.1685275728993692</v>
       </c>
       <c r="C56">
-        <v>-2392.552524882159</v>
+        <v>-2489.162693360529</v>
       </c>
       <c r="D56">
-        <v>1356.839475117841</v>
+        <v>1335.177306639471</v>
       </c>
       <c r="E56">
-        <v>-1769.208</v>
+        <v>-1694.259999999999</v>
       </c>
       <c r="F56">
-        <v>4047.192</v>
+        <v>4122.14</v>
       </c>
       <c r="G56">
         <v>297.8</v>
@@ -5885,37 +5885,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M56">
-        <v>978.3545010636747</v>
+        <v>996.4721770092984</v>
       </c>
       <c r="N56">
-        <v>-645.1973582065318</v>
+        <v>-663.3150341521556</v>
       </c>
       <c r="O56">
-        <v>-161.299339551633</v>
+        <v>-165.8287585380389</v>
       </c>
       <c r="P56">
-        <v>-483.8980186548989</v>
+        <v>-497.4862756141167</v>
       </c>
       <c r="Q56">
-        <v>895.8019813451012</v>
+        <v>882.2137243858833</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1024856017479887</v>
+        <v>0.1037452817868329</v>
       </c>
       <c r="T56">
-        <v>1.104907886923349</v>
+        <v>1.129461395521646</v>
       </c>
       <c r="U56">
         <v>0.2417366166625341</v>
       </c>
       <c r="V56">
-        <v>0.08513201055827202</v>
+        <v>0.08358415582084888</v>
       </c>
       <c r="W56">
-        <v>0.2211570924604983</v>
+        <v>0.221531265627808</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3405280422330881</v>
+        <v>0.3343366232833955</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1685275728993692</v>
+        <v>0.1704869390659945</v>
       </c>
       <c r="C57">
-        <v>-2489.162693360529</v>
+        <v>-2585.092050836075</v>
       </c>
       <c r="D57">
-        <v>1335.177306639471</v>
+        <v>1314.195949163925</v>
       </c>
       <c r="E57">
-        <v>-1694.259999999999</v>
+        <v>-1619.312</v>
       </c>
       <c r="F57">
-        <v>4122.14</v>
+        <v>4197.088</v>
       </c>
       <c r="G57">
         <v>297.8</v>
@@ -5967,37 +5967,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M57">
-        <v>996.4721770092984</v>
+        <v>1014.589852954922</v>
       </c>
       <c r="N57">
-        <v>-663.3150341521556</v>
+        <v>-681.432710097779</v>
       </c>
       <c r="O57">
-        <v>-165.8287585380389</v>
+        <v>-170.3581775244448</v>
       </c>
       <c r="P57">
-        <v>-497.4862756141167</v>
+        <v>-511.0745325733343</v>
       </c>
       <c r="Q57">
-        <v>882.2137243858833</v>
+        <v>868.6254674266658</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1037452817868329</v>
+        <v>0.1050622200092609</v>
       </c>
       <c r="T57">
-        <v>1.129461395521646</v>
+        <v>1.155130972692592</v>
       </c>
       <c r="U57">
         <v>0.2417366166625341</v>
       </c>
       <c r="V57">
-        <v>0.08358415582084888</v>
+        <v>0.08209158160976231</v>
       </c>
       <c r="W57">
-        <v>0.221531265627808</v>
+        <v>0.2218920754677139</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3343366232833955</v>
+        <v>0.3283663264390493</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1704869390659945</v>
+        <v>0.1724463052326199</v>
       </c>
       <c r="C58">
-        <v>-2585.092050836075</v>
+        <v>-2680.372196131418</v>
       </c>
       <c r="D58">
-        <v>1314.195949163925</v>
+        <v>1293.863803868583</v>
       </c>
       <c r="E58">
-        <v>-1619.312</v>
+        <v>-1544.364</v>
       </c>
       <c r="F58">
-        <v>4197.088</v>
+        <v>4272.036</v>
       </c>
       <c r="G58">
         <v>297.8</v>
@@ -6049,37 +6049,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M58">
-        <v>1014.589852954922</v>
+        <v>1032.707528900546</v>
       </c>
       <c r="N58">
-        <v>-681.432710097779</v>
+        <v>-699.5503860434028</v>
       </c>
       <c r="O58">
-        <v>-170.3581775244448</v>
+        <v>-174.8875965108507</v>
       </c>
       <c r="P58">
-        <v>-511.0745325733343</v>
+        <v>-524.6627895325521</v>
       </c>
       <c r="Q58">
-        <v>868.6254674266658</v>
+        <v>855.0372104674479</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1050622200092609</v>
+        <v>0.106440411172267</v>
       </c>
       <c r="T58">
-        <v>1.155130972692592</v>
+        <v>1.181994483685443</v>
       </c>
       <c r="U58">
         <v>0.2417366166625341</v>
       </c>
       <c r="V58">
-        <v>0.08209158160976231</v>
+        <v>0.08065137842362612</v>
       </c>
       <c r="W58">
-        <v>0.2218920754677139</v>
+        <v>0.222240225313237</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3283663264390493</v>
+        <v>0.3226055136945045</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1724463052326199</v>
+        <v>0.1744056713992453</v>
       </c>
       <c r="C59">
-        <v>-2680.372196131418</v>
+        <v>-2775.032802379172</v>
       </c>
       <c r="D59">
-        <v>1293.863803868583</v>
+        <v>1274.151197620829</v>
       </c>
       <c r="E59">
-        <v>-1544.364</v>
+        <v>-1469.415999999999</v>
       </c>
       <c r="F59">
-        <v>4272.036</v>
+        <v>4346.984</v>
       </c>
       <c r="G59">
         <v>297.8</v>
@@ -6131,37 +6131,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M59">
-        <v>1032.707528900546</v>
+        <v>1050.825204846169</v>
       </c>
       <c r="N59">
-        <v>-699.5503860434028</v>
+        <v>-717.6680619890265</v>
       </c>
       <c r="O59">
-        <v>-174.8875965108507</v>
+        <v>-179.4170154972566</v>
       </c>
       <c r="P59">
-        <v>-524.6627895325521</v>
+        <v>-538.2510464917698</v>
       </c>
       <c r="Q59">
-        <v>855.0372104674479</v>
+        <v>841.4489535082303</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.106440411172267</v>
+        <v>0.1078842304858924</v>
       </c>
       <c r="T59">
-        <v>1.181994483685443</v>
+        <v>1.210137209487478</v>
       </c>
       <c r="U59">
         <v>0.2417366166625341</v>
       </c>
       <c r="V59">
-        <v>0.08065137842362612</v>
+        <v>0.07926083741632221</v>
       </c>
       <c r="W59">
-        <v>0.222240225313237</v>
+        <v>0.2225763699916732</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3226055136945045</v>
+        <v>0.3170433496652889</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1744056713992452</v>
+        <v>0.1763650375658706</v>
       </c>
       <c r="C60">
-        <v>-2775.032802379171</v>
+        <v>-2869.101761514375</v>
       </c>
       <c r="D60">
-        <v>1274.151197620829</v>
+        <v>1255.030238485625</v>
       </c>
       <c r="E60">
-        <v>-1469.416</v>
+        <v>-1394.468</v>
       </c>
       <c r="F60">
-        <v>4346.983999999999</v>
+        <v>4421.932</v>
       </c>
       <c r="G60">
         <v>297.8</v>
@@ -6213,37 +6213,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M60">
-        <v>1050.825204846169</v>
+        <v>1068.942880791793</v>
       </c>
       <c r="N60">
-        <v>-717.6680619890262</v>
+        <v>-735.7857379346499</v>
       </c>
       <c r="O60">
-        <v>-179.4170154972566</v>
+        <v>-183.9464344836625</v>
       </c>
       <c r="P60">
-        <v>-538.2510464917697</v>
+        <v>-551.8393034509875</v>
       </c>
       <c r="Q60">
-        <v>841.4489535082304</v>
+        <v>827.8606965490126</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1078842304858924</v>
+        <v>0.1093984800099385</v>
       </c>
       <c r="T60">
-        <v>1.210137209487477</v>
+        <v>1.239652751182294</v>
       </c>
       <c r="U60">
         <v>0.2417366166625341</v>
       </c>
       <c r="V60">
-        <v>0.07926083741632223</v>
+        <v>0.07791743339231677</v>
       </c>
       <c r="W60">
-        <v>0.2225763699916732</v>
+        <v>0.2229011199352471</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3170433496652889</v>
+        <v>0.3116697335692671</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1763650375658706</v>
+        <v>0.1783244037324959</v>
       </c>
       <c r="C61">
-        <v>-2869.101761514375</v>
+        <v>-2962.605315949044</v>
       </c>
       <c r="D61">
-        <v>1255.030238485625</v>
+        <v>1236.474684050956</v>
       </c>
       <c r="E61">
-        <v>-1394.468</v>
+        <v>-1319.52</v>
       </c>
       <c r="F61">
-        <v>4421.932</v>
+        <v>4496.879999999999</v>
       </c>
       <c r="G61">
         <v>297.8</v>
@@ -6295,37 +6295,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M61">
-        <v>1068.942880791793</v>
+        <v>1087.060556737416</v>
       </c>
       <c r="N61">
-        <v>-735.7857379346499</v>
+        <v>-753.9034138802733</v>
       </c>
       <c r="O61">
-        <v>-183.9464344836625</v>
+        <v>-188.4758534700683</v>
       </c>
       <c r="P61">
-        <v>-551.8393034509875</v>
+        <v>-565.4275604102049</v>
       </c>
       <c r="Q61">
-        <v>827.8606965490126</v>
+        <v>814.2724395897951</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1093984800099385</v>
+        <v>0.110988442010187</v>
       </c>
       <c r="T61">
-        <v>1.239652751182294</v>
+        <v>1.270644069961851</v>
       </c>
       <c r="U61">
         <v>0.2417366166625341</v>
       </c>
       <c r="V61">
-        <v>0.07791743339231677</v>
+        <v>0.07661880950244483</v>
       </c>
       <c r="W61">
-        <v>0.2229011199352471</v>
+        <v>0.2232150448807019</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3116697335692671</v>
+        <v>0.3064752380097794</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1783244037324959</v>
+        <v>0.1802837698991213</v>
       </c>
       <c r="C62">
-        <v>-2962.605315949044</v>
+        <v>-3055.568178736096</v>
       </c>
       <c r="D62">
-        <v>1236.474684050956</v>
+        <v>1218.459821263903</v>
       </c>
       <c r="E62">
-        <v>-1319.52</v>
+        <v>-1244.572</v>
       </c>
       <c r="F62">
-        <v>4496.879999999999</v>
+        <v>4571.828</v>
       </c>
       <c r="G62">
         <v>297.8</v>
@@ -6377,37 +6377,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M62">
-        <v>1087.060556737416</v>
+        <v>1105.17823268304</v>
       </c>
       <c r="N62">
-        <v>-753.9034138802733</v>
+        <v>-772.021089825897</v>
       </c>
       <c r="O62">
-        <v>-188.4758534700683</v>
+        <v>-193.0052724564742</v>
       </c>
       <c r="P62">
-        <v>-565.4275604102049</v>
+        <v>-579.0158173694227</v>
       </c>
       <c r="Q62">
-        <v>814.2724395897951</v>
+        <v>800.6841826305773</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.110988442010187</v>
+        <v>0.1126599405232687</v>
       </c>
       <c r="T62">
-        <v>1.270644069961851</v>
+        <v>1.30322468714036</v>
       </c>
       <c r="U62">
         <v>0.2417366166625341</v>
       </c>
       <c r="V62">
-        <v>0.07661880950244483</v>
+        <v>0.07536276344502769</v>
       </c>
       <c r="W62">
-        <v>0.2232150448807019</v>
+        <v>0.2235186772049942</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3064752380097794</v>
+        <v>0.3014510537801108</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1802837698991213</v>
+        <v>0.1822431360657466</v>
       </c>
       <c r="C63">
-        <v>-3055.568178736096</v>
+        <v>-3148.013643379731</v>
       </c>
       <c r="D63">
-        <v>1218.459821263903</v>
+        <v>1200.962356620269</v>
       </c>
       <c r="E63">
-        <v>-1244.572</v>
+        <v>-1169.624</v>
       </c>
       <c r="F63">
-        <v>4571.828</v>
+        <v>4646.776</v>
       </c>
       <c r="G63">
         <v>297.8</v>
@@ -6459,37 +6459,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M63">
-        <v>1105.17823268304</v>
+        <v>1123.295908628663</v>
       </c>
       <c r="N63">
-        <v>-772.021089825897</v>
+        <v>-790.1387657715206</v>
       </c>
       <c r="O63">
-        <v>-193.0052724564742</v>
+        <v>-197.5346914428802</v>
       </c>
       <c r="P63">
-        <v>-579.0158173694227</v>
+        <v>-592.6040743286405</v>
       </c>
       <c r="Q63">
-        <v>800.6841826305773</v>
+        <v>787.0959256713595</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1126599405232687</v>
+        <v>0.1144194126423021</v>
       </c>
       <c r="T63">
-        <v>1.30322468714036</v>
+        <v>1.337520073644054</v>
       </c>
       <c r="U63">
         <v>0.2417366166625341</v>
       </c>
       <c r="V63">
-        <v>0.07536276344502769</v>
+        <v>0.07414723500236596</v>
       </c>
       <c r="W63">
-        <v>0.2235186772049942</v>
+        <v>0.2238125149381803</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3014510537801108</v>
+        <v>0.2965889400094638</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1822431360657466</v>
+        <v>0.1842025022323719</v>
       </c>
       <c r="C64">
-        <v>-3148.013643379731</v>
+        <v>-3239.963684318279</v>
       </c>
       <c r="D64">
-        <v>1200.962356620269</v>
+        <v>1183.96031568172</v>
       </c>
       <c r="E64">
-        <v>-1169.624</v>
+        <v>-1094.676</v>
       </c>
       <c r="F64">
-        <v>4646.776</v>
+        <v>4721.723999999999</v>
       </c>
       <c r="G64">
         <v>297.8</v>
@@ -6541,37 +6541,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M64">
-        <v>1123.295908628663</v>
+        <v>1141.413584574287</v>
       </c>
       <c r="N64">
-        <v>-790.1387657715206</v>
+        <v>-808.2564417171441</v>
       </c>
       <c r="O64">
-        <v>-197.5346914428802</v>
+        <v>-202.064110429286</v>
       </c>
       <c r="P64">
-        <v>-592.6040743286405</v>
+        <v>-606.192331287858</v>
       </c>
       <c r="Q64">
-        <v>787.0959256713595</v>
+        <v>773.507668712142</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1144194126423021</v>
+        <v>0.1162739913623643</v>
       </c>
       <c r="T64">
-        <v>1.337520073644054</v>
+        <v>1.373669264823623</v>
       </c>
       <c r="U64">
         <v>0.2417366166625341</v>
       </c>
       <c r="V64">
-        <v>0.07414723500236596</v>
+        <v>0.07297029476423318</v>
       </c>
       <c r="W64">
-        <v>0.2238125149381803</v>
+        <v>0.2240970244893605</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2965889400094638</v>
+        <v>0.2918811790569327</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1842025022323719</v>
+        <v>0.1861618683989973</v>
       </c>
       <c r="C65">
-        <v>-3239.963684318279</v>
+        <v>-3331.439048990994</v>
       </c>
       <c r="D65">
-        <v>1183.96031568172</v>
+        <v>1167.432951009006</v>
       </c>
       <c r="E65">
-        <v>-1094.676</v>
+        <v>-1019.728</v>
       </c>
       <c r="F65">
-        <v>4721.723999999999</v>
+        <v>4796.672</v>
       </c>
       <c r="G65">
         <v>297.8</v>
@@ -6623,37 +6623,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M65">
-        <v>1141.413584574287</v>
+        <v>1159.531260519911</v>
       </c>
       <c r="N65">
-        <v>-808.2564417171441</v>
+        <v>-826.3741176627677</v>
       </c>
       <c r="O65">
-        <v>-202.064110429286</v>
+        <v>-206.5935294156919</v>
       </c>
       <c r="P65">
-        <v>-606.192331287858</v>
+        <v>-619.7805882470758</v>
       </c>
       <c r="Q65">
-        <v>773.507668712142</v>
+        <v>759.9194117529242</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1162739913623643</v>
+        <v>0.1182316022335411</v>
       </c>
       <c r="T65">
-        <v>1.373669264823623</v>
+        <v>1.411826744402057</v>
       </c>
       <c r="U65">
         <v>0.2417366166625341</v>
       </c>
       <c r="V65">
-        <v>0.07297029476423318</v>
+        <v>0.07183013390854202</v>
       </c>
       <c r="W65">
-        <v>0.2240970244893605</v>
+        <v>0.2243726431170664</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2918811790569327</v>
+        <v>0.2873205356341682</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1861618683989973</v>
+        <v>0.1881212345656226</v>
       </c>
       <c r="C66">
-        <v>-3331.439048990994</v>
+        <v>-3422.459342299804</v>
       </c>
       <c r="D66">
-        <v>1167.432951009006</v>
+        <v>1151.360657700196</v>
       </c>
       <c r="E66">
-        <v>-1019.728</v>
+        <v>-944.7799999999997</v>
       </c>
       <c r="F66">
-        <v>4796.672</v>
+        <v>4871.62</v>
       </c>
       <c r="G66">
         <v>297.8</v>
@@ -6705,37 +6705,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M66">
-        <v>1159.531260519911</v>
+        <v>1177.648936465534</v>
       </c>
       <c r="N66">
-        <v>-826.3741176627677</v>
+        <v>-844.4917936083914</v>
       </c>
       <c r="O66">
-        <v>-206.5935294156919</v>
+        <v>-211.1229484020978</v>
       </c>
       <c r="P66">
-        <v>-619.7805882470758</v>
+        <v>-633.3688452062936</v>
       </c>
       <c r="Q66">
-        <v>759.9194117529242</v>
+        <v>746.3311547937064</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1182316022335411</v>
+        <v>0.1203010765830708</v>
       </c>
       <c r="T66">
-        <v>1.411826744402057</v>
+        <v>1.452164651384973</v>
       </c>
       <c r="U66">
         <v>0.2417366166625341</v>
       </c>
       <c r="V66">
-        <v>0.07183013390854202</v>
+        <v>0.07072505492533369</v>
       </c>
       <c r="W66">
-        <v>0.2243726431170664</v>
+        <v>0.224639781171612</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2873205356341682</v>
+        <v>0.2829002197013347</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1881212345656226</v>
+        <v>0.190080600732248</v>
       </c>
       <c r="C67">
-        <v>-3422.459342299804</v>
+        <v>-3513.043104189011</v>
       </c>
       <c r="D67">
-        <v>1151.360657700196</v>
+        <v>1135.724895810989</v>
       </c>
       <c r="E67">
-        <v>-944.7799999999997</v>
+        <v>-869.8320000000003</v>
       </c>
       <c r="F67">
-        <v>4871.62</v>
+        <v>4946.567999999999</v>
       </c>
       <c r="G67">
         <v>297.8</v>
@@ -6787,37 +6787,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M67">
-        <v>1177.648936465534</v>
+        <v>1195.766612411158</v>
       </c>
       <c r="N67">
-        <v>-844.4917936083914</v>
+        <v>-862.609469554015</v>
       </c>
       <c r="O67">
-        <v>-211.1229484020978</v>
+        <v>-215.6523673885038</v>
       </c>
       <c r="P67">
-        <v>-633.3688452062936</v>
+        <v>-646.9571021655113</v>
       </c>
       <c r="Q67">
-        <v>746.3311547937064</v>
+        <v>732.7428978344888</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1203010765830708</v>
+        <v>0.1224922847178671</v>
       </c>
       <c r="T67">
-        <v>1.452164651384973</v>
+        <v>1.494875376425707</v>
       </c>
       <c r="U67">
         <v>0.2417366166625341</v>
       </c>
       <c r="V67">
-        <v>0.07072505492533369</v>
+        <v>0.06965346318404075</v>
       </c>
       <c r="W67">
-        <v>0.224639781171612</v>
+        <v>0.2248988241335957</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2829002197013347</v>
+        <v>0.278613852736163</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.190080600732248</v>
+        <v>0.1920399668988733</v>
       </c>
       <c r="C68">
-        <v>-3513.043104189011</v>
+        <v>-3603.207880988372</v>
       </c>
       <c r="D68">
-        <v>1135.724895810989</v>
+        <v>1120.508119011628</v>
       </c>
       <c r="E68">
-        <v>-869.8320000000003</v>
+        <v>-794.884</v>
       </c>
       <c r="F68">
-        <v>4946.567999999999</v>
+        <v>5021.516</v>
       </c>
       <c r="G68">
         <v>297.8</v>
@@ -6869,37 +6869,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M68">
-        <v>1195.766612411158</v>
+        <v>1213.884288356782</v>
       </c>
       <c r="N68">
-        <v>-862.609469554015</v>
+        <v>-880.7271454996387</v>
       </c>
       <c r="O68">
-        <v>-215.6523673885038</v>
+        <v>-220.1817863749097</v>
       </c>
       <c r="P68">
-        <v>-646.9571021655113</v>
+        <v>-660.545359124729</v>
       </c>
       <c r="Q68">
-        <v>732.7428978344888</v>
+        <v>719.1546408752711</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1224922847178671</v>
+        <v>0.1248162933456812</v>
       </c>
       <c r="T68">
-        <v>1.494875376425707</v>
+        <v>1.540174630256789</v>
       </c>
       <c r="U68">
         <v>0.2417366166625341</v>
       </c>
       <c r="V68">
-        <v>0.06965346318404075</v>
+        <v>0.06861385925592074</v>
       </c>
       <c r="W68">
-        <v>0.2248988241335957</v>
+        <v>0.2251501344698485</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.278613852736163</v>
+        <v>0.2744554370236829</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1920399668988733</v>
+        <v>0.1939993330654987</v>
       </c>
       <c r="C69">
-        <v>-3603.207880988372</v>
+        <v>-3692.97029109675</v>
       </c>
       <c r="D69">
-        <v>1120.508119011628</v>
+        <v>1105.69370890325</v>
       </c>
       <c r="E69">
-        <v>-794.884</v>
+        <v>-719.9359999999997</v>
       </c>
       <c r="F69">
-        <v>5021.516</v>
+        <v>5096.464</v>
       </c>
       <c r="G69">
         <v>297.8</v>
@@ -6951,37 +6951,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M69">
-        <v>1213.884288356782</v>
+        <v>1232.001964302405</v>
       </c>
       <c r="N69">
-        <v>-880.7271454996387</v>
+        <v>-898.8448214452624</v>
       </c>
       <c r="O69">
-        <v>-220.1817863749097</v>
+        <v>-224.7112053613156</v>
       </c>
       <c r="P69">
-        <v>-660.545359124729</v>
+        <v>-674.1336160839468</v>
       </c>
       <c r="Q69">
-        <v>719.1546408752711</v>
+        <v>705.5663839160533</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1248162933456812</v>
+        <v>0.1272855525127337</v>
       </c>
       <c r="T69">
-        <v>1.540174630256789</v>
+        <v>1.588305087452314</v>
       </c>
       <c r="U69">
         <v>0.2417366166625341</v>
       </c>
       <c r="V69">
-        <v>0.06861385925592074</v>
+        <v>0.0676048319139219</v>
       </c>
       <c r="W69">
-        <v>0.2251501344698485</v>
+        <v>0.2253940533256233</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2744554370236829</v>
+        <v>0.2704193276556875</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1939993330654987</v>
+        <v>0.195958699232124</v>
       </c>
       <c r="C70">
-        <v>-3692.97029109675</v>
+        <v>-3782.346085523275</v>
       </c>
       <c r="D70">
-        <v>1105.69370890325</v>
+        <v>1091.265914476725</v>
       </c>
       <c r="E70">
-        <v>-719.9359999999997</v>
+        <v>-644.9879999999994</v>
       </c>
       <c r="F70">
-        <v>5096.464</v>
+        <v>5171.412</v>
       </c>
       <c r="G70">
         <v>297.8</v>
@@ -7033,37 +7033,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M70">
-        <v>1232.001964302405</v>
+        <v>1250.119640248029</v>
       </c>
       <c r="N70">
-        <v>-898.8448214452624</v>
+        <v>-916.962497390886</v>
       </c>
       <c r="O70">
-        <v>-224.7112053613156</v>
+        <v>-229.2406243477215</v>
       </c>
       <c r="P70">
-        <v>-674.1336160839468</v>
+        <v>-687.7218730431646</v>
       </c>
       <c r="Q70">
-        <v>705.5663839160533</v>
+        <v>691.9781269568355</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1272855525127337</v>
+        <v>0.1299141187228219</v>
       </c>
       <c r="T70">
-        <v>1.588305087452314</v>
+        <v>1.639540735434647</v>
       </c>
       <c r="U70">
         <v>0.2417366166625341</v>
       </c>
       <c r="V70">
-        <v>0.0676048319139219</v>
+        <v>0.06662505174125637</v>
       </c>
       <c r="W70">
-        <v>0.2253940533256233</v>
+        <v>0.2256309020696365</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2704193276556875</v>
+        <v>0.2665002069650254</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.195958699232124</v>
+        <v>0.1979180653987493</v>
       </c>
       <c r="C71">
-        <v>-3782.346085523275</v>
+        <v>-3871.350203749682</v>
       </c>
       <c r="D71">
-        <v>1091.265914476725</v>
+        <v>1077.209796250318</v>
       </c>
       <c r="E71">
-        <v>-644.9879999999994</v>
+        <v>-570.04</v>
       </c>
       <c r="F71">
-        <v>5171.412</v>
+        <v>5246.36</v>
       </c>
       <c r="G71">
         <v>297.8</v>
@@ -7115,37 +7115,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M71">
-        <v>1250.119640248029</v>
+        <v>1268.237316193652</v>
       </c>
       <c r="N71">
-        <v>-916.962497390886</v>
+        <v>-935.0801733365095</v>
       </c>
       <c r="O71">
-        <v>-229.2406243477215</v>
+        <v>-233.7700433341274</v>
       </c>
       <c r="P71">
-        <v>-687.7218730431646</v>
+        <v>-701.310130002382</v>
       </c>
       <c r="Q71">
-        <v>691.9781269568355</v>
+        <v>678.389869997618</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1299141187228219</v>
+        <v>0.1327179226802493</v>
       </c>
       <c r="T71">
-        <v>1.639540735434647</v>
+        <v>1.694192093282469</v>
       </c>
       <c r="U71">
         <v>0.2417366166625341</v>
       </c>
       <c r="V71">
-        <v>0.06662505174125637</v>
+        <v>0.06567326528780985</v>
       </c>
       <c r="W71">
-        <v>0.2256309020696365</v>
+        <v>0.2258609837066779</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2665002069650254</v>
+        <v>0.2626930611512394</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1979180653987493</v>
+        <v>0.1998774315653747</v>
       </c>
       <c r="C72">
-        <v>-3871.350203749682</v>
+        <v>-3959.996825330319</v>
       </c>
       <c r="D72">
-        <v>1077.209796250318</v>
+        <v>1063.511174669681</v>
       </c>
       <c r="E72">
-        <v>-570.04</v>
+        <v>-495.0919999999996</v>
       </c>
       <c r="F72">
-        <v>5246.36</v>
+        <v>5321.308</v>
       </c>
       <c r="G72">
         <v>297.8</v>
@@ -7197,37 +7197,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M72">
-        <v>1268.237316193652</v>
+        <v>1286.354992139276</v>
       </c>
       <c r="N72">
-        <v>-935.0801733365095</v>
+        <v>-953.1978492821331</v>
       </c>
       <c r="O72">
-        <v>-233.7700433341274</v>
+        <v>-238.2994623205333</v>
       </c>
       <c r="P72">
-        <v>-701.310130002382</v>
+        <v>-714.8983869615998</v>
       </c>
       <c r="Q72">
-        <v>678.389869997618</v>
+        <v>664.8016130384002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1327179226802493</v>
+        <v>0.1357150924278441</v>
       </c>
       <c r="T72">
-        <v>1.694192093282469</v>
+        <v>1.752612510292209</v>
       </c>
       <c r="U72">
         <v>0.2417366166625341</v>
       </c>
       <c r="V72">
-        <v>0.06567326528780985</v>
+        <v>0.06474828972037591</v>
       </c>
       <c r="W72">
-        <v>0.2258609837066779</v>
+        <v>0.2260845841708449</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2626930611512394</v>
+        <v>0.2589931588815036</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1998774315653746</v>
+        <v>0.201836797732</v>
       </c>
       <c r="C73">
-        <v>-3959.996825330317</v>
+        <v>-4048.299417604474</v>
       </c>
       <c r="D73">
-        <v>1063.511174669683</v>
+        <v>1050.156582395525</v>
       </c>
       <c r="E73">
-        <v>-495.0920000000006</v>
+        <v>-420.1440000000002</v>
       </c>
       <c r="F73">
-        <v>5321.307999999999</v>
+        <v>5396.255999999999</v>
       </c>
       <c r="G73">
         <v>297.8</v>
@@ -7279,37 +7279,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M73">
-        <v>1286.354992139276</v>
+        <v>1304.472668084899</v>
       </c>
       <c r="N73">
-        <v>-953.1978492821329</v>
+        <v>-971.3155252277566</v>
       </c>
       <c r="O73">
-        <v>-238.2994623205332</v>
+        <v>-242.8288813069391</v>
       </c>
       <c r="P73">
-        <v>-714.8983869615997</v>
+        <v>-728.4866439208174</v>
       </c>
       <c r="Q73">
-        <v>664.8016130384003</v>
+        <v>651.2133560791826</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1357150924278441</v>
+        <v>0.1389263457288386</v>
       </c>
       <c r="T73">
-        <v>1.752612510292208</v>
+        <v>1.815205814231216</v>
       </c>
       <c r="U73">
         <v>0.2417366166625341</v>
       </c>
       <c r="V73">
-        <v>0.06474828972037591</v>
+        <v>0.06384900791870403</v>
       </c>
       <c r="W73">
-        <v>0.2260845841708449</v>
+        <v>0.2263019735110072</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2589931588815036</v>
+        <v>0.2553960316748161</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.201836797732</v>
+        <v>0.2037961638986253</v>
       </c>
       <c r="C74">
-        <v>-4048.299417604474</v>
+        <v>-4136.270779858539</v>
       </c>
       <c r="D74">
-        <v>1050.156582395525</v>
+        <v>1037.133220141461</v>
       </c>
       <c r="E74">
-        <v>-420.1440000000002</v>
+        <v>-345.1959999999999</v>
       </c>
       <c r="F74">
-        <v>5396.255999999999</v>
+        <v>5471.204</v>
       </c>
       <c r="G74">
         <v>297.8</v>
@@ -7361,37 +7361,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M74">
-        <v>1304.472668084899</v>
+        <v>1322.590344030523</v>
       </c>
       <c r="N74">
-        <v>-971.3155252277566</v>
+        <v>-989.4332011733802</v>
       </c>
       <c r="O74">
-        <v>-242.8288813069391</v>
+        <v>-247.3583002933451</v>
       </c>
       <c r="P74">
-        <v>-728.4866439208174</v>
+        <v>-742.0749008800351</v>
       </c>
       <c r="Q74">
-        <v>651.2133560791826</v>
+        <v>637.6250991199649</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1389263457288386</v>
+        <v>0.1423754696447214</v>
       </c>
       <c r="T74">
-        <v>1.815205814231216</v>
+        <v>1.882435659202742</v>
       </c>
       <c r="U74">
         <v>0.2417366166625341</v>
       </c>
       <c r="V74">
-        <v>0.06384900791870403</v>
+        <v>0.06297436397461219</v>
       </c>
       <c r="W74">
-        <v>0.2263019735110072</v>
+        <v>0.2265134069788364</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2553960316748161</v>
+        <v>0.2518974558984487</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2037961638986253</v>
+        <v>0.2057555300652507</v>
       </c>
       <c r="C75">
-        <v>-4136.270779858539</v>
+        <v>-4223.923084242386</v>
       </c>
       <c r="D75">
-        <v>1037.133220141461</v>
+        <v>1024.428915757613</v>
       </c>
       <c r="E75">
-        <v>-345.1959999999999</v>
+        <v>-270.2480000000005</v>
       </c>
       <c r="F75">
-        <v>5471.204</v>
+        <v>5546.151999999999</v>
       </c>
       <c r="G75">
         <v>297.8</v>
@@ -7443,37 +7443,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M75">
-        <v>1322.590344030523</v>
+        <v>1340.708019976147</v>
       </c>
       <c r="N75">
-        <v>-989.4332011733802</v>
+        <v>-1007.550877119004</v>
       </c>
       <c r="O75">
-        <v>-247.3583002933451</v>
+        <v>-251.887719279751</v>
       </c>
       <c r="P75">
-        <v>-742.0749008800351</v>
+        <v>-755.6631578392529</v>
       </c>
       <c r="Q75">
-        <v>637.6250991199649</v>
+        <v>624.0368421607471</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1423754696447214</v>
+        <v>0.146089910784903</v>
       </c>
       <c r="T75">
-        <v>1.882435659202742</v>
+        <v>1.95483703071054</v>
       </c>
       <c r="U75">
         <v>0.2417366166625341</v>
       </c>
       <c r="V75">
-        <v>0.06297436397461219</v>
+        <v>0.06212335905603635</v>
       </c>
       <c r="W75">
-        <v>0.2265134069788364</v>
+        <v>0.2267191260286161</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2518974558984487</v>
+        <v>0.2484934362241453</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2057555300652507</v>
+        <v>0.2077148962318761</v>
       </c>
       <c r="C76">
-        <v>-4223.923084242386</v>
+        <v>-4311.26791371491</v>
       </c>
       <c r="D76">
-        <v>1024.428915757613</v>
+        <v>1012.032086285089</v>
       </c>
       <c r="E76">
-        <v>-270.2480000000005</v>
+        <v>-195.3000000000002</v>
       </c>
       <c r="F76">
-        <v>5546.151999999999</v>
+        <v>5621.099999999999</v>
       </c>
       <c r="G76">
         <v>297.8</v>
@@ -7525,37 +7525,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M76">
-        <v>1340.708019976147</v>
+        <v>1358.82569592177</v>
       </c>
       <c r="N76">
-        <v>-1007.550877119004</v>
+        <v>-1025.668553064628</v>
       </c>
       <c r="O76">
-        <v>-251.887719279751</v>
+        <v>-256.4171382661569</v>
       </c>
       <c r="P76">
-        <v>-755.6631578392529</v>
+        <v>-769.2514147984707</v>
       </c>
       <c r="Q76">
-        <v>624.0368421607471</v>
+        <v>610.4485852015293</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.146089910784903</v>
+        <v>0.1501015072162992</v>
       </c>
       <c r="T76">
-        <v>1.95483703071054</v>
+        <v>2.033030511938962</v>
       </c>
       <c r="U76">
         <v>0.2417366166625341</v>
       </c>
       <c r="V76">
-        <v>0.06212335905603635</v>
+        <v>0.06129504760195586</v>
       </c>
       <c r="W76">
-        <v>0.2267191260286161</v>
+        <v>0.2269193592370683</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2484934362241453</v>
+        <v>0.2451801904078235</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2077148962318761</v>
+        <v>0.2096742623985014</v>
       </c>
       <c r="C77">
-        <v>-4311.26791371491</v>
+        <v>-4398.31629726742</v>
       </c>
       <c r="D77">
-        <v>1012.032086285089</v>
+        <v>999.9317027325797</v>
       </c>
       <c r="E77">
-        <v>-195.3000000000002</v>
+        <v>-120.3519999999999</v>
       </c>
       <c r="F77">
-        <v>5621.099999999999</v>
+        <v>5696.048</v>
       </c>
       <c r="G77">
         <v>297.8</v>
@@ -7607,37 +7607,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M77">
-        <v>1358.82569592177</v>
+        <v>1376.943371867394</v>
       </c>
       <c r="N77">
-        <v>-1025.668553064628</v>
+        <v>-1043.786229010251</v>
       </c>
       <c r="O77">
-        <v>-256.4171382661569</v>
+        <v>-260.9465572525628</v>
       </c>
       <c r="P77">
-        <v>-769.2514147984707</v>
+        <v>-782.8396717576884</v>
       </c>
       <c r="Q77">
-        <v>610.4485852015293</v>
+        <v>596.8603282423117</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1501015072162992</v>
+        <v>0.1544474033503117</v>
       </c>
       <c r="T77">
-        <v>2.033030511938962</v>
+        <v>2.117740116603085</v>
       </c>
       <c r="U77">
         <v>0.2417366166625341</v>
       </c>
       <c r="V77">
-        <v>0.06129504760195586</v>
+        <v>0.0604885338177196</v>
       </c>
       <c r="W77">
-        <v>0.2269193592370683</v>
+        <v>0.2271143231505613</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2451801904078235</v>
+        <v>0.2419541352708784</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2096742623985014</v>
+        <v>0.2116336285651267</v>
       </c>
       <c r="C78">
-        <v>-4398.31629726742</v>
+        <v>-4485.078742649954</v>
       </c>
       <c r="D78">
-        <v>999.9317027325797</v>
+        <v>988.117257350046</v>
       </c>
       <c r="E78">
-        <v>-120.3519999999999</v>
+        <v>-45.40400000000045</v>
       </c>
       <c r="F78">
-        <v>5696.048</v>
+        <v>5770.995999999999</v>
       </c>
       <c r="G78">
         <v>297.8</v>
@@ -7689,37 +7689,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M78">
-        <v>1376.943371867394</v>
+        <v>1395.061047813017</v>
       </c>
       <c r="N78">
-        <v>-1043.786229010251</v>
+        <v>-1061.903904955875</v>
       </c>
       <c r="O78">
-        <v>-260.9465572525628</v>
+        <v>-265.4759762389687</v>
       </c>
       <c r="P78">
-        <v>-782.8396717576884</v>
+        <v>-796.427928716906</v>
       </c>
       <c r="Q78">
-        <v>596.8603282423117</v>
+        <v>583.2720712830941</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1544474033503117</v>
+        <v>0.1591712034959774</v>
       </c>
       <c r="T78">
-        <v>2.117740116603085</v>
+        <v>2.209815773846698</v>
       </c>
       <c r="U78">
         <v>0.2417366166625341</v>
       </c>
       <c r="V78">
-        <v>0.0604885338177196</v>
+        <v>0.0597029684434635</v>
       </c>
       <c r="W78">
-        <v>0.2271143231505613</v>
+        <v>0.2273042230663012</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2419541352708784</v>
+        <v>0.238811873773854</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2116336285651267</v>
+        <v>0.2135929947317521</v>
       </c>
       <c r="C79">
-        <v>-4485.078742649954</v>
+        <v>-4571.565266804706</v>
       </c>
       <c r="D79">
-        <v>988.117257350046</v>
+        <v>976.5787331952937</v>
       </c>
       <c r="E79">
-        <v>-45.40400000000045</v>
+        <v>29.54399999999987</v>
       </c>
       <c r="F79">
-        <v>5770.995999999999</v>
+        <v>5845.944</v>
       </c>
       <c r="G79">
         <v>297.8</v>
@@ -7771,37 +7771,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M79">
-        <v>1395.061047813017</v>
+        <v>1413.178723758641</v>
       </c>
       <c r="N79">
-        <v>-1061.903904955875</v>
+        <v>-1080.021580901498</v>
       </c>
       <c r="O79">
-        <v>-265.4759762389687</v>
+        <v>-270.0053952253746</v>
       </c>
       <c r="P79">
-        <v>-796.427928716906</v>
+        <v>-810.0161856761238</v>
       </c>
       <c r="Q79">
-        <v>583.2720712830941</v>
+        <v>569.6838143238763</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1591712034959774</v>
+        <v>0.1643244400185218</v>
       </c>
       <c r="T79">
-        <v>2.209815773846698</v>
+        <v>2.310261945385184</v>
       </c>
       <c r="U79">
         <v>0.2417366166625341</v>
       </c>
       <c r="V79">
-        <v>0.0597029684434635</v>
+        <v>0.0589375457711114</v>
       </c>
       <c r="W79">
-        <v>0.2273042230663012</v>
+        <v>0.2274892537534324</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.238811873773854</v>
+        <v>0.2357501830844456</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2135929947317521</v>
+        <v>0.2155523608983774</v>
       </c>
       <c r="C80">
-        <v>-4571.565266804706</v>
+        <v>-4657.785424191748</v>
       </c>
       <c r="D80">
-        <v>976.5787331952937</v>
+        <v>965.3065758082522</v>
       </c>
       <c r="E80">
-        <v>29.54399999999987</v>
+        <v>104.4920000000002</v>
       </c>
       <c r="F80">
-        <v>5845.944</v>
+        <v>5920.892</v>
       </c>
       <c r="G80">
         <v>297.8</v>
@@ -7853,37 +7853,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M80">
-        <v>1413.178723758641</v>
+        <v>1431.296399704265</v>
       </c>
       <c r="N80">
-        <v>-1080.021580901498</v>
+        <v>-1098.139256847122</v>
       </c>
       <c r="O80">
-        <v>-270.0053952253746</v>
+        <v>-274.5348142117805</v>
       </c>
       <c r="P80">
-        <v>-810.0161856761238</v>
+        <v>-823.6044426353415</v>
       </c>
       <c r="Q80">
-        <v>569.6838143238763</v>
+        <v>556.0955573646586</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1643244400185218</v>
+        <v>0.1699684609717848</v>
       </c>
       <c r="T80">
-        <v>2.310261945385184</v>
+        <v>2.420274418974955</v>
       </c>
       <c r="U80">
         <v>0.2417366166625341</v>
       </c>
       <c r="V80">
-        <v>0.0589375457711114</v>
+        <v>0.05819150088793278</v>
       </c>
       <c r="W80">
-        <v>0.2274892537534324</v>
+        <v>0.2276696001193704</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2357501830844456</v>
+        <v>0.2327660035517312</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2155523608983774</v>
+        <v>0.2175117270650027</v>
       </c>
       <c r="C81">
-        <v>-4657.785424191748</v>
+        <v>-4743.748333175477</v>
       </c>
       <c r="D81">
-        <v>965.3065758082522</v>
+        <v>954.2916668245232</v>
       </c>
       <c r="E81">
-        <v>104.4920000000002</v>
+        <v>179.4400000000005</v>
       </c>
       <c r="F81">
-        <v>5920.892</v>
+        <v>5995.84</v>
       </c>
       <c r="G81">
         <v>297.8</v>
@@ -7935,37 +7935,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M81">
-        <v>1431.296399704265</v>
+        <v>1449.414075649888</v>
       </c>
       <c r="N81">
-        <v>-1098.139256847122</v>
+        <v>-1116.256932792746</v>
       </c>
       <c r="O81">
-        <v>-274.5348142117805</v>
+        <v>-279.0642331981864</v>
       </c>
       <c r="P81">
-        <v>-823.6044426353415</v>
+        <v>-837.1926995945591</v>
       </c>
       <c r="Q81">
-        <v>556.0955573646586</v>
+        <v>542.5073004054409</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1699684609717848</v>
+        <v>0.176176884020374</v>
       </c>
       <c r="T81">
-        <v>2.420274418974955</v>
+        <v>2.541288139923703</v>
       </c>
       <c r="U81">
         <v>0.2417366166625341</v>
       </c>
       <c r="V81">
-        <v>0.05819150088793278</v>
+        <v>0.05746410712683361</v>
       </c>
       <c r="W81">
-        <v>0.2276696001193704</v>
+        <v>0.2278454378261599</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2327660035517312</v>
+        <v>0.2298564285073345</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2175117270650027</v>
+        <v>0.2194710932316281</v>
       </c>
       <c r="C82">
-        <v>-4743.748333175477</v>
+        <v>-4829.462700624862</v>
       </c>
       <c r="D82">
-        <v>954.2916668245232</v>
+        <v>943.5252993751374</v>
       </c>
       <c r="E82">
-        <v>179.4400000000005</v>
+        <v>254.3879999999999</v>
       </c>
       <c r="F82">
-        <v>5995.84</v>
+        <v>6070.788</v>
       </c>
       <c r="G82">
         <v>297.8</v>
@@ -8017,37 +8017,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M82">
-        <v>1449.414075649888</v>
+        <v>1467.531751595512</v>
       </c>
       <c r="N82">
-        <v>-1116.256932792746</v>
+        <v>-1134.374608738369</v>
       </c>
       <c r="O82">
-        <v>-279.0642331981864</v>
+        <v>-283.5936521845923</v>
       </c>
       <c r="P82">
-        <v>-837.1926995945591</v>
+        <v>-850.7809565537768</v>
       </c>
       <c r="Q82">
-        <v>542.5073004054409</v>
+        <v>528.9190434462232</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.176176884020374</v>
+        <v>0.1830388252846042</v>
       </c>
       <c r="T82">
-        <v>2.541288139923703</v>
+        <v>2.675040147288108</v>
       </c>
       <c r="U82">
         <v>0.2417366166625341</v>
       </c>
       <c r="V82">
-        <v>0.05746410712683361</v>
+        <v>0.05675467370551469</v>
       </c>
       <c r="W82">
-        <v>0.2278454378261599</v>
+        <v>0.2280169338611769</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2298564285073345</v>
+        <v>0.2270186948220587</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2194710932316281</v>
+        <v>0.2214304593982534</v>
       </c>
       <c r="C83">
-        <v>-4829.462700624862</v>
+        <v>-4914.936844867068</v>
       </c>
       <c r="D83">
-        <v>943.5252993751374</v>
+        <v>932.9991551329309</v>
       </c>
       <c r="E83">
-        <v>254.3879999999999</v>
+        <v>329.3360000000002</v>
       </c>
       <c r="F83">
-        <v>6070.788</v>
+        <v>6145.736</v>
       </c>
       <c r="G83">
         <v>297.8</v>
@@ -8099,37 +8099,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M83">
-        <v>1467.531751595512</v>
+        <v>1485.649427541136</v>
       </c>
       <c r="N83">
-        <v>-1134.374608738369</v>
+        <v>-1152.492284683993</v>
       </c>
       <c r="O83">
-        <v>-283.5936521845923</v>
+        <v>-288.1230711709982</v>
       </c>
       <c r="P83">
-        <v>-850.7809565537768</v>
+        <v>-864.3692135129945</v>
       </c>
       <c r="Q83">
-        <v>528.9190434462232</v>
+        <v>515.3307864870055</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1830388252846042</v>
+        <v>0.1906632044670822</v>
       </c>
       <c r="T83">
-        <v>2.675040147288108</v>
+        <v>2.823653488804115</v>
       </c>
       <c r="U83">
         <v>0.2417366166625341</v>
       </c>
       <c r="V83">
-        <v>0.05675467370551469</v>
+        <v>0.05606254353837426</v>
       </c>
       <c r="W83">
-        <v>0.2280169338611769</v>
+        <v>0.2281842470660715</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2270186948220587</v>
+        <v>0.224250174153497</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2214304593982534</v>
+        <v>0.2233898255648788</v>
       </c>
       <c r="C84">
-        <v>-4914.936844867068</v>
+        <v>-5000.178717121533</v>
       </c>
       <c r="D84">
-        <v>932.9991551329309</v>
+        <v>922.7052828784671</v>
       </c>
       <c r="E84">
-        <v>329.3360000000002</v>
+        <v>404.2840000000006</v>
       </c>
       <c r="F84">
-        <v>6145.736</v>
+        <v>6220.684</v>
       </c>
       <c r="G84">
         <v>297.8</v>
@@ -8181,37 +8181,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M84">
-        <v>1485.649427541136</v>
+        <v>1503.767103486759</v>
       </c>
       <c r="N84">
-        <v>-1152.492284683993</v>
+        <v>-1170.609960629617</v>
       </c>
       <c r="O84">
-        <v>-288.1230711709982</v>
+        <v>-292.6524901574041</v>
       </c>
       <c r="P84">
-        <v>-864.3692135129945</v>
+        <v>-877.9574704722124</v>
       </c>
       <c r="Q84">
-        <v>515.3307864870055</v>
+        <v>501.7425295277876</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1906632044670822</v>
+        <v>0.1991845694357341</v>
       </c>
       <c r="T84">
-        <v>2.823653488804115</v>
+        <v>2.989750752851415</v>
       </c>
       <c r="U84">
         <v>0.2417366166625341</v>
       </c>
       <c r="V84">
-        <v>0.05606254353837426</v>
+        <v>0.05538709120658661</v>
       </c>
       <c r="W84">
-        <v>0.2281842470660715</v>
+        <v>0.2283475286274747</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.224250174153497</v>
+        <v>0.2215483648263464</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2233898255648788</v>
+        <v>0.2253491917315041</v>
       </c>
       <c r="C85">
-        <v>-5000.178717121533</v>
+        <v>-5085.195921530662</v>
       </c>
       <c r="D85">
-        <v>922.7052828784671</v>
+        <v>912.6360784693372</v>
       </c>
       <c r="E85">
-        <v>404.2840000000006</v>
+        <v>479.232</v>
       </c>
       <c r="F85">
-        <v>6220.684</v>
+        <v>6295.632</v>
       </c>
       <c r="G85">
         <v>297.8</v>
@@ -8263,37 +8263,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M85">
-        <v>1503.767103486759</v>
+        <v>1521.884779432383</v>
       </c>
       <c r="N85">
-        <v>-1170.609960629617</v>
+        <v>-1188.72763657524</v>
       </c>
       <c r="O85">
-        <v>-292.6524901574041</v>
+        <v>-297.18190914381</v>
       </c>
       <c r="P85">
-        <v>-877.9574704722124</v>
+        <v>-891.54572743143</v>
       </c>
       <c r="Q85">
-        <v>501.7425295277876</v>
+        <v>488.15427256857</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1991845694357341</v>
+        <v>0.2087711050254676</v>
       </c>
       <c r="T85">
-        <v>2.989750752851415</v>
+        <v>3.17661017490463</v>
       </c>
       <c r="U85">
         <v>0.2417366166625341</v>
       </c>
       <c r="V85">
-        <v>0.05538709120658661</v>
+        <v>0.05472772107317487</v>
       </c>
       <c r="W85">
-        <v>0.2283475286274747</v>
+        <v>0.2285069225326539</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2215483648263464</v>
+        <v>0.2189108842926994</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2253491917315041</v>
+        <v>0.2273085578981295</v>
       </c>
       <c r="C86">
-        <v>-5085.195921530662</v>
+        <v>-5169.995733893129</v>
       </c>
       <c r="D86">
-        <v>912.636078469338</v>
+        <v>902.7842661068695</v>
       </c>
       <c r="E86">
-        <v>479.232</v>
+        <v>554.1799999999994</v>
       </c>
       <c r="F86">
-        <v>6295.632</v>
+        <v>6370.579999999999</v>
       </c>
       <c r="G86">
         <v>297.8</v>
@@ -8345,37 +8345,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M86">
-        <v>1521.884779432383</v>
+        <v>1540.002455378006</v>
       </c>
       <c r="N86">
-        <v>-1188.72763657524</v>
+        <v>-1206.845312520863</v>
       </c>
       <c r="O86">
-        <v>-297.18190914381</v>
+        <v>-301.7113281302159</v>
       </c>
       <c r="P86">
-        <v>-891.54572743143</v>
+        <v>-905.1339843906476</v>
       </c>
       <c r="Q86">
-        <v>488.15427256857</v>
+        <v>474.5660156093525</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2087711050254674</v>
+        <v>0.2196358453604986</v>
       </c>
       <c r="T86">
-        <v>3.176610174904627</v>
+        <v>3.388384186564936</v>
       </c>
       <c r="U86">
         <v>0.2417366166625341</v>
       </c>
       <c r="V86">
-        <v>0.05472772107317487</v>
+        <v>0.05408386553113752</v>
       </c>
       <c r="W86">
-        <v>0.2285069225326539</v>
+        <v>0.2286625659930055</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2189108842926994</v>
+        <v>0.2163354621245501</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2273085578981295</v>
+        <v>0.2292679240647548</v>
       </c>
       <c r="C87">
-        <v>-5169.995733893129</v>
+        <v>-5254.585119196791</v>
       </c>
       <c r="D87">
-        <v>902.7842661068695</v>
+        <v>893.142880803208</v>
       </c>
       <c r="E87">
-        <v>554.1799999999994</v>
+        <v>629.1279999999997</v>
       </c>
       <c r="F87">
-        <v>6370.579999999999</v>
+        <v>6445.527999999999</v>
       </c>
       <c r="G87">
         <v>297.8</v>
@@ -8427,37 +8427,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M87">
-        <v>1540.002455378006</v>
+        <v>1558.12013132363</v>
       </c>
       <c r="N87">
-        <v>-1206.845312520863</v>
+        <v>-1224.962988466487</v>
       </c>
       <c r="O87">
-        <v>-301.7113281302159</v>
+        <v>-306.2407471166218</v>
       </c>
       <c r="P87">
-        <v>-905.1339843906476</v>
+        <v>-918.7222413498653</v>
       </c>
       <c r="Q87">
-        <v>474.5660156093525</v>
+        <v>460.9777586501348</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2196358453604986</v>
+        <v>0.2320526914576771</v>
       </c>
       <c r="T87">
-        <v>3.388384186564936</v>
+        <v>3.630411628462431</v>
       </c>
       <c r="U87">
         <v>0.2417366166625341</v>
       </c>
       <c r="V87">
-        <v>0.05408386553113752</v>
+        <v>0.05345498337379872</v>
       </c>
       <c r="W87">
-        <v>0.2286625659930055</v>
+        <v>0.228814589838</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2163354621245501</v>
+        <v>0.2138199334951949</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2292679240647548</v>
+        <v>0.2312272902313801</v>
       </c>
       <c r="C88">
-        <v>-5254.585119196791</v>
+        <v>-5338.970748040013</v>
       </c>
       <c r="D88">
-        <v>893.142880803208</v>
+        <v>883.7052519599864</v>
       </c>
       <c r="E88">
-        <v>629.1279999999997</v>
+        <v>704.076</v>
       </c>
       <c r="F88">
-        <v>6445.527999999999</v>
+        <v>6520.476</v>
       </c>
       <c r="G88">
         <v>297.8</v>
@@ -8509,37 +8509,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M88">
-        <v>1558.12013132363</v>
+        <v>1576.237807269254</v>
       </c>
       <c r="N88">
-        <v>-1224.962988466487</v>
+        <v>-1243.080664412111</v>
       </c>
       <c r="O88">
-        <v>-306.2407471166218</v>
+        <v>-310.7701661030277</v>
       </c>
       <c r="P88">
-        <v>-918.7222413498653</v>
+        <v>-932.3104983090831</v>
       </c>
       <c r="Q88">
-        <v>460.9777586501348</v>
+        <v>447.389501690917</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2320526914576771</v>
+        <v>0.2463798215698061</v>
       </c>
       <c r="T88">
-        <v>3.630411628462431</v>
+        <v>3.90967406142108</v>
       </c>
       <c r="U88">
         <v>0.2417366166625341</v>
       </c>
       <c r="V88">
-        <v>0.05345498337379872</v>
+        <v>0.05284055827754815</v>
       </c>
       <c r="W88">
-        <v>0.228814589838</v>
+        <v>0.2289631188819601</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2138199334951949</v>
+        <v>0.2113622331101926</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2312272902313801</v>
+        <v>0.2331866563980055</v>
       </c>
       <c r="C89">
-        <v>-5338.970748040013</v>
+        <v>-5423.159012022747</v>
       </c>
       <c r="D89">
-        <v>883.7052519599864</v>
+        <v>874.4649879772514</v>
       </c>
       <c r="E89">
-        <v>704.076</v>
+        <v>779.0239999999994</v>
       </c>
       <c r="F89">
-        <v>6520.476</v>
+        <v>6595.423999999999</v>
       </c>
       <c r="G89">
         <v>297.8</v>
@@ -8591,37 +8591,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M89">
-        <v>1576.237807269254</v>
+        <v>1594.355483214877</v>
       </c>
       <c r="N89">
-        <v>-1243.080664412111</v>
+        <v>-1261.198340357734</v>
       </c>
       <c r="O89">
-        <v>-310.7701661030277</v>
+        <v>-315.2995850894335</v>
       </c>
       <c r="P89">
-        <v>-932.3104983090831</v>
+        <v>-945.8987552683006</v>
       </c>
       <c r="Q89">
-        <v>447.389501690917</v>
+        <v>433.8012447316994</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2463798215698061</v>
+        <v>0.2630948067006233</v>
       </c>
       <c r="T89">
-        <v>3.90967406142108</v>
+        <v>4.235480233206171</v>
       </c>
       <c r="U89">
         <v>0.2417366166625341</v>
       </c>
       <c r="V89">
-        <v>0.05284055827754815</v>
+        <v>0.05224009738803057</v>
       </c>
       <c r="W89">
-        <v>0.2289631188819601</v>
+        <v>0.2291082722658303</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2113622331101926</v>
+        <v>0.2089603895521223</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2331866563980055</v>
+        <v>0.2351460225646308</v>
       </c>
       <c r="C90">
-        <v>-5423.159012022747</v>
+        <v>-5507.156038182018</v>
       </c>
       <c r="D90">
-        <v>874.4649879772514</v>
+        <v>865.4159618179816</v>
       </c>
       <c r="E90">
-        <v>779.0239999999994</v>
+        <v>853.9719999999998</v>
       </c>
       <c r="F90">
-        <v>6595.423999999999</v>
+        <v>6670.371999999999</v>
       </c>
       <c r="G90">
         <v>297.8</v>
@@ -8673,37 +8673,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M90">
-        <v>1594.355483214877</v>
+        <v>1612.473159160501</v>
       </c>
       <c r="N90">
-        <v>-1261.198340357734</v>
+        <v>-1279.316016303358</v>
       </c>
       <c r="O90">
-        <v>-315.2995850894335</v>
+        <v>-319.8290040758395</v>
       </c>
       <c r="P90">
-        <v>-945.8987552683006</v>
+        <v>-959.4870122275183</v>
       </c>
       <c r="Q90">
-        <v>433.8012447316994</v>
+        <v>420.2129877724817</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2630948067006233</v>
+        <v>0.2828488800370436</v>
       </c>
       <c r="T90">
-        <v>4.235480233206171</v>
+        <v>4.620523890770368</v>
       </c>
       <c r="U90">
         <v>0.2417366166625341</v>
       </c>
       <c r="V90">
-        <v>0.05224009738803057</v>
+        <v>0.0516531300016482</v>
       </c>
       <c r="W90">
-        <v>0.2291082722658303</v>
+        <v>0.2292501637759056</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2089603895521223</v>
+        <v>0.2066125200065928</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2351460225646308</v>
+        <v>0.2371053887312561</v>
       </c>
       <c r="C91">
-        <v>-5507.156038182018</v>
+        <v>-5590.967702540295</v>
       </c>
       <c r="D91">
-        <v>865.4159618179816</v>
+        <v>856.5522974597042</v>
       </c>
       <c r="E91">
-        <v>853.9719999999998</v>
+        <v>928.9200000000001</v>
       </c>
       <c r="F91">
-        <v>6670.371999999999</v>
+        <v>6745.32</v>
       </c>
       <c r="G91">
         <v>297.8</v>
@@ -8755,37 +8755,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M91">
-        <v>1612.473159160501</v>
+        <v>1630.590835106124</v>
       </c>
       <c r="N91">
-        <v>-1279.316016303358</v>
+        <v>-1297.433692248982</v>
       </c>
       <c r="O91">
-        <v>-319.8290040758395</v>
+        <v>-324.3584230622454</v>
       </c>
       <c r="P91">
-        <v>-959.4870122275183</v>
+        <v>-973.0752691867361</v>
       </c>
       <c r="Q91">
-        <v>420.2129877724817</v>
+        <v>406.6247308132639</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2828488800370436</v>
+        <v>0.306553768040748</v>
       </c>
       <c r="T91">
-        <v>4.620523890770368</v>
+        <v>5.082576279847405</v>
       </c>
       <c r="U91">
         <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.0516531300016482</v>
+        <v>0.05107920633496322</v>
       </c>
       <c r="W91">
-        <v>0.2292501637759056</v>
+        <v>0.2293889021413126</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2066125200065928</v>
+        <v>0.2043168253398528</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2371053887312561</v>
+        <v>0.2390647548978815</v>
       </c>
       <c r="C92">
-        <v>-5590.967702540295</v>
+        <v>-5674.599642829743</v>
       </c>
       <c r="D92">
-        <v>856.5522974597042</v>
+        <v>847.8683571702562</v>
       </c>
       <c r="E92">
-        <v>928.9200000000001</v>
+        <v>1003.867999999999</v>
       </c>
       <c r="F92">
-        <v>6745.32</v>
+        <v>6820.267999999999</v>
       </c>
       <c r="G92">
         <v>297.8</v>
@@ -8837,37 +8837,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M92">
-        <v>1630.590835106124</v>
+        <v>1648.708511051748</v>
       </c>
       <c r="N92">
-        <v>-1297.433692248982</v>
+        <v>-1315.551368194605</v>
       </c>
       <c r="O92">
-        <v>-324.3584230622454</v>
+        <v>-328.8878420486512</v>
       </c>
       <c r="P92">
-        <v>-973.0752691867361</v>
+        <v>-986.6635261459537</v>
       </c>
       <c r="Q92">
-        <v>406.6247308132639</v>
+        <v>393.0364738540463</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.306553768040748</v>
+        <v>0.3355264089341644</v>
       </c>
       <c r="T92">
-        <v>5.082576279847405</v>
+        <v>5.647306977608228</v>
       </c>
       <c r="U92">
         <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.05107920633496322</v>
+        <v>0.05051789637523835</v>
       </c>
       <c r="W92">
-        <v>0.2293889021413126</v>
+        <v>0.2295245913118755</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2043168253398528</v>
+        <v>0.2020715855009534</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2390647548978815</v>
+        <v>0.2410241210645068</v>
       </c>
       <c r="C93">
-        <v>-5674.599642829743</v>
+        <v>-5758.057270450207</v>
       </c>
       <c r="D93">
-        <v>847.8683571702562</v>
+        <v>839.3587295497917</v>
       </c>
       <c r="E93">
-        <v>1003.867999999999</v>
+        <v>1078.816</v>
       </c>
       <c r="F93">
-        <v>6820.267999999999</v>
+        <v>6895.215999999999</v>
       </c>
       <c r="G93">
         <v>297.8</v>
@@ -8919,37 +8919,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M93">
-        <v>1648.708511051748</v>
+        <v>1666.826186997372</v>
       </c>
       <c r="N93">
-        <v>-1315.551368194605</v>
+        <v>-1333.669044140229</v>
       </c>
       <c r="O93">
-        <v>-328.8878420486512</v>
+        <v>-333.4172610350572</v>
       </c>
       <c r="P93">
-        <v>-986.6635261459537</v>
+        <v>-1000.251783105172</v>
       </c>
       <c r="Q93">
-        <v>393.0364738540463</v>
+        <v>379.4482168948284</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3355264089341644</v>
+        <v>0.3717422100509351</v>
       </c>
       <c r="T93">
-        <v>5.647306977608228</v>
+        <v>6.353220349809259</v>
       </c>
       <c r="U93">
         <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.05051789637523835</v>
+        <v>0.04996878880594228</v>
       </c>
       <c r="W93">
-        <v>0.2295245913118755</v>
+        <v>0.2296573307178609</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2020715855009534</v>
+        <v>0.1998751552237691</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2410241210645068</v>
+        <v>0.2429834872311322</v>
       </c>
       <c r="C94">
-        <v>-5758.057270450207</v>
+        <v>-5841.345781714286</v>
       </c>
       <c r="D94">
-        <v>839.3587295497917</v>
+        <v>831.0182182857136</v>
       </c>
       <c r="E94">
-        <v>1078.816</v>
+        <v>1153.764</v>
       </c>
       <c r="F94">
-        <v>6895.215999999999</v>
+        <v>6970.164</v>
       </c>
       <c r="G94">
         <v>297.8</v>
@@ -9001,37 +9001,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M94">
-        <v>1666.826186997372</v>
+        <v>1684.943862942995</v>
       </c>
       <c r="N94">
-        <v>-1333.669044140229</v>
+        <v>-1351.786720085852</v>
       </c>
       <c r="O94">
-        <v>-333.4172610350572</v>
+        <v>-337.9466800214631</v>
       </c>
       <c r="P94">
-        <v>-1000.251783105172</v>
+        <v>-1013.840040064389</v>
       </c>
       <c r="Q94">
-        <v>379.4482168948284</v>
+        <v>365.8599599356107</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3717422100509351</v>
+        <v>0.4183053829153544</v>
       </c>
       <c r="T94">
-        <v>6.353220349809259</v>
+        <v>7.260823256924867</v>
       </c>
       <c r="U94">
         <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.04996878880594228</v>
+        <v>0.0494314900015773</v>
       </c>
       <c r="W94">
-        <v>0.2296573307178609</v>
+        <v>0.2297872155129649</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1998751552237691</v>
+        <v>0.1977259600063093</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2429834872311322</v>
+        <v>0.2449428533977575</v>
       </c>
       <c r="C95">
-        <v>-5841.345781714286</v>
+        <v>-5924.470168428533</v>
       </c>
       <c r="D95">
-        <v>831.0182182857136</v>
+        <v>822.8418315714675</v>
       </c>
       <c r="E95">
-        <v>1153.764</v>
+        <v>1228.712</v>
       </c>
       <c r="F95">
-        <v>6970.164</v>
+        <v>7045.112</v>
       </c>
       <c r="G95">
         <v>297.8</v>
@@ -9083,37 +9083,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M95">
-        <v>1684.943862942995</v>
+        <v>1703.061538888619</v>
       </c>
       <c r="N95">
-        <v>-1351.786720085852</v>
+        <v>-1369.904396031476</v>
       </c>
       <c r="O95">
-        <v>-337.9466800214631</v>
+        <v>-342.476099007869</v>
       </c>
       <c r="P95">
-        <v>-1013.840040064389</v>
+        <v>-1027.428297023607</v>
       </c>
       <c r="Q95">
-        <v>365.8599599356107</v>
+        <v>352.2717029763928</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4183053829153544</v>
+        <v>0.480389613401247</v>
       </c>
       <c r="T95">
-        <v>7.260823256924867</v>
+        <v>8.470960466412349</v>
       </c>
       <c r="U95">
         <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.0494314900015773</v>
+        <v>0.04890562308666691</v>
       </c>
       <c r="W95">
-        <v>0.2297872155129649</v>
+        <v>0.2299143368017901</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1977259600063093</v>
+        <v>0.1956224923466676</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2449428533977575</v>
+        <v>0.2469022195643829</v>
       </c>
       <c r="C96">
-        <v>-5924.470168428533</v>
+        <v>-6007.435227856107</v>
       </c>
       <c r="D96">
-        <v>822.8418315714675</v>
+        <v>814.8247721438922</v>
       </c>
       <c r="E96">
-        <v>1228.712</v>
+        <v>1303.66</v>
       </c>
       <c r="F96">
-        <v>7045.112</v>
+        <v>7120.059999999999</v>
       </c>
       <c r="G96">
         <v>297.8</v>
@@ -9165,37 +9165,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M96">
-        <v>1703.061538888619</v>
+        <v>1721.179214834242</v>
       </c>
       <c r="N96">
-        <v>-1369.904396031476</v>
+        <v>-1388.0220719771</v>
       </c>
       <c r="O96">
-        <v>-342.476099007869</v>
+        <v>-347.0055179942749</v>
       </c>
       <c r="P96">
-        <v>-1027.428297023607</v>
+        <v>-1041.016553982825</v>
       </c>
       <c r="Q96">
-        <v>352.2717029763928</v>
+        <v>338.6834460171754</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.480389613401247</v>
+        <v>0.5673075360814966</v>
       </c>
       <c r="T96">
-        <v>8.470960466412349</v>
+        <v>10.16515255969482</v>
       </c>
       <c r="U96">
         <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.04890562308666691</v>
+        <v>0.04839082705417568</v>
       </c>
       <c r="W96">
-        <v>0.2299143368017901</v>
+        <v>0.2300387818529559</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1956224923466676</v>
+        <v>0.1935633082167028</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2469022195643829</v>
+        <v>0.2488615857310082</v>
       </c>
       <c r="C97">
-        <v>-6007.435227856107</v>
+        <v>-6090.245572102654</v>
       </c>
       <c r="D97">
-        <v>814.8247721438922</v>
+        <v>806.9624278973454</v>
       </c>
       <c r="E97">
-        <v>1303.66</v>
+        <v>1378.608</v>
       </c>
       <c r="F97">
-        <v>7120.059999999999</v>
+        <v>7195.008</v>
       </c>
       <c r="G97">
         <v>297.8</v>
@@ -9247,37 +9247,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M97">
-        <v>1721.179214834242</v>
+        <v>1739.296890779866</v>
       </c>
       <c r="N97">
-        <v>-1388.0220719771</v>
+        <v>-1406.139747922723</v>
       </c>
       <c r="O97">
-        <v>-347.0055179942749</v>
+        <v>-351.5349369806808</v>
       </c>
       <c r="P97">
-        <v>-1041.016553982825</v>
+        <v>-1054.604810942042</v>
       </c>
       <c r="Q97">
-        <v>338.6834460171754</v>
+        <v>325.0951890579577</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5673075360814966</v>
+        <v>0.6976844201018709</v>
       </c>
       <c r="T97">
-        <v>10.16515255969482</v>
+        <v>12.70644069961853</v>
       </c>
       <c r="U97">
         <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.04839082705417568</v>
+        <v>0.04788675593902801</v>
       </c>
       <c r="W97">
-        <v>0.2300387818529559</v>
+        <v>0.2301606342988889</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1935633082167028</v>
+        <v>0.1915470237561121</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2488615857310082</v>
+        <v>0.2508209518976335</v>
       </c>
       <c r="C98">
-        <v>-6090.245572102655</v>
+        <v>-6172.905636963954</v>
       </c>
       <c r="D98">
-        <v>806.9624278973438</v>
+        <v>799.2503630360452</v>
       </c>
       <c r="E98">
-        <v>1378.607999999999</v>
+        <v>1453.556</v>
       </c>
       <c r="F98">
-        <v>7195.007999999999</v>
+        <v>7269.955999999999</v>
       </c>
       <c r="G98">
         <v>297.8</v>
@@ -9329,37 +9329,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M98">
-        <v>1739.296890779866</v>
+        <v>1757.41456672549</v>
       </c>
       <c r="N98">
-        <v>-1406.139747922723</v>
+        <v>-1424.257423868347</v>
       </c>
       <c r="O98">
-        <v>-351.5349369806808</v>
+        <v>-356.0643559670867</v>
       </c>
       <c r="P98">
-        <v>-1054.604810942042</v>
+        <v>-1068.19306790126</v>
       </c>
       <c r="Q98">
-        <v>325.0951890579579</v>
+        <v>311.50693209874</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6976844201018693</v>
+        <v>0.9149792268024924</v>
       </c>
       <c r="T98">
-        <v>12.7064406996185</v>
+        <v>16.94192093282467</v>
       </c>
       <c r="U98">
         <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.04788675593902802</v>
+        <v>0.04739307804274938</v>
       </c>
       <c r="W98">
-        <v>0.2301606342988889</v>
+        <v>0.2302799743232564</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1915470237561121</v>
+        <v>0.1895723121709976</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2508209518976335</v>
+        <v>0.2527803180642589</v>
       </c>
       <c r="C99">
-        <v>-6172.905636963954</v>
+        <v>-6255.419690271059</v>
       </c>
       <c r="D99">
-        <v>799.2503630360452</v>
+        <v>791.6843097289402</v>
       </c>
       <c r="E99">
-        <v>1453.556</v>
+        <v>1528.504</v>
       </c>
       <c r="F99">
-        <v>7269.955999999999</v>
+        <v>7344.904</v>
       </c>
       <c r="G99">
         <v>297.8</v>
@@ -9411,37 +9411,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M99">
-        <v>1757.41456672549</v>
+        <v>1775.532242671113</v>
       </c>
       <c r="N99">
-        <v>-1424.257423868347</v>
+        <v>-1442.37509981397</v>
       </c>
       <c r="O99">
-        <v>-356.0643559670867</v>
+        <v>-360.5937749534926</v>
       </c>
       <c r="P99">
-        <v>-1068.19306790126</v>
+        <v>-1081.781324860478</v>
       </c>
       <c r="Q99">
-        <v>311.50693209874</v>
+        <v>297.9186751395223</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9149792268024924</v>
+        <v>1.349568840203739</v>
       </c>
       <c r="T99">
-        <v>16.94192093282467</v>
+        <v>25.412881399237</v>
       </c>
       <c r="U99">
         <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.04739307804274938</v>
+        <v>0.04690947520557846</v>
       </c>
       <c r="W99">
-        <v>0.2302799743232564</v>
+        <v>0.2303968788369225</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1895723121709976</v>
+        <v>0.1876379008223139</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2527803180642589</v>
+        <v>0.2547396842308842</v>
       </c>
       <c r="C100">
-        <v>-6255.419690271059</v>
+        <v>-6337.791839765881</v>
       </c>
       <c r="D100">
-        <v>791.6843097289402</v>
+        <v>784.2601602341177</v>
       </c>
       <c r="E100">
-        <v>1528.504</v>
+        <v>1603.451999999999</v>
       </c>
       <c r="F100">
-        <v>7344.904</v>
+        <v>7419.851999999999</v>
       </c>
       <c r="G100">
         <v>297.8</v>
@@ -9493,37 +9493,37 @@
         <v>333.1571428571428</v>
       </c>
       <c r="M100">
-        <v>1775.532242671113</v>
+        <v>1793.649918616737</v>
       </c>
       <c r="N100">
-        <v>-1442.37509981397</v>
+        <v>-1460.492775759594</v>
       </c>
       <c r="O100">
-        <v>-360.5937749534926</v>
+        <v>-365.1231939398984</v>
       </c>
       <c r="P100">
-        <v>-1081.781324860478</v>
+        <v>-1095.369581819695</v>
       </c>
       <c r="Q100">
-        <v>297.9186751395223</v>
+        <v>284.3304181803048</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.349568840203739</v>
+        <v>2.653337680407477</v>
       </c>
       <c r="T100">
-        <v>25.412881399237</v>
+        <v>50.825762798474</v>
       </c>
       <c r="U100">
         <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.04690947520557846</v>
+        <v>0.04643564212269384</v>
       </c>
       <c r="W100">
-        <v>0.2303968788369225</v>
+        <v>0.2305114216432418</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1876379008223139</v>
+        <v>0.1857425684907753</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2547396842308842</v>
-      </c>
-      <c r="C101">
-        <v>-6337.791839765881</v>
-      </c>
-      <c r="D101">
-        <v>784.2601602341177</v>
-      </c>
-      <c r="E101">
-        <v>1603.451999999999</v>
-      </c>
-      <c r="F101">
-        <v>7419.851999999999</v>
-      </c>
-      <c r="G101">
-        <v>297.8</v>
-      </c>
-      <c r="H101">
-        <v>1678.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1712.857142857143</v>
-      </c>
-      <c r="K101">
-        <v>1379.7</v>
-      </c>
-      <c r="L101">
-        <v>333.1571428571428</v>
-      </c>
-      <c r="M101">
-        <v>1793.649918616737</v>
-      </c>
-      <c r="N101">
-        <v>-1460.492775759594</v>
-      </c>
-      <c r="O101">
-        <v>-365.1231939398984</v>
-      </c>
-      <c r="P101">
-        <v>-1095.369581819695</v>
-      </c>
-      <c r="Q101">
-        <v>284.3304181803048</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.653337680407477</v>
-      </c>
-      <c r="T101">
-        <v>50.825762798474</v>
-      </c>
-      <c r="U101">
-        <v>0.2417366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.04643564212269384</v>
-      </c>
-      <c r="W101">
-        <v>0.2305114216432418</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1857425684907753</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
